--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,451 +453,271 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>311307</v>
+        <v>301843</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOLINHO DE TILAPIA 270GR CONG</t>
+          <t>APERITIVO BITER CAMPARI 998ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.99</v>
+        <v>78.98999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>303488</v>
+        <v>215568</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAMARAO CINZA COSTAMAR 1KG DESC 51/60</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>115.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>323487</v>
+        <v>174010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAMARAO VAN S/C COZ  IQF-M 45/80 40X300G</t>
+          <t>CACHACA SELETA 600ML</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.99</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>262170</v>
+        <v>287369</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>COSTELA DE TILAPIA KG</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>141831</v>
+        <v>170451</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FILE DE PEIXE PANGA KG</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>44.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>315711</v>
+        <v>247800</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILE DE TILAPIA DO PESCADO 500G</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>203263</v>
+        <v>177250</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FILE DE TILAPIA KG</t>
+          <t>CERV DEVASSA PURO MALTE 269ML C/ 12UND</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>323489</v>
+        <v>303283</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>25.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>323501</v>
+        <v>286362</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PEIXE SALMAO COSTA SUL 400GR C/PELE FILE</t>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>48.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>254014</v>
+        <v>108686</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PESCADA AMARELA FILE 1KG</t>
+          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>35.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>284245</v>
+        <v>155994</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
+          <t>VINHO GALIOTTO 1LT TINTO SECO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEXTA - FRUTOS DO MAR 10/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>284246</v>
+        <v>139964</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
+          <t>VINHO PERGOLA TINTO SUAVE 1LT</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>105461</v>
+        <v>110373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.99</v>
+        <v>83.98999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105458</v>
+        <v>248750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.99</v>
+        <v>55.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
+          <t>SABADAO - BIRITAO 12/04/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>105451</v>
+        <v>102077</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>WHISKY OLD PARR 12 ANOS 1L</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>38.99</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>105449</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>BOVINO - COXAO DURO KG</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>105453</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>BOVINO - FILE MIGNON KG</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>40.99</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>105474</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>BOVINO - FRALDINHA KG</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>31.99</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>305039</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>106053</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>105062</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>106054</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>SUINO - LOMBO FRESCO KG</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>106052</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>106034</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>SUINO - SUAN FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SEXTA - AÇOUGUE 11/04/25</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>106032</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>19.99</v>
+        <v>179.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -720,6 +720,132 @@
         <v>179.99</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>105470</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BOVINO - ACEM KG</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>105450</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BOVINO - ALCATRA KG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>105456</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>105474</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BOVINO - FRALDINHA KG</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>107260</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BOVINO - MACA DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>305039</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 12/04/25</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>105475</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MUSCULO BOV KG</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,213 +453,213 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>301843</v>
+        <v>105842</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>APERITIVO BITER CAMPARI 998ML</t>
+          <t>ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>78.98999999999999</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>215568</v>
+        <v>227503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>39.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>174010</v>
+        <v>105838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CACHACA SELETA 600ML</t>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>45.99</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>287369</v>
+        <v>105840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.59</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>170451</v>
+        <v>306504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>247800</v>
+        <v>109597</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.69</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>177250</v>
+        <v>108786</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CERV DEVASSA PURO MALTE 269ML C/ 12UND</t>
+          <t>FILEZINHO PEITO SADIA  PACOTE 1KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>2.79</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>303283</v>
+        <v>108788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286362</v>
+        <v>105853</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
+          <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>9.49</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>108686</v>
+        <v>185934</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
+          <t>GALINHA LEVE NOROESTE CONG KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>155994</v>
+        <v>228422</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>VINHO GALIOTTO 1LT TINTO SECO</t>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>26.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>139964</v>
+        <v>108774</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>VINHO PERGOLA TINTO SUAVE 1LT</t>
+          <t>MEIO DA  ASA FRANGO SADIA 1KG TULIPA PAC</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -669,61 +669,61 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>110373</v>
+        <v>108773</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>83.98999999999999</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - COROCOCO 14/04/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>248750</v>
+        <v>105770</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+          <t>MORTADELA FRANGO PERDIGAO KG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>55.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADAO - BIRITAO 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>102077</v>
+        <v>105460</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>WHISKY OLD PARR 12 ANOS 1L</t>
+          <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>179.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -741,97 +741,97 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>105450</v>
+        <v>158997</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOVINO - ALCATRA KG</t>
+          <t>BOVINO - BISTECA DO ACEM KG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>37.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105456</v>
+        <v>105458</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>26.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>105474</v>
+        <v>115278</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>BOVINO - MIOLO DA PALETA KG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>31.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>107260</v>
+        <v>231292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>BOVINO - MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>28.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>305039</v>
+        <v>105469</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>BOVINO - PALETA KG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 12/04/25</t>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -844,6 +844,906 @@
       </c>
       <c r="D23" t="n">
         <v>21.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>106032</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SUINO - TOUCINHO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>255232</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ACHOC PO TODDY 750G</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>298736</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>298239</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>107878</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>179914</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>136523</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>100020</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ARROZ REALENGO 5KG BRANCO TIPO 1</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>199440</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ARROZ SANTA FE 5 KG TP1</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>111378</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>250013</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>102085</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>101137</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>170451</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>298701</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4.09</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>184034</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>101063</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>110330</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>100391</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>100394</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>100392</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>100402</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML COCO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>100403</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>100393</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML MACA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>100390</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>102282</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ENERG RED BULL 250ML TRAD</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>273714</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>128930</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>279573</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>255841</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO AMAFIL 500G</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>108434</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>231627</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>LEITE EM PO INTEGRAL CAMPONESA 1KG</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>101113</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>290255</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MACARRAO CRISTAL 500GR SEMOLA ESPAGUETE</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>101728</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>130920</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>100054</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OLEO SOJA BREJEIRO 900 ML</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>104404</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>REFRIG FANTA LARANJA 2L</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>104410</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>239315</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ROSQ COCO RANCHEIRO 600G</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>289451</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>228234</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>100706</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>221089</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO OLEO 125G</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>100373</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SODA CAUSTICA SOL 1KG</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>102237</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 14/04/25</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>106961</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3.29</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,1297 +453,1333 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105842</v>
+        <v>255232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASA FRANGO KG</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.89</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>227503</v>
+        <v>298239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.99</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105838</v>
+        <v>100431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COXA/SOBRECOXA FRANGO KG</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.89</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105840</v>
+        <v>116139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA FRANGO KG</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>306504</v>
+        <v>107395</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109597</v>
+        <v>225670</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILE PEITO FRANGO KG</t>
+          <t>ARROZ BENTO TIPO 1 5KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108786</v>
+        <v>100038</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FILEZINHO PEITO SADIA  PACOTE 1KG</t>
+          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.99</v>
+        <v>35.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108788</v>
+        <v>136523</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.99</v>
+        <v>33.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105853</v>
+        <v>234617</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FRANGO CONG MARINGA KG</t>
+          <t>BISC CREAM CRACKER ESTRELA 350G</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.29</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>185934</v>
+        <v>199869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GALINHA LEVE NOROESTE CONG KG</t>
+          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.99</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>228422</v>
+        <v>102085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.99</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108774</v>
+        <v>101137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MEIO DA  ASA FRANGO SADIA 1KG TULIPA PAC</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>108773</v>
+        <v>170451</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105770</v>
+        <v>247800</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MORTADELA FRANGO PERDIGAO KG</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>105460</v>
+        <v>239382</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>CERV DEVASSA PURO MALTE 269ML UNID</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>105470</v>
+        <v>298701</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM KG</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158997</v>
+        <v>184034</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA DO ACEM KG</t>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105458</v>
+        <v>324556</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>115278</v>
+        <v>101063</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DA PALETA KG</t>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.99</v>
+        <v>4.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>231292</v>
+        <v>112978</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DO ACEM KG</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>105469</v>
+        <v>134193</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOVINO - PALETA KG</t>
+          <t>DESINFETANTE BAK YPE FLORAL 2LTS</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105475</v>
+        <v>100391</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MUSCULO BOV KG</t>
+          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>106034</v>
+        <v>100394</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>106032</v>
+        <v>100392</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>255232</v>
+        <v>100402</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>298736</v>
+        <v>100403</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>298239</v>
+        <v>100393</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.390000000000001</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>107878</v>
+        <v>100390</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>179914</v>
+        <v>102282</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.49</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>136523</v>
+        <v>273714</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100020</v>
+        <v>100024</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ARROZ REALENGO 5KG BRANCO TIPO 1</t>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>199440</v>
+        <v>100014</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>111378</v>
+        <v>100119</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>250013</v>
+        <v>139059</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>LAVA LOUCAS LIQ YPE LIMAO FRASCO 500ML</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102085</v>
+        <v>108434</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101137</v>
+        <v>101113</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>170451</v>
+        <v>106922</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.79</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>298701</v>
+        <v>131884</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4.09</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>184034</v>
+        <v>101726</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>101063</v>
+        <v>130920</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.69</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>110330</v>
+        <v>106680</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.19</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100391</v>
+        <v>128920</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>100394</v>
+        <v>104404</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
+          <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>100392</v>
+        <v>104406</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>100402</v>
+        <v>261360</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML COCO</t>
+          <t>SABAO BARRA MINUANO NEUTRO GLIC 5X180G</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>100403</v>
+        <v>228234</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>100393</v>
+        <v>100705</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML MACA</t>
+          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>100390</v>
+        <v>100693</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
+          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>102282</v>
+        <v>100373</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8.69</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>273714</v>
+        <v>100876</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>128930</v>
+        <v>106961</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - OFERTAS 16/04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>100024</v>
+        <v>106960</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>279573</v>
+        <v>104937</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>255841</v>
+        <v>105023</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO AMAFIL 500G</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.89</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>108434</v>
+        <v>105010</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>231627</v>
+        <v>105001</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEITE EM PO INTEGRAL CAMPONESA 1KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>39.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>101113</v>
+        <v>104919</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>290255</v>
+        <v>104862</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MACARRAO CRISTAL 500GR SEMOLA ESPAGUETE</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>101728</v>
+        <v>104931</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.99</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>130920</v>
+        <v>104944</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.99</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>100054</v>
+        <v>104928</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OLEO SOJA BREJEIRO 900 ML</t>
+          <t>MANGA PALMER KG</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.390000000000001</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>104404</v>
+        <v>104947</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LARANJA 2L</t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9.49</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>104410</v>
+        <v>104996</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+          <t>MELAO AMARELO KG</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>104406</v>
+        <v>239921</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>OVOS BRANCOS CARTELA 30 UNID</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.49</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>239315</v>
+        <v>104992</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ROSQ COCO RANCHEIRO 600G</t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - VERDURA 16/04/25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>289451</v>
+        <v>104961</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>27.99</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>228234</v>
+        <v>105470</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>BOVINO - ACEM KG</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>100706</v>
+        <v>105459</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5.59</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>221089</v>
+        <v>105449</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO OLEO 125G</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5.59</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>100373</v>
+        <v>107260</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
+          <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>102237</v>
+        <v>115278</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+          <t>BOVINO - MIOLO DA PALETA KG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>27.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>106961</v>
+        <v>231292</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+          <t>BOVINO - MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3.29</v>
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>305039</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 16/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,1297 +453,1549 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105842</v>
+        <v>255232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASA FRANGO KG</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.89</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>227503</v>
+        <v>298239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105838</v>
+        <v>100426</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COXA/SOBRECOXA FRANGO KG</t>
+          <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.89</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105840</v>
+        <v>207640</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA FRANGO KG</t>
+          <t>AGUA SANITARIA LAVABEM 2L</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.59</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>306504</v>
+        <v>133368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+          <t>AMAC +FAMILIA ORIG 5 LT</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>5.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109597</v>
+        <v>181416</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILE PEITO FRANGO KG</t>
+          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108786</v>
+        <v>107394</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FILEZINHO PEITO SADIA  PACOTE 1KG</t>
+          <t>AMAC ROUPAS YPE 2L CARINHO</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108788</v>
+        <v>107393</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+          <t>AMAC ROUPAS YPE 2L INTENSO</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105853</v>
+        <v>106711</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FRANGO CONG MARINGA KG</t>
+          <t>AMAC ROUPAS YPE 2LT ACONCHEGO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.29</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>185934</v>
+        <v>106712</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GALINHA LEVE NOROESTE CONG KG</t>
+          <t>AMAC ROUPAS YPE 2LT TERNURA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>228422</v>
+        <v>107413</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+          <t>AMACIANTE YPE 2L DELICADO BRANCO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108774</v>
+        <v>179914</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MEIO DA  ASA FRANGO SADIA 1KG TULIPA PAC</t>
+          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>29.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>108773</v>
+        <v>245393</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+          <t>AMACIANTE YPE ACONCHEGO L2 P1,6 L</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105770</v>
+        <v>100037</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MORTADELA FRANGO PERDIGAO KG</t>
+          <t>ARROZ PAINHO 5KG BRANCO TIPO 1 BRANCO TI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>105460</v>
+        <v>100040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>ARROZ TIO JORGE 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>19.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>105470</v>
+        <v>113480</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM KG</t>
+          <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158997</v>
+        <v>132657</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA DO ACEM KG</t>
+          <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.99</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105458</v>
+        <v>123206</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>AZEITONA LA VIOLETERA FATIADA 160GR SACH</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>115278</v>
+        <v>250013</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DA PALETA KG</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>231292</v>
+        <v>239682</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DO ACEM KG</t>
+          <t>BOMBOM GAROTO SORTIDO 250G</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>25.99</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>105469</v>
+        <v>237036</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOVINO - PALETA KG</t>
+          <t>BOMBOM NESTLE ESPECIALIDADES 251G</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>21.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105475</v>
+        <v>181622</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MUSCULO BOV KG</t>
+          <t>BOMBONS LACTA FAVORITOS  250,6 GR</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.99</v>
+        <v>17.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>106034</v>
+        <v>114037</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>106032</v>
+        <v>239446</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
+          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>255232</v>
+        <v>242930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>298736</v>
+        <v>303283</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO ITALAKINHO 200ML CHOCOLATE</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>298239</v>
+        <v>324556</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.390000000000001</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>107878</v>
+        <v>295198</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+          <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>4.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>179914</v>
+        <v>101066</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
+          <t>CREME LEITE ITALAC 200GR TP</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.49</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>136523</v>
+        <v>247502</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+          <t>DESINFETANTE +FAMILIA 5LT LAVANDA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>30.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100020</v>
+        <v>207582</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ARROZ REALENGO 5KG BRANCO TIPO 1</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>28.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>199440</v>
+        <v>256724</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>27.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>111378</v>
+        <v>207588</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>250013</v>
+        <v>207586</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102085</v>
+        <v>207584</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101137</v>
+        <v>100780</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>15.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>170451</v>
+        <v>134629</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.79</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>298701</v>
+        <v>200178</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>FEIJAO CARIOCA DONA DE 1KG</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4.09</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>184034</v>
+        <v>100120</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>101063</v>
+        <v>155080</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>4.69</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>110330</v>
+        <v>231627</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+          <t>LEITE EM PO INTEGRAL CAMPONESA 1KG</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.19</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100391</v>
+        <v>170363</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>100394</v>
+        <v>183340</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
+          <t>LEITE UHT ITALAC SEMI DESNATADO 1L</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.99</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>100392</v>
+        <v>156422</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>100402</v>
+        <v>101728</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML COCO</t>
+          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>100403</v>
+        <v>108414</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
+          <t>MASSA LASANHA CRISTAL 500G</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>100393</v>
+        <v>302126</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML MACA</t>
+          <t>MASSA P/ TAPIOCA DONA DE 1KG HIDRATADA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>100390</v>
+        <v>107640</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
+          <t>MILHO VERDE QUERO 170GR LATA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>102282</v>
+        <v>101130</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>MIST BOLO DONA BENTA 450GR CASEICHOCOLAT</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8.69</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>273714</v>
+        <v>321107</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>128930</v>
+        <v>244444</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
+          <t>MOLHO TOMATE DEZ 300GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>100024</v>
+        <v>100754</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+          <t>PALMITO PERIQUITU 300GR ACAI INTEIRO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>279573</v>
+        <v>236651</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+          <t>PAPEL HIGIENICO NOBLE 12X20M</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>5.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>255841</v>
+        <v>104404</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO AMAFIL 500G</t>
+          <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.89</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>108434</v>
+        <v>104410</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>231627</v>
+        <v>104406</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LEITE EM PO INTEGRAL CAMPONESA 1KG</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>39.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>101113</v>
+        <v>239315</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
+          <t>ROSQ COCO RANCHEIRO 600G</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>290255</v>
+        <v>286199</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MACARRAO CRISTAL 500GR SEMOLA ESPAGUETE</t>
+          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>101728</v>
+        <v>261083</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>130920</v>
+        <v>100706</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>100054</v>
+        <v>221089</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OLEO SOJA BREJEIRO 900 ML</t>
+          <t>SARDINHA COQUEIRO OLEO 125G</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.390000000000001</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>104404</v>
+        <v>100373</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LARANJA 2L</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>104410</v>
+        <v>102237</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>104406</v>
+        <v>100876</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>239315</v>
+        <v>155994</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ROSQ COCO RANCHEIRO 600G</t>
+          <t>VINHO GALIOTTO 1LT TINTO SECO</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 17 A 20/04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>289451</v>
+        <v>139964</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
+          <t>VINHO PERGOLA TINTO SUAVE 1LT</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>27.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>228234</v>
+        <v>311307</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>BOLINHO DE TILAPIA 270GR CONG</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>100706</v>
+        <v>303488</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>CAMARAO CINZA COSTAMAR 1KG DESC 51/60</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5.59</v>
+        <v>115.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>221089</v>
+        <v>323487</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO OLEO 125G</t>
+          <t>CAMARAO VAN S/C COZ  IQF-M 45/80 40X300G</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5.59</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>100373</v>
+        <v>262170</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
+          <t>COSTELA DE TILAPIA KG</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>102237</v>
+        <v>141831</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+          <t>FILE DE PEIXE PANGA KG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>27.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 14/04/25</t>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>106961</v>
+        <v>315711</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+          <t>FILE DE TILAPIA DO PESCADO 500G</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3.29</v>
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>323489</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>323501</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>PEIXE SALMAO COSTA SUL 400GR C/PELE FILE</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>284245</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>QUINTA - FRUTOS DO MAR 17/04/25</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>284246</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>105468</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>105458</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BOVINO - CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>105435</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>305039</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>106053</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>320822</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PALETA FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>106054</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SUINO - LOMBO FRESCO KG</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>106052</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QUINTA - SUINO 17/04/25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,1333 +453,703 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255232</v>
+        <v>157014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>298239</v>
+        <v>152232</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>BOVINO - BUCHO/HUMEM KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.289999999999999</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100431</v>
+        <v>105458</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>116139</v>
+        <v>105451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>107395</v>
+        <v>105471</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>225670</v>
+        <v>105449</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARROZ BENTO TIPO 1 5KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>27.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100038</v>
+        <v>107260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
+          <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>35.69</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>136523</v>
+        <v>305039</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>33.29</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>234617</v>
+        <v>189031</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BISC CREAM CRACKER ESTRELA 350G</t>
+          <t>LINGUICA MISTA FRICO KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.19</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>199869</v>
+        <v>105475</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
+          <t>MUSCULO BOV KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.79</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102085</v>
+        <v>105062</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.59</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101137</v>
+        <v>105433</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - AÇOUGUE 19/04/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>170451</v>
+        <v>106052</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.79</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>247800</v>
+        <v>229014</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>AGUA DE COCO MAIS COCO 1L</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>239382</v>
+        <v>215568</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CERV DEVASSA PURO MALTE 269ML UNID</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2.69</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>298701</v>
+        <v>174010</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>CACHACA SELETA 600ML</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>184034</v>
+        <v>158451</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>CACHACA YPIOCA PRATA S/ PALHA 965 ML</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5.89</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>324556</v>
+        <v>170451</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>40.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>101063</v>
+        <v>247800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>4.79</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>112978</v>
+        <v>267604</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500GR</t>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>134193</v>
+        <v>184034</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DESINFETANTE BAK YPE FLORAL 2LTS</t>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>100391</v>
+        <v>309102</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100394</v>
+        <v>298123</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK UNID</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>100392</v>
+        <v>259153</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
+          <t>CERVEJA SPATEN PURO MALTE LT 350ML C/12U</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2.69</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100402</v>
+        <v>244424</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML COCO</t>
+          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>100403</v>
+        <v>253877</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
+          <t>ENERG BALY DRINK 2LT COCO E ACAI PET</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100393</v>
+        <v>253878</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML MACA</t>
+          <t>ENERG BALY ENERGY DRINK 2LT</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>100390</v>
+        <v>253880</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
+          <t>ENERG BALY MACA VERDE PET 2LT</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>102282</v>
+        <v>244426</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>ENERGETICO BALY 2L  FRUTAS TROPICAIS PET</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>8.789999999999999</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>273714</v>
+        <v>305261</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+          <t>ENERGETICO BALY 2L ABACAXI C/HORTELA DAS</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>7.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100024</v>
+        <v>320467</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+          <t>ENERGETICO BALY 2L CITRUS PET</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>5.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100014</v>
+        <v>302661</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>ENERGETICO BALY 2L MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>5.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>100119</v>
+        <v>302660</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+          <t>ENERGETICO BALY 2L TANGERINA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.89</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>139059</v>
+        <v>303008</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LAVA LOUCAS LIQ YPE LIMAO FRASCO 500ML</t>
+          <t>ENERGETICO BALY ENERGY 2L CRANBERRY PET</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>108434</v>
+        <v>102287</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101113</v>
+        <v>161871</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
+          <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.69</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO- BIRITAO 19/04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>106922</v>
+        <v>134156</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>VODKA SKYY 980ML</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>44.99</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - PREÇO BALA 17/04/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>131884</v>
+        <v>100038</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>3.49</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 16/04</t>
+          <t>SABADO - PREÇO BALA 17/04/25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>101726</v>
+        <v>106680</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D40" t="n">
         <v>8.99</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>130920</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
-        </is>
-      </c>
-      <c r="D41" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>106680</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>OLEO SOJA SOYA  900ML</t>
-        </is>
-      </c>
-      <c r="D42" t="n">
-        <v>9.59</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>128920</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>104404</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>REFRIG FANTA LARANJA 2L</t>
-        </is>
-      </c>
-      <c r="D44" t="n">
-        <v>9.69</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>104406</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>261360</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>SABAO BARRA MINUANO NEUTRO GLIC 5X180G</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>9.99</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>228234</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>100705</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
-        </is>
-      </c>
-      <c r="D48" t="n">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>100693</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>5.49</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>100373</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>100876</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>14.99</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>106961</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>QUARTA - OFERTAS 16/04</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>106960</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>104937</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>105023</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>6.39</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>105010</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>6.59</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>105001</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>104919</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>104862</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>104931</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>8.890000000000001</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>104944</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>MACA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="D61" t="n">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>104928</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>MANGA PALMER KG</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>104947</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="D63" t="n">
-        <v>2.99</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>104996</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>MELAO AMARELO KG</t>
-        </is>
-      </c>
-      <c r="D64" t="n">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>239921</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>OVOS BRANCOS CARTELA 30 UNID</t>
-        </is>
-      </c>
-      <c r="D65" t="n">
-        <v>0.75</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>104992</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>REPOLHO VERDE KG</t>
-        </is>
-      </c>
-      <c r="D66" t="n">
-        <v>3.49</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 16/04/25</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>104961</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="D67" t="n">
-        <v>9.390000000000001</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>105470</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>BOVINO - ACEM KG</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>105459</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>BOVINO - BISTECA MACA PEITO KG</t>
-        </is>
-      </c>
-      <c r="D69" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>105449</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>BOVINO - COXAO DURO KG</t>
-        </is>
-      </c>
-      <c r="D70" t="n">
-        <v>30.99</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>107260</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="D71" t="n">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>115278</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>BOVINO - MIOLO DA PALETA KG</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>231292</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>BOVINO - MIOLO DO ACEM KG</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>305039</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>15.99</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 16/04/25</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>106034</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>SUINO - SUAN FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1152,6 +1152,168 @@
         <v>8.99</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>105010</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>BATATA MONALISA KG</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>105001</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>104862</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>104931</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>104855</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LIMAO TAITI KG</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>4.69</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>104962</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MARACUJA AZEDO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>104992</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>104961</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,703 +453,1405 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>157014</v>
+        <v>105842</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM C/ OSSO KG</t>
+          <t>ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.99</v>
+        <v>14.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>152232</v>
+        <v>227503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105458</v>
+        <v>105838</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105451</v>
+        <v>105840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.99</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>306504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105449</v>
+        <v>108786</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>FILEZINHO PEITO SADIA  PACOTE 1KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>107260</v>
+        <v>108788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>305039</v>
+        <v>225767</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>FRANGO CONGELADO BONASA KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189031</v>
+        <v>185934</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LINGUICA MISTA FRICO KG</t>
+          <t>GALINHA LEVE NOROESTE CONG KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105475</v>
+        <v>228422</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MUSCULO BOV KG</t>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105062</v>
+        <v>309350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>MASSA PASTEL JK 1KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>105433</v>
+        <v>309331</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUINO - COSTELA SUINA KG</t>
+          <t>MASSA PASTEL JK 500GR DISCAO</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106052</v>
+        <v>309332</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
+          <t>MASSA PASTEL JK 500GR ROLO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>229014</v>
+        <v>108774</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AGUA DE COCO MAIS COCO 1L</t>
+          <t>MEIO DA  ASA FRANGO SADIA 1KG TULIPA PAC</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - COROCOCO 19/04/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>215568</v>
+        <v>108773</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174010</v>
+        <v>157014</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CACHACA SELETA 600ML</t>
+          <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158451</v>
+        <v>105470</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CACHACA YPIOCA PRATA S/ PALHA 965 ML</t>
+          <t>BOVINO - ACEM KG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170451</v>
+        <v>105456</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.79</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>247800</v>
+        <v>105463</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>BOVINO - CORACAO KG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.99</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>267604</v>
+        <v>105449</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>184034</v>
+        <v>105487</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>BOVINO - CUPIM KG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.99</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>309102</v>
+        <v>305039</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.19</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>298123</v>
+        <v>105475</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK UNID</t>
+          <t>MUSCULO BOV KG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.19</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>259153</v>
+        <v>320822</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN PURO MALTE LT 350ML C/12U</t>
+          <t>SUINO - BISTECA PALETA FRESCA KG</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.59</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>244424</v>
+        <v>106054</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - AÇOUGUE 21/04/25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>253877</v>
+        <v>106034</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ENERG BALY DRINK 2LT COCO E ACAI PET</t>
+          <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>253878</v>
+        <v>255232</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ENERG BALY ENERGY DRINK 2LT</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>253880</v>
+        <v>298239</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ENERG BALY MACA VERDE PET 2LT</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>244426</v>
+        <v>100426</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L  FRUTAS TROPICAIS PET</t>
+          <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.99</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>305261</v>
+        <v>116139</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ABACAXI C/HORTELA DAS</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.99</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>320467</v>
+        <v>107395</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L CITRUS PET</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.99</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>302661</v>
+        <v>225670</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L MORANGO E PESSEGO</t>
+          <t>ARROZ BENTO TIPO 1 5KG</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>302660</v>
+        <v>325990</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L TANGERINA</t>
+          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>303008</v>
+        <v>258938</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY ENERGY 2L CRANBERRY PET</t>
+          <t>ARROZ BRILHANTE TIPO1 BRANCO 5KG</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102287</v>
+        <v>100031</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4.99</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>161871</v>
+        <v>261728</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA TUCHAUA 2LT</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>134156</v>
+        <v>199869</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VODKA SKYY 980ML</t>
+          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>59.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>100038</v>
+        <v>239682</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
+          <t>BOMBOM GAROTO SORTIDO 250G</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>101137</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>287369</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>170451</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>249597</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CERV HEINEKEN ZERO ALCOOL 330ML UNID</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>242930</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>295198</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>155079</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CREME DE LEITE LEITBOM TP 200G</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>112978</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>247502</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 5LT LAVANDA</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>100423</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML COCO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>100419</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>220037</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>204461</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>100420</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>100417</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML MACA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>106661</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>102282</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ENERG RED BULL 250ML TRAD</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>273714</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>128930</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FARINHA MANDIOCA AMAFIL AMARELA OURO 1KG</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>167687</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>FEIJAO CARIOCA JOAOZINHO PREMIUM 1KG</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>255841</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO AMAFIL 500G</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>108434</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>170363</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>307145</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>303196</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>101726</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>130920</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>244444</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MOLHO TOMATE DEZ 300GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
         <v>106680</v>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C69" t="inlineStr">
         <is>
           <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
-      <c r="D40" t="n">
+      <c r="D69" t="n">
         <v>8.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>236651</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO NOBLE 12X20M</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>104404</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>REFRIG FANTA LARANJA 2L</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>108686</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>150356</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SABAO LIQUIDO OMO 3L MULTIACAO</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>40.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>286199</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>261083</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>100876</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>106961</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>3.89</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 21/04/25</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>106960</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>3.89</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,865 +453,1693 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>157014</v>
+        <v>255232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM C/ OSSO KG</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>152232</v>
+        <v>298239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105458</v>
+        <v>100431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105451</v>
+        <v>133368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>AMAC +FAMILIA ORIG 5 LT</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.99</v>
+        <v>17.49</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>269680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>ARROZ DONA VAVA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105449</v>
+        <v>136523</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>107260</v>
+        <v>100020</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>ARROZ REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>28.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>305039</v>
+        <v>186826</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>BISCOITO CREAM CRACKER GALLO 360GR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.99</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>189031</v>
+        <v>315855</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LINGUICA MISTA FRICO KG</t>
+          <t>BISCOITO RENATA 360GR COCO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>18.99</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105475</v>
+        <v>102085</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MUSCULO BOV KG</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.99</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105062</v>
+        <v>114037</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.99</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>105433</v>
+        <v>242311</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUINO - COSTELA SUINA KG</t>
+          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 19/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106052</v>
+        <v>287369</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>229014</v>
+        <v>298701</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AGUA DE COCO MAIS COCO 1L</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.99</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>215568</v>
+        <v>184034</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>39.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>174010</v>
+        <v>324556</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CACHACA SELETA 600ML</t>
+          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>44.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158451</v>
+        <v>107928</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CACHACA YPIOCA PRATA S/ PALHA 965 ML</t>
+          <t>CR DENTAL COLGATE MPA 180G</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>170451</v>
+        <v>101063</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.79</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>247800</v>
+        <v>208281</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>DES AERO MOOD MEN 150ML</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>267604</v>
+        <v>208304</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>184034</v>
+        <v>208280</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>DES AERO MOOD WOMEN 150ML</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>309102</v>
+        <v>247502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
+          <t>DESINFETANTE +FAMILIA 5LT LAVANDA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>6.19</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>298123</v>
+        <v>312369</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK UNID</t>
+          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>259153</v>
+        <v>312371</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CERVEJA SPATEN PURO MALTE LT 350ML C/12U</t>
+          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>244424</v>
+        <v>312370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>253877</v>
+        <v>312366</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ENERG BALY DRINK 2LT COCO E ACAI PET</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>253878</v>
+        <v>312367</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ENERG BALY ENERGY DRINK 2LT</t>
+          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>253880</v>
+        <v>312368</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ENERG BALY MACA VERDE PET 2LT</t>
+          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>244426</v>
+        <v>298929</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L  FRUTAS TROPICAIS PET</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>305261</v>
+        <v>298928</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ABACAXI C/HORTELA DAS</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>320467</v>
+        <v>298927</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L CITRUS PET</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>302661</v>
+        <v>298933</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L MORANGO E PESSEGO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>302660</v>
+        <v>298932</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L TANGERINA</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>303008</v>
+        <v>298931</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY ENERGY 2L CRANBERRY PET</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>102287</v>
+        <v>298930</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>161871</v>
+        <v>311881</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA TUCHAUA 2LT</t>
+          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO- BIRITAO 19/04</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>134156</v>
+        <v>100423</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>VODKA SKYY 980ML</t>
+          <t>DETERG LIQ LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>59.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>100038</v>
+        <v>100419</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
+          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>31.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/04/25</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>106680</v>
+        <v>220037</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>105010</v>
+        <v>204461</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>105001</v>
+        <v>100420</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>104862</v>
+        <v>100417</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>DETERG LIQ LIMPOL 500ML MACA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>104931</v>
+        <v>106661</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>9.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>104855</v>
+        <v>312365</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LIMAO TAITI KG</t>
+          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104962</v>
+        <v>312364</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MARACUJA AZEDO</t>
+          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>104947</v>
+        <v>102287</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>104992</v>
+        <v>273714</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>4.39</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FINAL DE SEMANA  - HORTIFRUTI</t>
+          <t>TERCA - OFERTAS 22/04/2025</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>104961</v>
+        <v>155501</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>FARINHA DE TRIGO MIRELLA S/FERMENTO</t>
         </is>
       </c>
       <c r="D49" t="n">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>286381</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>FEIJAO DONA DE 1KG PRETO</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>163918</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>100119</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>113183</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LEITE COND MARAJOARA 395GR SEMIDESNATADO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>6.79</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>170363</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>106922</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>43.99</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>183340</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>LEITE UHT ITALAC SEMI DESNATADO 1L</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>131884</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>101728</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>12.69</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>169708</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>MASSA PRONTA PARA TAPIOCA DO ZE 500GR AL</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>107640</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MILHO VERDE QUERO 170GR LATA</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>321107</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2.29</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>106680</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>OLEO SOJA SOYA  900ML</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>145874</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>POLVILHO AMAFIL MATUTO AZEDO 1KG</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
         <v>10.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>104403</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>REFRIG FANTA UVA 2L</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>104424</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>REFRIG PEPSI COLA PET 2L</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>239315</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>ROSQ COCO RANCHEIRO 600G</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>248450</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>22.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>319396</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR  ANTIBAC LIMPEZA PR</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>276292</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR FRUTAS VERMELHAS</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>276293</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR LAVANDA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>276291</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR LIRIO SELVAGEM</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>276290</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR ROSA AVELUDADA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>319398</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR SUAVE CAPIM LIMAO V</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>319397</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY 85GR SUAVE JASMIM ROXO</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>193867</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY SUAVE 85G HID. INTEN</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>193868</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY SUAVE 85G LEITE DE COCO</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>193870</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY SUAVE 85G MENT HOM</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>193869</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY SUAVE 85G MULT HOM</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>193865</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY SUAVE CONTRO HOME 85G</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>193866</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SABONETE ALBANY SUAVE MACD. AVEI 85G</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>227599</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SABONTE ALBANY SUAVE ANTIBAC 85GR EXT DE</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>100705</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>100693</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>100373</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SODA CAUSTICA SOL 1KG</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>106831</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>TEMP COMPLETO SABORELLE 930GR</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>TERCA - OFERTAS 22/04/2025</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>109729</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>WHISKY WHITE HORSE 1LT</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>99.98999999999999</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>239334</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>105458</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BOVINO - CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>107260</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BOVINO - MACA DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>231292</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BOVINO - MIOLO DO ACEM KG</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>105469</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BOVINO - PALETA KG</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>105452</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BOVINO - PATINHO KG</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>106053</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>TERÇA - AÇOUGUE 22/04/25</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>18.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D95"/>
+  <dimension ref="A1:D84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,141 +453,141 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255232</v>
+        <v>104937</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>298239</v>
+        <v>105023</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.390000000000001</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100431</v>
+        <v>105010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.39</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>133368</v>
+        <v>105001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AMAC +FAMILIA ORIG 5 LT</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>269680</v>
+        <v>104919</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ARROZ DONA VAVA 5KG TIPO 1</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.99</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>136523</v>
+        <v>104862</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100020</v>
+        <v>104931</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ARROZ REALENGO 5KG BRANCO TIPO 1</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>26.99</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>186826</v>
+        <v>104855</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BISCOITO CREAM CRACKER GALLO 360GR</t>
+          <t>LIMAO TAITI KG</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -597,573 +597,573 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>315855</v>
+        <v>104944</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BISCOITO RENATA 360GR COCO</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.89</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>102085</v>
+        <v>104928</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>MANGA PALMER KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>114037</v>
+        <v>104947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>242311</v>
+        <v>104996</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
+          <t>MELAO AMARELO KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>8.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>287369</v>
+        <v>104992</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - VERDURA 23/04/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>298701</v>
+        <v>104961</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.19</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>184034</v>
+        <v>255232</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.89</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>324556</v>
+        <v>298239</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL PILSEN 269ML CAIXA C/15 MUL</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>40.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>107928</v>
+        <v>107878</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CR DENTAL COLGATE MPA 180G</t>
+          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>7.99</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>101063</v>
+        <v>116139</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>4.69</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>208281</v>
+        <v>107395</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DES AERO MOOD MEN 150ML</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>208304</v>
+        <v>100038</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
+          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.99</v>
+        <v>35.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>208280</v>
+        <v>199440</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DES AERO MOOD WOMEN 150ML</t>
+          <t>ARROZ SANTA FE 5 KG TP1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>6.99</v>
+        <v>29.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>247502</v>
+        <v>113480</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 5LT LAVANDA</t>
+          <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.99</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>312369</v>
+        <v>132657</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
+          <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>6.99</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>312371</v>
+        <v>107799</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
+          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>6.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>312370</v>
+        <v>261728</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6.99</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>312366</v>
+        <v>199869</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
+          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>6.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>312367</v>
+        <v>102085</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>6.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>312368</v>
+        <v>215568</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>6.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>298929</v>
+        <v>115855</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CAFE 3CORACOES EXTRAFORTE 250G</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6.99</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>298928</v>
+        <v>101137</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>298927</v>
+        <v>242311</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>298933</v>
+        <v>252992</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>298932</v>
+        <v>170451</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>298931</v>
+        <v>247800</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>298930</v>
+        <v>239446</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>311881</v>
+        <v>242930</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.99</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>100423</v>
+        <v>309102</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML COCO</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2.69</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>100419</v>
+        <v>107376</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.69</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>220037</v>
+        <v>101066</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
+          <t>CREME LEITE ITALAC 200GR TP</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>204461</v>
+        <v>112978</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1173,973 +1173,775 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>100420</v>
+        <v>148554</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
+          <t>DESINFETANTE BAK YPE EUCALIPTO 2LTS</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100417</v>
+        <v>207588</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML MACA</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>106661</v>
+        <v>207586</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.69</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>312365</v>
+        <v>207584</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>312364</v>
+        <v>207582</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>102287</v>
+        <v>256724</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>4.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>273714</v>
+        <v>102282</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.289999999999999</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>155501</v>
+        <v>100780</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA S/FERMENTO</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>5.29</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>286381</v>
+        <v>155501</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FEIJAO DONA DE 1KG PRETO</t>
+          <t>FARINHA DE TRIGO MIRELLA S/FERMENTO</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>8.69</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>163918</v>
+        <v>100027</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FEIJAO KICALDO 1KG CARIOCA</t>
+          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6.99</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>100119</v>
+        <v>279573</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.79</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>113183</v>
+        <v>166152</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LEITE COND MARAJOARA 395GR SEMIDESNATADO</t>
+          <t>FLOCAO MILHO SUPER FLOCAO CORINGA 500GR</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.79</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>170363</v>
+        <v>155080</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>106922</v>
+        <v>170363</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>43.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>183340</v>
+        <v>307145</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LEITE UHT ITALAC SEMI DESNATADO 1L</t>
+          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6.69</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>131884</v>
+        <v>156422</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>101728</v>
+        <v>108415</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.69</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>169708</v>
+        <v>303196</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MASSA PRONTA PARA TAPIOCA DO ZE 500GR AL</t>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>5.19</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>107640</v>
+        <v>101726</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MILHO VERDE QUERO 170GR LATA</t>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>321107</v>
+        <v>313828</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
+          <t>MASSA TAPIOCA AMAFIL MATUTO 500GR SEMI P</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.29</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>106680</v>
+        <v>130920</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>145874</v>
+        <v>106680</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>POLVILHO AMAFIL MATUTO AZEDO 1KG</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>104403</v>
+        <v>316048</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REFRIG FANTA UVA 2L</t>
+          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>9.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>104424</v>
+        <v>128920</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REFRIG PEPSI COLA PET 2L</t>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>7.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>104406</v>
+        <v>122984</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>REFRI SPRITE PET 2L</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>239315</v>
+        <v>161871</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ROSQ COCO RANCHEIRO 600G</t>
+          <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>248450</v>
+        <v>104406</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>22.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>319396</v>
+        <v>257710</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR  ANTIBAC LIMPEZA PR</t>
+          <t>SABAO BARRA YPE 5X180GR NEUTRO GLICERINA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1.99</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>276292</v>
+        <v>228234</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR FRUTAS VERMELHAS</t>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.99</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>276293</v>
+        <v>100706</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR LAVANDA</t>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>276291</v>
+        <v>259589</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR LIRIO SELVAGEM</t>
+          <t>STELLA ARTOIS ONE WAY 600ML</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1.99</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>276290</v>
+        <v>100876</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR ROSA AVELUDADA</t>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>319398</v>
+        <v>106961</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR SUAVE CAPIM LIMAO V</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>319397</v>
+        <v>106960</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY 85GR SUAVE JASMIM ROXO</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>193867</v>
+        <v>152232</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY SUAVE 85G HID. INTEN</t>
+          <t>BOVINO - BUCHO/HUMEM KG</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>193868</v>
+        <v>105456</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY SUAVE 85G LEITE DE COCO</t>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>193870</v>
+        <v>105449</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY SUAVE 85G MENT HOM</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>193869</v>
+        <v>105435</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY SUAVE 85G MULT HOM</t>
+          <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>193865</v>
+        <v>173342</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY SUAVE CONTRO HOME 85G</t>
+          <t>BOVINO - MOCOTO KG</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>193866</v>
+        <v>105475</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SABONETE ALBANY SUAVE MACD. AVEI 85G</t>
+          <t>MUSCULO BOV KG</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>227599</v>
+        <v>105433</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SABONTE ALBANY SUAVE ANTIBAC 85GR EXT DE</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>100705</v>
+        <v>106052</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>5.39</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>100693</v>
+        <v>106034</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+          <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>5.39</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>100373</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>25.99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>106831</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>TEMP COMPLETO SABORELLE 930GR</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TERCA - OFERTAS 22/04/2025</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>109729</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>WHISKY WHITE HORSE 1LT</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>99.98999999999999</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>239334</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>105458</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>BOVINO - CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>107260</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>231292</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>BOVINO - MIOLO DO ACEM KG</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>26.99</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>105469</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>BOVINO - PALETA KG</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>105452</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>BOVINO - PATINHO KG</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>106053</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>TERÇA - AÇOUGUE 22/04/25</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>105062</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>18.99</v>
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,1494 +453,1386 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>104937</v>
+        <v>318330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105023</v>
+        <v>298239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.39</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105010</v>
+        <v>100426</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.59</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105001</v>
+        <v>112174</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>ALCOOL START 1L 70INPM</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104919</v>
+        <v>116139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4.29</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>104862</v>
+        <v>107395</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>104931</v>
+        <v>269680</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>ARROZ DONA VAVA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.890000000000001</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104855</v>
+        <v>100037</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LIMAO TAITI KG</t>
+          <t>ARROZ PAINHO 5KG BRANCO TIPO 1 BRANCO TI</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.59</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104944</v>
+        <v>225003</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.89</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104928</v>
+        <v>186826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>BISCOITO CREAM CRACKER GALLO 360GR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.99</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104947</v>
+        <v>315854</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>BISCOITO RENATA 360GR MAIZENA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.69</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104996</v>
+        <v>102085</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>7.39</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104992</v>
+        <v>114037</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 23/04/25</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104961</v>
+        <v>287369</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>255232</v>
+        <v>170451</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>298239</v>
+        <v>168466</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>CERV EISENBAHN L.NECK PILSEN 355ML</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>8.49</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>107878</v>
+        <v>298701</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4.89</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>116139</v>
+        <v>242930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>7.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>107395</v>
+        <v>309102</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>7.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100038</v>
+        <v>107376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199440</v>
+        <v>286362</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.39</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113480</v>
+        <v>155079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
+          <t>CREME DE LEITE LEITBOM TP 200G</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.49</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>132657</v>
+        <v>110330</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65.98999999999999</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>107799</v>
+        <v>247502</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
+          <t>DESINFETANTE +FAMILIA 5LT LAVANDA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>261728</v>
+        <v>100423</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+          <t>DETERG LIQ LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>199869</v>
+        <v>100419</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
+          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102085</v>
+        <v>220037</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>215568</v>
+        <v>204461</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>115855</v>
+        <v>100420</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CAFE 3CORACOES EXTRAFORTE 250G</t>
+          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.89</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>101137</v>
+        <v>100417</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>DETERG LIQ LIMPOL 500ML MACA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>242311</v>
+        <v>106661</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
+          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8.49</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>252992</v>
+        <v>253879</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
+          <t>ENERG BALY MACA VERDE LATA 250ML</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>170451</v>
+        <v>244425</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>ENERG.BALY FRUTAS TROPICAIS LATA 250ML</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.89</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>247800</v>
+        <v>244427</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>ENERG.BALY MELANCIA LATA 250ML</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>239446</v>
+        <v>318892</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
+          <t>ENERGETICO BALY 250ML ABACAXI  C/ HORTEL</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.29</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>242930</v>
+        <v>244422</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>ENERGETICO BALY 250ML COCO E ACAI</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.89</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>309102</v>
+        <v>312640</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
+          <t>ENERGETICO BALY 250ML COLA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6.19</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>107376</v>
+        <v>303516</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
+          <t>ENERGETICO BALY 250ML FLYNOW S/ACUCAR</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>101066</v>
+        <v>312067</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CREME LEITE ITALAC 200GR TP</t>
+          <t>ENERGETICO BALY 250ML FRUTAS VERMELHAS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>112978</v>
+        <v>302658</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500GR</t>
+          <t>ENERGETICO BALY 250ML MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>148554</v>
+        <v>302659</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DESINFETANTE BAK YPE EUCALIPTO 2LTS</t>
+          <t>ENERGETICO BALY 250ML TANGERINA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>207588</v>
+        <v>312639</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>ENERGETICO BALY 250ML TROPICAL ZERO ACUC</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>207586</v>
+        <v>303517</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>ENERGETICO BALY 250ML ZERO ACUCAR</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>207584</v>
+        <v>100780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.69</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>207582</v>
+        <v>134629</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1.69</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>256724</v>
+        <v>163918</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1.69</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>102282</v>
+        <v>100119</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>100780</v>
+        <v>170363</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>155501</v>
+        <v>106922</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA S/FERMENTO</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5.19</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>100027</v>
+        <v>131884</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.289999999999999</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>279573</v>
+        <v>101728</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6.39</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>166152</v>
+        <v>302126</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SUPER FLOCAO CORINGA 500GR</t>
+          <t>MASSA P/ TAPIOCA DONA DE 1KG HIDRATADA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>155080</v>
+        <v>107640</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
+          <t>MILHO VERDE QUERO 170GR LATA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.69</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>170363</v>
+        <v>101130</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+          <t>MIST BOLO DONA BENTA 450GR CASEICHOCOLAT</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>7.69</v>
+        <v>7.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>307145</v>
+        <v>321107</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
+          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20.89</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>156422</v>
+        <v>106680</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.99</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>108415</v>
+        <v>144572</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
+          <t>POLVILHO DOCE LOPES 1KG</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3.89</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>303196</v>
+        <v>104404</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
+          <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.39</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>101726</v>
+        <v>108686</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+          <t>REFRIG SODA LIMONADA ANTARCTICA PET 2 LT</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8.99</v>
+        <v>7.79</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>313828</v>
+        <v>104406</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MASSA TAPIOCA AMAFIL MATUTO 500GR SEMI P</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>130920</v>
+        <v>239315</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>ROSQ COCO RANCHEIRO 600G</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3.89</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>106680</v>
+        <v>286199</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9.49</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>316048</v>
+        <v>261083</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
+          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>128920</v>
+        <v>100373</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>122984</v>
+        <v>100876</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REFRI SPRITE PET 2L</t>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9.69</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>SEMANAL - OFERTAS ARRASADORAS 24 A 27/04</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>161871</v>
+        <v>109729</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA TUCHAUA 2LT</t>
+          <t>WHISKY WHITE HORSE 1LT</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7.99</v>
+        <v>110.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>104406</v>
+        <v>105460</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>257710</v>
+        <v>105459</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SABAO BARRA YPE 5X180GR NEUTRO GLICERINA</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.79</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>228234</v>
+        <v>105451</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15.89</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>100706</v>
+        <v>105471</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5.69</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>259589</v>
+        <v>105469</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>STELLA ARTOIS ONE WAY 600ML</t>
+          <t>BOVINO - PALETA KG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.59</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>100876</v>
+        <v>106008</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+          <t>INGREDIENTES P/ FEIJOADA KG</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>106961</v>
+        <v>106053</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>106960</v>
+        <v>105062</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>3.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>152232</v>
+        <v>105433</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>105456</v>
+        <v>106054</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUINTA - AÇOUGUE 23/04/25</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>105449</v>
+        <v>106052</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>33.99</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>105435</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>BOVINO - COXAO MOLE KG</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>173342</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>BOVINO - MOCOTO KG</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>105475</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>MUSCULO BOV KG</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>105433</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>SUINO - COSTELA SUINA KG</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>106052</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>12.49</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>106034</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>SUINO - SUAN FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
         <v>13.99</v>
       </c>
     </row>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>6.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="4">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>6.59</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="5">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>4.59</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="10">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10.89</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="11">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="13">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>8.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -799,15 +799,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100038</v>
+        <v>225670</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
+          <t>ARROZ BENTO TIPO 1 5KG</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>35.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="22">
@@ -817,15 +817,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>199440</v>
+        <v>100038</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>ARROZ BREJEIRO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>29.39</v>
+        <v>32.69</v>
       </c>
     </row>
     <row r="23">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113480</v>
+        <v>199440</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
+          <t>ARROZ SANTA FE 5 KG TP1</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>33.49</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="24">
@@ -853,15 +853,15 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>132657</v>
+        <v>113480</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
+          <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>65.98999999999999</v>
+        <v>33.49</v>
       </c>
     </row>
     <row r="25">
@@ -871,15 +871,15 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>107799</v>
+        <v>132657</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
+          <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>10.99</v>
+        <v>65.98999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>261728</v>
+        <v>107799</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>6.69</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="27">
@@ -907,15 +907,15 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>199869</v>
+        <v>261728</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.69</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="28">
@@ -925,15 +925,15 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>102085</v>
+        <v>199869</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="29">
@@ -943,15 +943,15 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>215568</v>
+        <v>102085</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>39.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="30">
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>115855</v>
+        <v>215568</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CAFE 3CORACOES EXTRAFORTE 250G</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.89</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="31">
@@ -979,15 +979,15 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>101137</v>
+        <v>115855</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>CAFE 3CORACOES EXTRAFORTE 250G</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>16.99</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="32">
@@ -997,15 +997,15 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>242311</v>
+        <v>101137</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>8.49</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="33">
@@ -1015,15 +1015,15 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>252992</v>
+        <v>242311</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
+          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="34">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>170451</v>
+        <v>252992</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.89</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="35">
@@ -1051,15 +1051,15 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>247800</v>
+        <v>170451</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>5.69</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="36">
@@ -1069,15 +1069,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>239446</v>
+        <v>247800</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.29</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="37">
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>242930</v>
+        <v>239446</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.89</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="38">
@@ -1105,15 +1105,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>309102</v>
+        <v>242930</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6.19</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="39">
@@ -1123,15 +1123,15 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>107376</v>
+        <v>309102</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK C/12UN</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.99</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="40">
@@ -1141,15 +1141,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>101066</v>
+        <v>107376</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CREME LEITE ITALAC 200GR TP</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.79</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="41">
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>112978</v>
+        <v>101066</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500GR</t>
+          <t>CREME LEITE ITALAC 200GR TP</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.69</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="42">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>148554</v>
+        <v>112978</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DESINFETANTE BAK YPE EUCALIPTO 2LTS</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="43">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>207588</v>
+        <v>148554</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>DESINFETANTE BAK YPE EUCALIPTO 2LTS</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="44">
@@ -1285,15 +1285,15 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>102282</v>
+        <v>207588</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>DETERG LIQ LAVABEM 500ML</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>8.99</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="49">
@@ -1303,15 +1303,15 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>100780</v>
+        <v>102282</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="50">
@@ -1321,15 +1321,15 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>155501</v>
+        <v>100780</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FARINHA DE TRIGO MIRELLA S/FERMENTO</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>5.19</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="51">
@@ -1339,15 +1339,15 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>100027</v>
+        <v>155501</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
+          <t>FARINHA DE TRIGO MIRELLA S/FERMENTO</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>8.289999999999999</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="52">
@@ -1357,15 +1357,15 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>279573</v>
+        <v>100027</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
+          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6.39</v>
+        <v>8.289999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -1375,15 +1375,15 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>166152</v>
+        <v>279573</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SUPER FLOCAO CORINGA 500GR</t>
+          <t>FEIJAO DONA MARIA 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.29</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="54">
@@ -1393,15 +1393,15 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>155080</v>
+        <v>166152</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
+          <t>FLOCAO MILHO SUPER FLOCAO CORINGA 500GR</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>7.69</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="55">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>170363</v>
+        <v>155080</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1429,15 +1429,15 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>307145</v>
+        <v>170363</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>20.89</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="57">
@@ -1447,15 +1447,15 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>156422</v>
+        <v>307145</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>5.99</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="58">
@@ -1465,15 +1465,15 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>108415</v>
+        <v>156422</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>3.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="59">
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>303196</v>
+        <v>108415</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
+          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.39</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="60">
@@ -1501,15 +1501,15 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>101726</v>
+        <v>303196</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>8.99</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="61">
@@ -1519,15 +1519,15 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>313828</v>
+        <v>101726</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MASSA TAPIOCA AMAFIL MATUTO 500GR SEMI P</t>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>3.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="62">
@@ -1537,15 +1537,15 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>130920</v>
+        <v>313828</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>MASSA TAPIOCA AMAFIL MATUTO 500GR SEMI P</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>3.89</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="63">
@@ -1555,15 +1555,15 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>106680</v>
+        <v>130920</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9.49</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="64">
@@ -1573,15 +1573,15 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>316048</v>
+        <v>106680</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>20.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="65">
@@ -1591,15 +1591,15 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>128920</v>
+        <v>316048</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="66">
@@ -1609,15 +1609,15 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>122984</v>
+        <v>128920</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>REFRI SPRITE PET 2L</t>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="67">
@@ -1627,15 +1627,15 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>161871</v>
+        <v>122984</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA TUCHAUA 2LT</t>
+          <t>REFRI SPRITE PET 2L</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>7.99</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="68">
@@ -1645,15 +1645,15 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>104406</v>
+        <v>161871</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>REFRIG GUARANA TUCHAUA 2LT</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="69">
@@ -1663,15 +1663,15 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>257710</v>
+        <v>104406</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SABAO BARRA YPE 5X180GR NEUTRO GLICERINA</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.79</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="70">
@@ -1681,15 +1681,15 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>228234</v>
+        <v>257710</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>SABAO BARRA YPE 5X180GR NEUTRO GLICERINA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15.89</v>
+        <v>12.79</v>
       </c>
     </row>
     <row r="71">
@@ -1699,15 +1699,15 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>100706</v>
+        <v>228234</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>5.69</v>
+        <v>15.89</v>
       </c>
     </row>
     <row r="72">
@@ -1717,15 +1717,15 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>259589</v>
+        <v>100706</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>STELLA ARTOIS ONE WAY 600ML</t>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.59</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="73">
@@ -1735,15 +1735,15 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>100876</v>
+        <v>259589</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+          <t>STELLA ARTOIS ONE WAY 600ML</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>14.99</v>
+        <v>10.59</v>
       </c>
     </row>
     <row r="74">
@@ -1753,15 +1753,15 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>106961</v>
+        <v>100876</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>3.69</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="75">
@@ -1771,11 +1771,11 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>106960</v>
+        <v>106961</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -1785,19 +1785,19 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 23/04/25</t>
+          <t>QUARTA - OFERTAS DO DIA 23/04/2025</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>152232</v>
+        <v>106960</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="77">
@@ -1807,15 +1807,15 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>105456</v>
+        <v>152232</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+          <t>BOVINO - BUCHO/HUMEM KG</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>26.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="78">
@@ -1825,15 +1825,15 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>105449</v>
+        <v>105456</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>33.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="79">
@@ -1843,15 +1843,15 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>105435</v>
+        <v>105449</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>36.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="80">
@@ -1861,15 +1861,15 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>173342</v>
+        <v>105435</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BOVINO - MOCOTO KG</t>
+          <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>8.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="81">
@@ -1879,15 +1879,15 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>105475</v>
+        <v>173342</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MUSCULO BOV KG</t>
+          <t>BOVINO - MOCOTO KG</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="82">
@@ -1897,15 +1897,15 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>105433</v>
+        <v>105475</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUINO - COSTELA SUINA KG</t>
+          <t>MUSCULO BOV KG</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="83">
@@ -1915,15 +1915,15 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>106052</v>
+        <v>105433</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="84">
@@ -1933,14 +1933,32 @@
         </is>
       </c>
       <c r="B84" t="n">
+        <v>106052</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 23/04/25</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
         <v>106034</v>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
-      <c r="D84" t="n">
+      <c r="D85" t="n">
         <v>13.99</v>
       </c>
     </row>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,198 +453,1458 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105460</v>
+        <v>255232</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105459</v>
+        <v>298239</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA MACA PEITO KG</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105451</v>
+        <v>100431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>34.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>181416</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105469</v>
+        <v>179914</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - PALETA KG</t>
+          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>23.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106008</v>
+        <v>234617</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INGREDIENTES P/ FEIJOADA KG</t>
+          <t>BISC CREAM CRACKER ESTRELA 350G</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.99</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106053</v>
+        <v>199869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105062</v>
+        <v>102085</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.99</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105433</v>
+        <v>101137</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUINO - COSTELA SUINA KG</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>23.99</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>106054</v>
+        <v>287369</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUINO - LOMBO FRESCO KG</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>19.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 23/04/25</t>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106052</v>
+        <v>170451</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D12" t="n">
+        <v>2.79</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>239446</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>184034</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>101066</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CREME LEITE ITALAC 200GR TP</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>123791</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>123792</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>123793</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>123795</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>123796</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>123797</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>DESINFETANTE START VOREL 2LT PINHO</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>256724</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>207588</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>207586</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>207584</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>207582</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>DETERG LIQ LAVABEM 500ML</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1.79</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>102287</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>100780</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>EXT TOMATE OLE 190GR CP</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>134629</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>268021</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>FARINHA DE MANDIOCA XINGU 1KG FINA AMARE</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>5.89</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>167686</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>140665</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>FEIJAO PRETO KICALDO TP1 1KG</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>100120</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>108434</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>174382</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>142446</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>LEITE ITALAC INTEGRAL 1LT</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>183340</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>LEITE UHT ITALAC SEMI DESNATADO 1L</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>125011</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>MAC CRISTAL PARAFUSO OVOS 500GR</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>131884</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>3.39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>101728</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>12.49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>169708</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>MASSA PRONTA PARA TAPIOCA DO ZE 500GR AL</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>130920</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>168910</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>MIST BOLO ITALAC 400GR CHOCOLATE</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>106680</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>OLEO SOJA SOYA  900ML</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>236651</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO NOBLE 12X20M</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>128920</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>104403</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>REFRIG FANTA UVA 2L</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>248450</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>100706</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>5.59</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>102237</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>106831</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>TEMP COMPLETO SABORELLE 930GR</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>106961</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>106960</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 28/04/25</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>102077</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>WHISKY OLD PARR 12 ANOS 1L</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>179.99</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>105842</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ASA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>14.49</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>227503</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>104602</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>COXA SADIA FRANGO PACOTE 1KG</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>105838</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>105840</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>COXINHA DA ASA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>14.59</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>306504</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>109597</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>FILE PEITO FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>108788</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>228289</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>FRANGO INTEIRO SADIA KG S/ MIUDOS TEMPER</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>185934</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>GALINHA LEVE NOROESTE CONG KG</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>228422</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>309350</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MASSA PASTEL JK 1KG</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>309331</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MASSA PASTEL JK 500GR DISCAO</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>309332</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MASSA PASTEL JK 500GR ROLO</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>108773</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>261357</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>130293</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>PIZZA SEARA 460GR FRANGO C/ CATUPIRY</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 28/04/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>108771</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>157014</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>BOVINO - ACEM C/ OSSO KG</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>105456</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>105468</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>105458</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>BOVINO - CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>105449</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO DURO KG</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>105435</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
         <v>13.99</v>
       </c>
     </row>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,25 +453,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255232</v>
+        <v>318330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -483,13 +483,13 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.59</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -501,13 +501,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.39</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,7 +525,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,249 +543,249 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>234617</v>
+        <v>123206</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BISC CREAM CRACKER ESTRELA 350G</t>
+          <t>AZEITONA LA VIOLETERA FATIADA 160GR SACH</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.39</v>
+        <v>7.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>199869</v>
+        <v>107799</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
+          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>7.39</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102085</v>
+        <v>261728</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>12.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101137</v>
+        <v>315854</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>BISCOITO RENATA 360GR MAIZENA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.49</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>287369</v>
+        <v>199869</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3.49</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>170451</v>
+        <v>102085</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>2.79</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>239446</v>
+        <v>101137</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3.19</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>184034</v>
+        <v>168712</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
+          <t>CERV ANTARCTICA 269ML C/ 15UND</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.99</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101066</v>
+        <v>170451</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CREME LEITE ITALAC 200GR TP</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>123791</v>
+        <v>247800</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>123792</v>
+        <v>239446</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>123793</v>
+        <v>267604</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>123795</v>
+        <v>242930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>123796</v>
+        <v>157496</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+          <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -795,249 +795,249 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>123797</v>
+        <v>101066</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT PINHO</t>
+          <t>CREME LEITE ITALAC 200GR TP</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>256724</v>
+        <v>110330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.79</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>207588</v>
+        <v>259583</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2L ERVA DOCE</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>207586</v>
+        <v>207624</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS FLORAL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>207584</v>
+        <v>207626</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS JASMIN</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>207582</v>
+        <v>207628</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DETERG LIQ LAVABEM 500ML</t>
+          <t>DESINFETANTE LAVABEM 2LTS LAVANDA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1.79</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>102287</v>
+        <v>207630</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>DESINFETANTE LAVABEM 2LTS LIMAO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.99</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>100780</v>
+        <v>119826</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>134629</v>
+        <v>111567</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5.49</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>268021</v>
+        <v>110352</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA XINGU 1KG FINA AMARE</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>100024</v>
+        <v>110353</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.89</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167686</v>
+        <v>252617</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>140665</v>
+        <v>106663</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>FEIJAO PRETO KICALDO TP1 1KG</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>8.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>100120</v>
+        <v>112163</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1047,465 +1047,465 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>108434</v>
+        <v>244424</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>174382</v>
+        <v>253877</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+          <t>ENERG BALY DRINK 2LT COCO E ACAI PET</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>38.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>142446</v>
+        <v>253878</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>LEITE ITALAC INTEGRAL 1LT</t>
+          <t>ENERG BALY ENERGY DRINK 2LT</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>183340</v>
+        <v>253880</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LEITE UHT ITALAC SEMI DESNATADO 1L</t>
+          <t>ENERG BALY MACA VERDE PET 2LT</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>125011</v>
+        <v>244426</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MAC CRISTAL PARAFUSO OVOS 500GR</t>
+          <t>ENERGETICO BALY 2L  FRUTAS TROPICAIS PET</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>4.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>131884</v>
+        <v>305261</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>ENERGETICO BALY 2L ABACAXI C/HORTELA DAS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>3.39</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>101728</v>
+        <v>320467</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+          <t>ENERGETICO BALY 2L CITRUS PET</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>169708</v>
+        <v>302661</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MASSA PRONTA PARA TAPIOCA DO ZE 500GR AL</t>
+          <t>ENERGETICO BALY 2L MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>5.69</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>130920</v>
+        <v>302660</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>ENERGETICO BALY 2L TANGERINA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>3.69</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>168910</v>
+        <v>102287</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MIST BOLO ITALAC 400GR CHOCOLATE</t>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>106680</v>
+        <v>100780</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>9.59</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>236651</v>
+        <v>273006</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO NOBLE 12X20M</t>
+          <t>FARINHA LACTEA NESTLE 160GR ORIGINAL</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>17.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>128920</v>
+        <v>107361</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>FARINHA TRIGO DONA BENTA 1KG C/FERMENTO</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>7.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>104403</v>
+        <v>100024</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>REFRIG FANTA UVA 2L</t>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>9.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>104406</v>
+        <v>100119</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.49</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>248450</v>
+        <v>108434</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
+          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>20.99</v>
+        <v>6.29</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>100706</v>
+        <v>101113</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>102237</v>
+        <v>106922</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>27.99</v>
+        <v>44.19</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>106831</v>
+        <v>108415</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR</t>
+          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.49</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>106961</v>
+        <v>303196</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>106960</v>
+        <v>101728</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>3.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>102077</v>
+        <v>169708</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WHISKY OLD PARR 12 ANOS 1L</t>
+          <t>MASSA PRONTA PARA TAPIOCA DO ZE 500GR AL</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>179.99</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>105842</v>
+        <v>130920</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ASA FRANGO KG</t>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>14.49</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>227503</v>
+        <v>106680</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>8.99</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>104602</v>
+        <v>236651</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>COXA SADIA FRANGO PACOTE 1KG</t>
+          <t>PAPEL HIGIENICO NOBLE 12X20M</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>15.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>105838</v>
+        <v>145874</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>COXA/SOBRECOXA FRANGO KG</t>
+          <t>POLVILHO AMAFIL MATUTO AZEDO 1KG</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -1515,87 +1515,87 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>105840</v>
+        <v>128920</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA FRANGO KG</t>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>14.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>306504</v>
+        <v>104404</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+          <t>REFRIG FANTA LARANJA 2L</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>5.99</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>109597</v>
+        <v>104403</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FILE PEITO FRANGO KG</t>
+          <t>REFRIG FANTA UVA 2L</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>20.99</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>108788</v>
+        <v>104424</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+          <t>REFRIG PEPSI COLA PET 2L</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>19.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>228289</v>
+        <v>104406</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FRANGO INTEIRO SADIA KG S/ MIUDOS TEMPER</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1605,307 +1605,577 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>185934</v>
+        <v>326954</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GALINHA LEVE NOROESTE CONG KG</t>
+          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>9.19</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>228422</v>
+        <v>228234</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>18.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>309350</v>
+        <v>100706</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MASSA PASTEL JK 1KG</t>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>20.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>309331</v>
+        <v>264452</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MASSA PASTEL JK 500GR DISCAO</t>
+          <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>309332</v>
+        <v>100876</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MASSA PASTEL JK 500GR ROLO</t>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>108773</v>
+        <v>106961</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>17.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>261357</v>
+        <v>106960</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>18.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>130293</v>
+        <v>102087</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PIZZA SEARA 460GR FRANGO C/ CATUPIRY</t>
+          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>21.99</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>108771</v>
+        <v>110373</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
+          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>17.99</v>
+        <v>89.98999999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - OFERTAS 30/04/2025</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>157014</v>
+        <v>102077</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM C/ OSSO KG</t>
+          <t>WHISKY OLD PARR 12 ANOS 1L</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.99</v>
+        <v>189.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>105456</v>
+        <v>104937</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>26.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>105468</v>
+        <v>105023</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>17.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>105458</v>
+        <v>105010</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>18.99</v>
+        <v>6.19</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>105449</v>
+        <v>105001</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>32.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>105435</v>
+        <v>104919</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>33.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>105062</v>
+        <v>104862</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>18.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 28/04/25</t>
+          <t>QUARTA - VERDURA 30/04/25</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>106034</v>
+        <v>104931</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.99</v>
+        <v>8.890000000000001</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>104855</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>LIMAO TAITI KG</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>104944</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MACA NACIONAL KG</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>11.69</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>104928</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MANGA PALMER KG</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>104947</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MELANCIA INTEIRA KG</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>104996</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MELAO AMARELO KG</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>7.39</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>104992</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>QUARTA - VERDURA 30/04/25</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>104961</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>TOMATE CARMEM KG</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>105470</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BOVINO - ACEM KG</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>24.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>239334</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>105458</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BOVINO - CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>105463</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BOVINO - CORACAO KG</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>105435</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>34.99</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>107260</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BOVINO - MACA DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>QUARTA - AÇOUGUE 30/04/25</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>105433</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SUINO - COSTELA SUINA KG</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>21.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D97"/>
+  <dimension ref="A1:D75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -471,7 +471,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -489,7 +489,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -507,7 +507,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,7 +525,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,7 +543,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -561,7 +561,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -579,7 +579,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -597,7 +597,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -615,7 +615,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -633,7 +633,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -651,7 +651,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -669,7 +669,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -687,7 +687,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -705,7 +705,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -723,7 +723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -741,7 +741,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -759,7 +759,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -777,7 +777,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -795,7 +795,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -813,7 +813,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -831,7 +831,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -849,7 +849,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -867,7 +867,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -885,7 +885,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -903,7 +903,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -921,7 +921,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -939,7 +939,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -957,7 +957,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -975,7 +975,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -993,7 +993,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -1011,7 +1011,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -1029,7 +1029,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -1047,7 +1047,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -1065,7 +1065,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -1083,7 +1083,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -1101,7 +1101,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -1119,7 +1119,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -1137,7 +1137,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -1155,7 +1155,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -1173,7 +1173,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -1191,7 +1191,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -1209,7 +1209,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -1227,7 +1227,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -1245,7 +1245,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -1263,7 +1263,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -1281,7 +1281,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -1299,7 +1299,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -1317,7 +1317,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -1335,7 +1335,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -1353,7 +1353,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -1371,7 +1371,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -1389,7 +1389,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -1407,7 +1407,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -1425,7 +1425,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -1443,7 +1443,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -1461,7 +1461,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B58" t="n">
@@ -1479,7 +1479,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B59" t="n">
@@ -1497,7 +1497,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B60" t="n">
@@ -1515,7 +1515,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B61" t="n">
@@ -1533,7 +1533,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -1551,7 +1551,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -1569,7 +1569,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -1587,7 +1587,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B65" t="n">
@@ -1605,7 +1605,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -1623,7 +1623,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -1641,7 +1641,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B68" t="n">
@@ -1659,7 +1659,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B69" t="n">
@@ -1677,7 +1677,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
@@ -1695,7 +1695,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
@@ -1713,7 +1713,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
@@ -1731,7 +1731,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B73" t="n">
@@ -1749,7 +1749,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B74" t="n">
@@ -1767,7 +1767,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30/04/2025</t>
+          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
         </is>
       </c>
       <c r="B75" t="n">
@@ -1780,402 +1780,6 @@
       </c>
       <c r="D75" t="n">
         <v>189.99</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>104937</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>ALHO A GRANEL KG</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>32.99</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>105023</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>BANANA PRATA KG</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>105010</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>BATATA MONALISA KG</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>6.19</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>105001</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>BETERRABA KG</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>104919</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>CEBOLA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>4.49</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>104862</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>CENOURA KG</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>4.99</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>104931</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>LARANJA KG</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>8.890000000000001</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>104855</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>LIMAO TAITI KG</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>4.39</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>104944</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>MACA NACIONAL KG</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>11.69</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>104928</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>MANGA PALMER KG</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>6.99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>104947</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>MELANCIA INTEIRA KG</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>1.99</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>104996</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>MELAO AMARELO KG</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>7.39</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>104992</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>REPOLHO VERDE KG</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>3.99</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>QUARTA - VERDURA 30/04/25</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>104961</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>TOMATE CARMEM KG</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>7.99</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>105470</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>BOVINO - ACEM KG</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>24.99</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>239334</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>28.99</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>105458</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>BOVINO - CHAMBARI KG</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>105463</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>BOVINO - CORACAO KG</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>12.99</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>105435</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>BOVINO - COXAO MOLE KG</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>34.99</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>107260</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>29.99</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>105062</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>QUARTA - AÇOUGUE 30/04/25</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>105433</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>SUINO - COSTELA SUINA KG</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>21.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D75"/>
+  <dimension ref="A1:D117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,61 +453,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>318330</v>
+        <v>298239</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>298239</v>
+        <v>100426</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>8.49</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100431</v>
+        <v>112174</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>ALCOOL START 1L 70INPM</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>7.49</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -525,7 +525,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -543,1243 +543,1999 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>123206</v>
+        <v>100037</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AZEITONA LA VIOLETERA FATIADA 160GR SACH</t>
+          <t>ARROZ PAINHO 5KG BRANCO TIPO 1 BRANCO TI</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>7.89</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>107799</v>
+        <v>225003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BEB RAIZES AMARGAS DE RACA 880ML</t>
+          <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>261728</v>
+        <v>199440</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+          <t>ARROZ SANTA FE 5 KG TP1</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>315854</v>
+        <v>113480</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BISCOITO RENATA 360GR MAIZENA</t>
+          <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.39</v>
+        <v>31.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>199869</v>
+        <v>250013</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA DE COCO ADORALLE 600G</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>102085</v>
+        <v>286197</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.49</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>101137</v>
+        <v>239682</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>BOMBOM GAROTO SORTIDO 250G</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>168712</v>
+        <v>102085</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA 269ML C/ 15UND</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3.09</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>170451</v>
+        <v>114037</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.89</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>247800</v>
+        <v>242311</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>CATCHUP ARISCO TRADICIONAL 370G</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.89</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>239446</v>
+        <v>249597</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 269ML LAGER LT C/ 12UNID</t>
+          <t>CERV HEINEKEN ZERO ALCOOL 330ML UNID</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.29</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>267604</v>
+        <v>298700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK UNID</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>5.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>242930</v>
+        <v>184034</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>CERVEJA HEINEKEN 250ML LN LAGER UNID</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>157496</v>
+        <v>107376</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN GARRAFA 600ML</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>11.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>101066</v>
+        <v>286362</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CREME LEITE ITALAC 200GR TP</t>
+          <t>CERVEJA SPATEN 600ML PURO MALTE LN</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2.79</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>110330</v>
+        <v>109002</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+          <t>CR DENTAL SORRISO DENTES BRANCO 180G DEN</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>259583</v>
+        <v>155079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>DESINFETANTE LAVABEM 2L ERVA DOCE</t>
+          <t>CREME DE LEITE LEITBOM TP 200G</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7.29</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>207624</v>
+        <v>112978</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>DESINFETANTE LAVABEM 2LTS FLORAL</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>7.29</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>207626</v>
+        <v>208281</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>DESINFETANTE LAVABEM 2LTS JASMIN</t>
+          <t>DES AERO MOOD MEN 150ML</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>7.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>207628</v>
+        <v>208304</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DESINFETANTE LAVABEM 2LTS LAVANDA</t>
+          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>7.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>207630</v>
+        <v>208280</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DESINFETANTE LAVABEM 2LTS LIMAO</t>
+          <t>DES AERO MOOD WOMEN 150ML</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>7.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>119826</v>
+        <v>123791</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>111567</v>
+        <v>123792</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>110352</v>
+        <v>123793</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>110353</v>
+        <v>123795</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>252617</v>
+        <v>123796</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>106663</v>
+        <v>123797</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+          <t>DESINFETANTE START VOREL 2LT PINHO</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.69</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>112163</v>
+        <v>312369</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.69</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>244424</v>
+        <v>312371</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
+          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>253877</v>
+        <v>312370</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ENERG BALY DRINK 2LT COCO E ACAI PET</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>253878</v>
+        <v>312366</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ENERG BALY ENERGY DRINK 2LT</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>253880</v>
+        <v>312367</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ENERG BALY MACA VERDE PET 2LT</t>
+          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>244426</v>
+        <v>298933</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L  FRUTAS TROPICAIS PET</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>305261</v>
+        <v>298932</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L ABACAXI C/HORTELA DAS</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>320467</v>
+        <v>298931</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L CITRUS PET</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>302661</v>
+        <v>298930</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L MORANGO E PESSEGO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>302660</v>
+        <v>298929</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 2L TANGERINA</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>102287</v>
+        <v>298928</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>100780</v>
+        <v>298927</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>273006</v>
+        <v>311881</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>FARINHA LACTEA NESTLE 160GR ORIGINAL</t>
+          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>107361</v>
+        <v>100391</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG C/FERMENTO</t>
+          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.49</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>100024</v>
+        <v>100394</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>5.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>100119</v>
+        <v>100392</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.89</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>108434</v>
+        <v>100403</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6.29</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>101113</v>
+        <v>100393</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LEITE PIRACANJUBA UHT 1L EDGE INTEGRAL</t>
+          <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>106922</v>
+        <v>100390</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>44.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>108415</v>
+        <v>312365</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MAC CRISTAL 500G SEMOLA PARAFUSO</t>
+          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>303196</v>
+        <v>312364</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
+          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.39</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>101728</v>
+        <v>244424</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+          <t>ENERG BALY 2L ENERGY DRINK MELANCIA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>169708</v>
+        <v>253877</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>MASSA PRONTA PARA TAPIOCA DO ZE 500GR AL</t>
+          <t>ENERG BALY DRINK 2LT COCO E ACAI PET</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>5.19</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>130920</v>
+        <v>253878</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>ENERG BALY ENERGY DRINK 2LT</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.89</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>106680</v>
+        <v>253880</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>ENERG BALY MACA VERDE PET 2LT</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>9.49</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>236651</v>
+        <v>102282</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO NOBLE 12X20M</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>18.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>145874</v>
+        <v>244426</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>POLVILHO AMAFIL MATUTO AZEDO 1KG</t>
+          <t>ENERGETICO BALY 2L  FRUTAS TROPICAIS PET</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>128920</v>
+        <v>305261</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>ENERGETICO BALY 2L ABACAXI C/HORTELA DAS</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>8.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>104404</v>
+        <v>320467</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>REFRIG FANTA LARANJA 2L</t>
+          <t>ENERGETICO BALY 2L CITRUS PET</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>9.789999999999999</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>104403</v>
+        <v>302661</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>REFRIG FANTA UVA 2L</t>
+          <t>ENERGETICO BALY 2L MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>9.789999999999999</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>104424</v>
+        <v>302660</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>REFRIG PEPSI COLA PET 2L</t>
+          <t>ENERGETICO BALY 2L TANGERINA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>7.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>104406</v>
+        <v>273714</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>326954</v>
+        <v>134629</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.39</v>
+        <v>5.19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>228234</v>
+        <v>163918</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>14.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>100706</v>
+        <v>140665</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>FEIJAO PRETO KICALDO TP1 1KG</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>5.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>264452</v>
+        <v>166152</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUCO PRONTO DAFRUTA 1L NECTAR UVA</t>
+          <t>FLOCAO MILHO SUPER FLOCAO CORINGA 500GR</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>5.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>100876</v>
+        <v>101085</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+          <t>LEITE CONDENSADO MOCOCA 395GR. TP</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>14.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>106961</v>
+        <v>142446</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL</t>
+          <t>LEITE ITALAC INTEGRAL 1LT</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>106960</v>
+        <v>307145</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.89</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>102087</v>
+        <v>290255</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
+          <t>MACARRAO CRISTAL 500GR SEMOLA ESPAGUETE</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>54.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>110373</v>
+        <v>303196</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>89.98999999999999</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 30 a 04/05/2025</t>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>102077</v>
+        <v>101726</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WHISKY OLD PARR 12 ANOS 1L</t>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>189.99</v>
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>134749</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>MILHO VERDE OLE 170GR LT</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>101130</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>MIST BOLO DONA BENTA 450GR CASEICHOCOLAT</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>167128</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>8.390000000000001</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>304108</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO LEBLON SOFT BLANC 12 ROL</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>318358</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>POLVILHO DONA DE 1KG AZEDO</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>104404</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>REFRIG FANTA LARANJA 2L</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>104410</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.69</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>261867</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>SABAO PO BRILHANTE 1,6KG 150GR GRATIS SA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>286199</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>261083</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>238146</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SABONETE FL YPE SV AGUA COCO ALEC 85G</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>236972</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE FLOR LAR/DAMASC 85G</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>236971</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE FRESIA E PESSEGO 85</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>236970</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR DE YPE ROSAS BRANCAS AVELA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>235599</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR YPE  GARDENIA ARGAN 85G</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>238147</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>SABONETE FLOR YPE FLOR BAUN AMENDOA 85G</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>1.49</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>100705</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>100693</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>286325</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>106831</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>TEMP COMPLETO SABORELLE 930GR</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>106960</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>VINAGRE CASTELO 750ML ALCOOL COLORIDO</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SEGUNDA- OFERTAS 05/05/2025</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>109729</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>WHISKY WHITE HORSE 1LT</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>99.98999999999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>105842</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>ASA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>14.89</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>227503</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>104602</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>COXA SADIA FRANGO PACOTE 1KG</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>105838</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.89</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>105840</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>COXINHA DA ASA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>14.89</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>306504</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>109597</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>FILE PEITO FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>108788</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>119927</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>FRANGO CONG AMERICANO KG</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>185934</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>GALINHA LEVE NOROESTE CONG KG</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>9.19</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>228422</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>309350</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>MASSA PASTEL JK 1KG</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>309331</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>MASSA PASTEL JK 500GR DISCAO</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>309332</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MASSA PASTEL JK 500GR ROLO</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>108773</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>116251</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MORTADELA  SADIA FRANGO KG</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>261357</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>130293</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PIZZA SEARA 460GR FRANGO C/ CATUPIRY</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SEGUNDA - COROCOCO 05/05/25</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>108771</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>17.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,433 +453,577 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>298239</v>
+        <v>230698</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>BE GIN TANQUERAI TEN 750 ML 750 ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>7.69</v>
+        <v>259.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>100038</v>
+        <v>286589</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>26.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>100031</v>
+        <v>287184</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.69</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>326645</v>
+        <v>286326</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
+          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - OFERTA ESPECIAL SEXTA</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>167128</v>
+        <v>287177</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.69</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105460</v>
+        <v>215568</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105461</v>
+        <v>157068</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+          <t>CERV BRAHMA DUPLO MALTE 350ML PAC C/12 U</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105451</v>
+        <v>265727</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>CERVEJA HEINEKEN 269ML LATA C/ 8UNID</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>36.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>105463</v>
+        <v>298123</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOVINO - CORACAO KG</t>
+          <t>CERVEJA HEINEKEN 350ML ZERO SLEEK UNID</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>12.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105471</v>
+        <v>107376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>105449</v>
+        <v>295198</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>CHOPP DE VINHO STEMPEL 600ML RED</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>36.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>106065</v>
+        <v>102282</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>BOVINO - FIGADO KG.</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.99</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>105838</v>
+        <v>273004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>COXA/SOBRECOXA FRANGO KG</t>
+          <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105840</v>
+        <v>273000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA FRANGO KG</t>
+          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>141831</v>
+        <v>273005</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>FILE DE PEIXE PANGA KG</t>
+          <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>44.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>203263</v>
+        <v>324170</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FILE DE TILAPIA KG</t>
+          <t>ENGOV AFTER 250ML PINK LEMONADE</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>49.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>109597</v>
+        <v>286271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>FILE PEITO FRANGO KG</t>
+          <t>REFRIGERANTE PEPSI 2L BLACK ZERO ACUCAR</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105853</v>
+        <v>139964</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>FRANGO CONG MARINGA KG</t>
+          <t>VINHO PERGOLA TINTO SUAVE 1LT</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10.89</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>305039</v>
+        <v>102087</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>VODKA SMIRNOFF 998ML TRIPLE DISTILLED</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.99</v>
+        <v>49.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>123758</v>
+        <v>110373</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LINGUICA FRIMESA TOSCANA MISTA KG</t>
+          <t>WHISKY BLACK &amp;WHITE 1L 8 ANOS</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22.99</v>
+        <v>79.98999999999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>189031</v>
+        <v>137381</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LINGUICA MISTA FRICO KG</t>
+          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.99</v>
+        <v>128.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105062</v>
+        <v>248750</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.99</v>
+        <v>54.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - BIRITÃO 10/05/25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>106054</v>
+        <v>102077</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUINO - LOMBO FRESCO KG</t>
+          <t>WHISKY OLD PARR 12 ANOS 1L</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.99</v>
+        <v>195.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OFERTA - AÇOUGUE E PAS 09/05/25</t>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>258810</v>
+        <v>105450</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUINO - PANCETA KG</t>
+          <t>BOVINO - ALCATRA KG</t>
         </is>
       </c>
       <c r="D25" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>105458</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BOVINO - CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
         <v>18.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>105451</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BOVINO - CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BOVINO - COSTELA KG</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>105474</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BOVINO - FRALDINHA KG</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>107260</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BOVINO - MACA DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>261519</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BOVINO - PICANHA FATIADA KG</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>305039</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 10/05/25</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="70">
   <si>
     <t>Promoção</t>
   </si>
@@ -28,13 +28,31 @@
     <t>Preço Promoção</t>
   </si>
   <si>
-    <t>SEGUNDA - OFERTAS 12/05/2025</t>
-  </si>
-  <si>
-    <t>SEGUNDA - COROCOCO 12/05/25</t>
-  </si>
-  <si>
-    <t>SEGUNDA - AÇOUGUE 12/05/25</t>
+    <t>TERÇA - AÇOUGUE 13/05/25</t>
+  </si>
+  <si>
+    <t>TERCA - OFERTAS 13/05/2025</t>
+  </si>
+  <si>
+    <t>TERÇA - PERECIVEIS 13/05/25</t>
+  </si>
+  <si>
+    <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+  </si>
+  <si>
+    <t>BOVINO - CARNE MOIDA KG</t>
+  </si>
+  <si>
+    <t>BOVINO - COSTELA KG</t>
+  </si>
+  <si>
+    <t>BOVINO - MACA DO PEITO KG</t>
+  </si>
+  <si>
+    <t>BOVINO - MUSCULO KG</t>
+  </si>
+  <si>
+    <t>LINGUICA BOVINA KG CASEIRA</t>
   </si>
   <si>
     <t>ACHOC PO TODDY 750G</t>
@@ -43,235 +61,169 @@
     <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
   </si>
   <si>
-    <t>AGUA SANITARIA YPE 1L CLORO ATIVO</t>
-  </si>
-  <si>
-    <t>ALCOOL START 1L 70INPM</t>
+    <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
   </si>
   <si>
     <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
   </si>
   <si>
-    <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
-  </si>
-  <si>
-    <t>ARROZ DONA VAVA 5KG TIPO 1</t>
-  </si>
-  <si>
-    <t>ARROZ RACHA PANELA 5 KG TP 1</t>
-  </si>
-  <si>
-    <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
-  </si>
-  <si>
-    <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
-  </si>
-  <si>
-    <t>AZEITE GALLO 500ML EXTRA VIRGEM</t>
+    <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+  </si>
+  <si>
+    <t>ARROZ TIO URBANO 5KG TP 1 BRANCO</t>
   </si>
   <si>
     <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
   </si>
   <si>
-    <t>BISCOITO RENATA 360GR COCO</t>
-  </si>
-  <si>
-    <t>BISCOITO ROSQUINHA 600GR SULLPER  COCO</t>
+    <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+  </si>
+  <si>
+    <t>BOMBOM GAROTO SORTIDO 250G</t>
   </si>
   <si>
     <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
   </si>
   <si>
-    <t>CAFE 3CORACOES EXTRAFORTE 250G</t>
-  </si>
-  <si>
-    <t>CERV ANTARCTICA SUBZERO 269ML UND</t>
-  </si>
-  <si>
-    <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN 330ML UND</t>
-  </si>
-  <si>
-    <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
-  </si>
-  <si>
-    <t>CREME DE LEITE LEITBOM TP 200G</t>
-  </si>
-  <si>
-    <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
-  </si>
-  <si>
-    <t>DESINFETANTE +FAMILIA 2LT PINHO</t>
-  </si>
-  <si>
-    <t>DETERG LIQ LAVABEM 500ML</t>
-  </si>
-  <si>
-    <t>EXT TOMATE OLE 260G CP</t>
-  </si>
-  <si>
-    <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
-  </si>
-  <si>
-    <t>FEIJAO DA CASA 1KG CARIOCA</t>
-  </si>
-  <si>
-    <t>FEIJAO PRETO KICALDO TP1 1KG</t>
-  </si>
-  <si>
-    <t>FLOCAO DE MILHO AMAFIL 500G</t>
-  </si>
-  <si>
-    <t>KETCHUP QUERO 400GR TRADICIONAL</t>
-  </si>
-  <si>
-    <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
-  </si>
-  <si>
-    <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
-  </si>
-  <si>
-    <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
-  </si>
-  <si>
-    <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
-  </si>
-  <si>
-    <t>MILHO VERDE SOFRUTA  LATA 170G</t>
-  </si>
-  <si>
-    <t>MIST BOLO ITALAC 400GR CHOCOLATE</t>
-  </si>
-  <si>
-    <t>MOLHO DE TOMATE SABORELLE 300GR TRADICIO</t>
-  </si>
-  <si>
-    <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+    <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+  </si>
+  <si>
+    <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+  </si>
+  <si>
+    <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+  </si>
+  <si>
+    <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 350ML SLEEK LT UNID</t>
+  </si>
+  <si>
+    <t>CORONA EXTRA N LONG NECK 330ML</t>
+  </si>
+  <si>
+    <t>CREME LEITE ITALAC 200GR TP</t>
+  </si>
+  <si>
+    <t>CUSCUZ DE MILHO SINHA 500GR</t>
+  </si>
+  <si>
+    <t>DESINFETANTE BAK YPE EUCALIPTO 2LTS</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML COCO</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML MACA</t>
+  </si>
+  <si>
+    <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
+  </si>
+  <si>
+    <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
+  </si>
+  <si>
+    <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+  </si>
+  <si>
+    <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+  </si>
+  <si>
+    <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
+  </si>
+  <si>
+    <t>FEIJAO KICALDO 1KG CARIOCA</t>
+  </si>
+  <si>
+    <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+  </si>
+  <si>
+    <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
+  </si>
+  <si>
+    <t>LEITE ITALAC INTEGRAL 1LT</t>
+  </si>
+  <si>
+    <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
+  </si>
+  <si>
+    <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
+  </si>
+  <si>
+    <t>MAIONESE HELLMANNS 500GR TRADICIONAL</t>
+  </si>
+  <si>
+    <t>MAIONESE QUERO SCHT 200GR</t>
+  </si>
+  <si>
+    <t>MILHO VERDE BONARE LATA 170G</t>
+  </si>
+  <si>
+    <t>OLEO SOJA SOYA  900ML</t>
   </si>
   <si>
     <t>PAPEL HIGIENICO NOBLE 12X20M</t>
   </si>
   <si>
-    <t>POLVILHO AMAFIL MATUTO AZEDO 1KG</t>
-  </si>
-  <si>
-    <t>REFRIG FANTA LARANJA 2L</t>
+    <t>REFRIG FANTA UVA 2L</t>
+  </si>
+  <si>
+    <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
   </si>
   <si>
     <t>REFRIGERANTE COCA COLA 2L</t>
   </si>
   <si>
-    <t>REFRIGERANTE PEPSI 2L BLACK ZERO ACUCAR</t>
-  </si>
-  <si>
-    <t>SABAO BARRA YPE 5X180GR NEUTRO GLICERINA</t>
-  </si>
-  <si>
-    <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
-  </si>
-  <si>
-    <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
-  </si>
-  <si>
-    <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
-  </si>
-  <si>
-    <t>SUCO UVA INTEGRAL TINTO AURORA 1,5L VD</t>
-  </si>
-  <si>
-    <t>TEMP COMPLETO SABORELLE 930GR</t>
-  </si>
-  <si>
-    <t>VINAGRE SABORELLE COMPOSTO BRANCO 750ML</t>
-  </si>
-  <si>
-    <t>WHISKY OLD PARR 12 ANOS 1L</t>
-  </si>
-  <si>
-    <t>ASA FRANGO KG</t>
-  </si>
-  <si>
-    <t>BATATA PALITO PRE-FRITA CONG. SADIA PT 4</t>
-  </si>
-  <si>
-    <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
-  </si>
-  <si>
-    <t>COXA SADIA FRANGO PACOTE 1KG</t>
-  </si>
-  <si>
-    <t>COXA/SOBRECOXA FRANGO KG</t>
-  </si>
-  <si>
-    <t>COXINHA DA ASA FRANGO KG</t>
-  </si>
-  <si>
-    <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
-  </si>
-  <si>
-    <t>FILE PEITO FRANGO KG</t>
-  </si>
-  <si>
-    <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+    <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
+  </si>
+  <si>
+    <t>SODA CAUSTICA SOL 1KG</t>
+  </si>
+  <si>
+    <t>STELLA ARTOIS ONE WAY 600ML</t>
+  </si>
+  <si>
+    <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+  </si>
+  <si>
+    <t>WHISKY WHITE HORSE 1LT</t>
+  </si>
+  <si>
+    <t>ASA 1JTA COXINHA DA  ASA DRUMETTE SADIA</t>
+  </si>
+  <si>
+    <t>FILE DE COXA E SOBRE COXA SEARA 1KG BAND</t>
+  </si>
+  <si>
+    <t>FILEZINHO DE PEITO SEARA 1KG SASSAMI BDJ</t>
   </si>
   <si>
     <t>FRANGO CONG AMERICANO KG</t>
   </si>
   <si>
-    <t>GALINHA LEVE NOROESTE CONG KG</t>
-  </si>
-  <si>
-    <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
-  </si>
-  <si>
-    <t>MASSA PASTEL JK 1KG</t>
-  </si>
-  <si>
-    <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
-  </si>
-  <si>
-    <t>MORTADELA  SADIA FRANGO KG</t>
-  </si>
-  <si>
-    <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
-  </si>
-  <si>
-    <t>PIZZA SEARA 460GR FRANGO C/ CATUPIRY</t>
-  </si>
-  <si>
-    <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
-  </si>
-  <si>
-    <t>BOVINA - BISTECA PALETA KG</t>
-  </si>
-  <si>
-    <t>BOVINO - ACEM KG</t>
-  </si>
-  <si>
-    <t>BOVINO - BISTECA MACA PEITO KG</t>
-  </si>
-  <si>
-    <t>BOVINO - CAPA DO CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>BOVINO - CHAMBARI KG</t>
-  </si>
-  <si>
-    <t>BOVINO - COXAO DURO KG</t>
-  </si>
-  <si>
-    <t>BOVINO - COXAO MOLE KG</t>
-  </si>
-  <si>
-    <t>SUINO - BISTECA PERNIL FRESCA KG</t>
-  </si>
-  <si>
-    <t>SUINO - SUAN FRESCA KG</t>
+    <t>LINGUICA MISTA FRICO KG</t>
+  </si>
+  <si>
+    <t>PAO DE QJO TRAD  ESPECIAL VITORIA  300G</t>
+  </si>
+  <si>
+    <t>PAO DE QUEIJO PREMIUM BRASIL 300GR TRADI</t>
   </si>
 </sst>
 </file>
@@ -629,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -651,13 +603,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>255232</v>
+        <v>105456</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
       </c>
       <c r="D2">
-        <v>18.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -665,13 +617,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>298239</v>
+        <v>105468</v>
       </c>
       <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3">
-        <v>8.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -679,13 +631,13 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>107878</v>
+        <v>105471</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
       </c>
       <c r="D4">
-        <v>4.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -693,13 +645,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>112174</v>
+        <v>107260</v>
       </c>
       <c r="C5" t="s">
         <v>10</v>
       </c>
       <c r="D5">
-        <v>11.39</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -707,13 +659,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>181416</v>
+        <v>105475</v>
       </c>
       <c r="C6" t="s">
         <v>11</v>
       </c>
       <c r="D6">
-        <v>11.69</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -721,1091 +673,811 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>179914</v>
+        <v>305039</v>
       </c>
       <c r="C7" t="s">
         <v>12</v>
       </c>
       <c r="D7">
-        <v>11.69</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B8">
-        <v>269680</v>
+        <v>255232</v>
       </c>
       <c r="C8" t="s">
         <v>13</v>
       </c>
       <c r="D8">
-        <v>23.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>199439</v>
+        <v>298239</v>
       </c>
       <c r="C9" t="s">
         <v>14</v>
       </c>
       <c r="D9">
-        <v>25.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>100031</v>
+        <v>100426</v>
       </c>
       <c r="C10" t="s">
         <v>15</v>
       </c>
       <c r="D10">
-        <v>27.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>326645</v>
+        <v>181416</v>
       </c>
       <c r="C11" t="s">
         <v>16</v>
       </c>
       <c r="D11">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>132657</v>
+        <v>136523</v>
       </c>
       <c r="C12" t="s">
         <v>17</v>
       </c>
       <c r="D12">
-        <v>66.98999999999999</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13">
-        <v>250013</v>
+        <v>113480</v>
       </c>
       <c r="C13" t="s">
         <v>18</v>
       </c>
       <c r="D13">
-        <v>5.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B14">
-        <v>315855</v>
+        <v>250013</v>
       </c>
       <c r="C14" t="s">
         <v>19</v>
       </c>
       <c r="D14">
-        <v>6.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B15">
-        <v>286746</v>
+        <v>286197</v>
       </c>
       <c r="C15" t="s">
         <v>20</v>
       </c>
       <c r="D15">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="16" spans="1:4">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16">
-        <v>102085</v>
+        <v>239682</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16">
-        <v>12.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="17" spans="1:4">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B17">
-        <v>115855</v>
+        <v>102085</v>
       </c>
       <c r="C17" t="s">
         <v>22</v>
       </c>
       <c r="D17">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="18" spans="1:4">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B18">
-        <v>239441</v>
+        <v>101137</v>
       </c>
       <c r="C18" t="s">
         <v>23</v>
       </c>
       <c r="D18">
-        <v>2.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="19" spans="1:4">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B19">
-        <v>298701</v>
+        <v>287369</v>
       </c>
       <c r="C19" t="s">
         <v>24</v>
       </c>
       <c r="D19">
-        <v>4.19</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="20" spans="1:4">
       <c r="A20" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B20">
-        <v>313599</v>
+        <v>170451</v>
       </c>
       <c r="C20" t="s">
         <v>25</v>
       </c>
       <c r="D20">
-        <v>3.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="21" spans="1:4">
       <c r="A21" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B21">
-        <v>242930</v>
+        <v>247800</v>
       </c>
       <c r="C21" t="s">
         <v>26</v>
       </c>
       <c r="D21">
-        <v>6.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B22">
-        <v>107376</v>
+        <v>267604</v>
       </c>
       <c r="C22" t="s">
         <v>27</v>
       </c>
       <c r="D22">
-        <v>2.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B23">
-        <v>155079</v>
+        <v>303282</v>
       </c>
       <c r="C23" t="s">
         <v>28</v>
       </c>
       <c r="D23">
-        <v>3.69</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B24">
-        <v>110330</v>
+        <v>220499</v>
       </c>
       <c r="C24" t="s">
         <v>29</v>
       </c>
       <c r="D24">
-        <v>2.19</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B25">
-        <v>100315</v>
+        <v>101066</v>
       </c>
       <c r="C25" t="s">
         <v>30</v>
       </c>
       <c r="D25">
-        <v>6.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B26">
-        <v>256724</v>
+        <v>112978</v>
       </c>
       <c r="C26" t="s">
         <v>31</v>
       </c>
       <c r="D26">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B27">
-        <v>207588</v>
+        <v>148554</v>
       </c>
       <c r="C27" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D27">
-        <v>1.79</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B28">
-        <v>207586</v>
+        <v>100423</v>
       </c>
       <c r="C28" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D28">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="29" spans="1:4">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B29">
-        <v>207584</v>
+        <v>100419</v>
       </c>
       <c r="C29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D29">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="30" spans="1:4">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B30">
-        <v>207582</v>
+        <v>220037</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D30">
-        <v>1.79</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="31" spans="1:4">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B31">
-        <v>118822</v>
+        <v>204461</v>
       </c>
       <c r="C31" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D31">
-        <v>4.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="32" spans="1:4">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B32">
-        <v>100024</v>
+        <v>100420</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D32">
-        <v>5.99</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="33" spans="1:4">
       <c r="A33" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B33">
-        <v>116507</v>
+        <v>100417</v>
       </c>
       <c r="C33" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D33">
-        <v>5.39</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="34" spans="1:4">
       <c r="A34" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B34">
-        <v>140665</v>
+        <v>106661</v>
       </c>
       <c r="C34" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D34">
-        <v>8.69</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="35" spans="1:4">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B35">
-        <v>255841</v>
+        <v>273004</v>
       </c>
       <c r="C35" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D35">
-        <v>2.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="36" spans="1:4">
       <c r="A36" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B36">
-        <v>100785</v>
+        <v>102287</v>
       </c>
       <c r="C36" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D36">
-        <v>7.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37" spans="1:4">
       <c r="A37" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B37">
-        <v>220451</v>
+        <v>273714</v>
       </c>
       <c r="C37" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D37">
-        <v>6.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="38" spans="1:4">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B38">
-        <v>174382</v>
+        <v>134629</v>
       </c>
       <c r="C38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D38">
-        <v>36.99</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="39" spans="1:4">
       <c r="A39" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B39">
-        <v>131884</v>
+        <v>163918</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D39">
-        <v>3.39</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="40" spans="1:4">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B40">
-        <v>101726</v>
+        <v>100119</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D40">
-        <v>8.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41" spans="1:4">
       <c r="A41" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B41">
-        <v>234316</v>
+        <v>108434</v>
       </c>
       <c r="C41" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D41">
-        <v>3.89</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="42" spans="1:4">
       <c r="A42" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B42">
-        <v>168910</v>
+        <v>142446</v>
       </c>
       <c r="C42" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="D42">
-        <v>4.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="43" spans="1:4">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B43">
-        <v>287073</v>
+        <v>307145</v>
       </c>
       <c r="C43" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="D43">
-        <v>2.19</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="44" spans="1:4">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B44">
-        <v>167128</v>
+        <v>100642</v>
       </c>
       <c r="C44" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D44">
-        <v>8.789999999999999</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="45" spans="1:4">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B45">
-        <v>236651</v>
+        <v>101728</v>
       </c>
       <c r="C45" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="D45">
-        <v>18.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="46" spans="1:4">
       <c r="A46" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B46">
-        <v>145874</v>
+        <v>115724</v>
       </c>
       <c r="C46" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="D46">
-        <v>10.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="47" spans="1:4">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B47">
-        <v>104404</v>
+        <v>234626</v>
       </c>
       <c r="C47" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D47">
-        <v>9.99</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="48" spans="1:4">
       <c r="A48" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B48">
-        <v>104406</v>
+        <v>106680</v>
       </c>
       <c r="C48" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D48">
-        <v>10.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B49">
-        <v>286271</v>
+        <v>236651</v>
       </c>
       <c r="C49" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D49">
-        <v>7.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B50">
-        <v>257710</v>
+        <v>104403</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D50">
-        <v>11.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="51" spans="1:4">
       <c r="A51" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B51">
-        <v>286199</v>
+        <v>104410</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D51">
-        <v>9.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="52" spans="1:4">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B52">
-        <v>261083</v>
+        <v>104406</v>
       </c>
       <c r="C52" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D52">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="53" spans="1:4">
       <c r="A53" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B53">
-        <v>100706</v>
+        <v>248450</v>
       </c>
       <c r="C53" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D53">
-        <v>5.69</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="54" spans="1:4">
       <c r="A54" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B54">
-        <v>102237</v>
+        <v>100373</v>
       </c>
       <c r="C54" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="D54">
-        <v>28.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="55" spans="1:4">
       <c r="A55" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B55">
-        <v>106831</v>
+        <v>259589</v>
       </c>
       <c r="C55" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="D55">
-        <v>11.69</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="56" spans="1:4">
       <c r="A56" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B56">
-        <v>137423</v>
+        <v>100876</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="D56">
-        <v>4.29</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="57" spans="1:4">
       <c r="A57" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B57">
-        <v>102077</v>
+        <v>109729</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D57">
-        <v>195.99</v>
+        <v>110.99</v>
       </c>
     </row>
     <row r="58" spans="1:4">
       <c r="A58" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B58">
-        <v>105842</v>
+        <v>108785</v>
       </c>
       <c r="C58" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D58">
-        <v>13.69</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="59" spans="1:4">
       <c r="A59" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B59">
-        <v>227503</v>
+        <v>299338</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="D59">
-        <v>8.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="60" spans="1:4">
       <c r="A60" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B60">
-        <v>119923</v>
+        <v>291440</v>
       </c>
       <c r="C60" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D60">
-        <v>32.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="61" spans="1:4">
       <c r="A61" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B61">
-        <v>104602</v>
+        <v>119927</v>
       </c>
       <c r="C61" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D61">
-        <v>15.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="62" spans="1:4">
       <c r="A62" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B62">
-        <v>105838</v>
+        <v>189031</v>
       </c>
       <c r="C62" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D62">
-        <v>11.69</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="63" spans="1:4">
       <c r="A63" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B63">
-        <v>105840</v>
+        <v>228484</v>
       </c>
       <c r="C63" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="D63">
-        <v>14.39</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="64" spans="1:4">
       <c r="A64" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B64">
-        <v>306504</v>
+        <v>320181</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D64">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>5</v>
-      </c>
-      <c r="B65">
-        <v>109597</v>
-      </c>
-      <c r="C65" t="s">
-        <v>66</v>
-      </c>
-      <c r="D65">
-        <v>19.89</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
-        <v>5</v>
-      </c>
-      <c r="B66">
-        <v>108788</v>
-      </c>
-      <c r="C66" t="s">
-        <v>67</v>
-      </c>
-      <c r="D66">
-        <v>19.99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>5</v>
-      </c>
-      <c r="B67">
-        <v>119927</v>
-      </c>
-      <c r="C67" t="s">
-        <v>68</v>
-      </c>
-      <c r="D67">
-        <v>10.89</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>5</v>
-      </c>
-      <c r="B68">
-        <v>185934</v>
-      </c>
-      <c r="C68" t="s">
-        <v>69</v>
-      </c>
-      <c r="D68">
-        <v>9.19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>5</v>
-      </c>
-      <c r="B69">
-        <v>228422</v>
-      </c>
-      <c r="C69" t="s">
-        <v>70</v>
-      </c>
-      <c r="D69">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>5</v>
-      </c>
-      <c r="B70">
-        <v>309350</v>
-      </c>
-      <c r="C70" t="s">
-        <v>71</v>
-      </c>
-      <c r="D70">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>5</v>
-      </c>
-      <c r="B71">
-        <v>108773</v>
-      </c>
-      <c r="C71" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
-        <v>5</v>
-      </c>
-      <c r="B72">
-        <v>116251</v>
-      </c>
-      <c r="C72" t="s">
-        <v>73</v>
-      </c>
-      <c r="D72">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
-        <v>5</v>
-      </c>
-      <c r="B73">
-        <v>261357</v>
-      </c>
-      <c r="C73" t="s">
-        <v>74</v>
-      </c>
-      <c r="D73">
         <v>16.99</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>5</v>
-      </c>
-      <c r="B74">
-        <v>130293</v>
-      </c>
-      <c r="C74" t="s">
-        <v>75</v>
-      </c>
-      <c r="D74">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>5</v>
-      </c>
-      <c r="B75">
-        <v>108771</v>
-      </c>
-      <c r="C75" t="s">
-        <v>76</v>
-      </c>
-      <c r="D75">
-        <v>17.99</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>6</v>
-      </c>
-      <c r="B76">
-        <v>105460</v>
-      </c>
-      <c r="C76" t="s">
-        <v>77</v>
-      </c>
-      <c r="D76">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>6</v>
-      </c>
-      <c r="B77">
-        <v>105470</v>
-      </c>
-      <c r="C77" t="s">
-        <v>78</v>
-      </c>
-      <c r="D77">
-        <v>23.99</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>6</v>
-      </c>
-      <c r="B78">
-        <v>105459</v>
-      </c>
-      <c r="C78" t="s">
-        <v>79</v>
-      </c>
-      <c r="D78">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>6</v>
-      </c>
-      <c r="B79">
-        <v>239334</v>
-      </c>
-      <c r="C79" t="s">
-        <v>80</v>
-      </c>
-      <c r="D79">
-        <v>27.99</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>6</v>
-      </c>
-      <c r="B80">
-        <v>105458</v>
-      </c>
-      <c r="C80" t="s">
-        <v>81</v>
-      </c>
-      <c r="D80">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>6</v>
-      </c>
-      <c r="B81">
-        <v>105449</v>
-      </c>
-      <c r="C81" t="s">
-        <v>82</v>
-      </c>
-      <c r="D81">
-        <v>33.99</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>6</v>
-      </c>
-      <c r="B82">
-        <v>105435</v>
-      </c>
-      <c r="C82" t="s">
-        <v>83</v>
-      </c>
-      <c r="D82">
-        <v>36.99</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>6</v>
-      </c>
-      <c r="B83">
-        <v>105062</v>
-      </c>
-      <c r="C83" t="s">
-        <v>84</v>
-      </c>
-      <c r="D83">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>6</v>
-      </c>
-      <c r="B84">
-        <v>106034</v>
-      </c>
-      <c r="C84" t="s">
-        <v>85</v>
-      </c>
-      <c r="D84">
-        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,127 +453,847 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105460</v>
+        <v>311307</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>BOLINHO DE TILAPIA 270GR CONG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105456</v>
+        <v>303488</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE DE SOL KG SEGUNDA</t>
+          <t>CAMARAO CINZA COSTAMAR 1KG DESC 36/40</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.99</v>
+        <v>118.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105458</v>
+        <v>323495</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>CAMARAO COSTA SUL 300GR 45/80 COZIDO DES</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.99</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105449</v>
+        <v>262170</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>COSTELA DE TILAPIA KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105487</v>
+        <v>164651</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - CUPIM KG</t>
+          <t>FILE DE MERLUZA CONG COSTA SUL 500G</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>40.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>305039</v>
+        <v>141831</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>FILE DE PEIXE PANGA KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 16/05/25</t>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106053</v>
+        <v>203263</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+          <t>FILE DE TILAPIA KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>19.99</v>
+        <v>49.99</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>320788</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>HAMBURGUER COSTA SUL 90GR  DE SALMAO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>323489</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>284245</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>260606</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>STEAK EMPANADO COSTA SUL 100GR DE PEIXE</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>284246</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>105461</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>31.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>BOVINO - COSTELA KG</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>105435</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>105474</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>BOVINO - FRALDINHA KG</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>107260</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BOVINO - MACA DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>146785</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LING PERDIGAO CARNE SUINA KG</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>305039</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>189031</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LINGUICA MISTA FRICO KG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>167154</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>LINGUICA SUINA FRICO FINA APIMENTADA KG</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>26.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 17/05/25</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>102242</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AGUARD VELHO BARREIRO 910ML</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>236674</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>236672</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU ABORIGENE 750ML</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>236671</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU CAJAZINHA 750ML</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>236673</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>286589</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>287184</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>286326</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>287177</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>215568</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CACHACA BANANAZINHA 900ML</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>174010</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CACHACA SELETA 600ML</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>171895</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CERV ANTARTICA ORIGINAL 300ML</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>170451</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>313599</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>267604</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>303283</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>273004</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>273000</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>273005</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>206930</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>GIN TANQUERAY LONDON 750ML</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>102036</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>VINHO GALIOTTO 1LT TINTO SUAVE</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>137381</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 17/05/2025</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>248750</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>55.99</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SABADO - PREÇO BALA 17/05/25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>100038</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SABADO - PREÇO BALA 17/05/25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>100031</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>27.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,847 +453,1585 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>311307</v>
+        <v>105842</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOLINHO DE TILAPIA 270GR CONG</t>
+          <t>ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.99</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>303488</v>
+        <v>105838</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAMARAO CINZA COSTAMAR 1KG DESC 36/40</t>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>118.99</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>323495</v>
+        <v>105840</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CAMARAO COSTA SUL 300GR 45/80 COZIDO DES</t>
+          <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.99</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>262170</v>
+        <v>109597</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>COSTELA DE TILAPIA KG</t>
+          <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.99</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>164651</v>
+        <v>105853</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FILE DE MERLUZA CONG COSTA SUL 500G</t>
+          <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.99</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>141831</v>
+        <v>228422</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FILE DE PEIXE PANGA KG</t>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>39.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>203263</v>
+        <v>193650</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FILE DE TILAPIA KG</t>
+          <t>BATATAS PRE-FRITAS CONG BOUA  400GR</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>49.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>320788</v>
+        <v>194792</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HAMBURGUER COSTA SUL 90GR  DE SALMAO</t>
+          <t>BATATAS PRE-FRITAS CONG BOUA 2KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.69</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>323489</v>
+        <v>119923</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
+          <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>25.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>284245</v>
+        <v>104602</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
+          <t>COXA SADIA FRANGO PACOTE 1KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>260606</v>
+        <v>306504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>STEAK EMPANADO COSTA SUL 100GR DE PEIXE</t>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>4.39</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - FRUTOS DO MAR 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>284246</v>
+        <v>108788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>105461</v>
+        <v>309350</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+          <t>MASSA PASTEL JK 1KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>105471</v>
+        <v>108773</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>105435</v>
+        <v>261357</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>36.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>105474</v>
+        <v>108771</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>107260</v>
+        <v>170464</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>29.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>146785</v>
+        <v>138538</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LING PERDIGAO CARNE SUINA KG</t>
+          <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>28.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - COROCOCO 19/05/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>305039</v>
+        <v>127328</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>189031</v>
+        <v>100431</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LINGUICA MISTA FRICO KG</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>167154</v>
+        <v>116139</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>LINGUICA SUINA FRICO FINA APIMENTADA KG</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>26.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>106034</v>
+        <v>107395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>102242</v>
+        <v>100038</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AGUARD VELHO BARREIRO 910ML</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>236674</v>
+        <v>325990</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
+          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>44.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>236672</v>
+        <v>100020</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BEB FIU FIU ABORIGENE 750ML</t>
+          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>236671</v>
+        <v>273799</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BEB FIU FIU CAJAZINHA 750ML</t>
+          <t>ARROZ DELLARROZ BRANCO 5KG POLIDO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>236673</v>
+        <v>111378</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
+          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>286589</v>
+        <v>261728</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>287184</v>
+        <v>286197</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>286326</v>
+        <v>102085</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.99</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>287177</v>
+        <v>101137</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>215568</v>
+        <v>287369</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>39.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>174010</v>
+        <v>170451</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CACHACA SELETA 600ML</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>171895</v>
+        <v>242930</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CERV ANTARTICA ORIGINAL 300ML</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.59</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>170451</v>
+        <v>303283</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>313599</v>
+        <v>101063</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>3.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>267604</v>
+        <v>123791</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>303283</v>
+        <v>123792</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>273004</v>
+        <v>123793</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
+          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>273000</v>
+        <v>123795</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
+          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>273005</v>
+        <v>123796</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
+          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>206930</v>
+        <v>123797</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GIN TANQUERAY LONDON 750ML</t>
+          <t>DESINFETANTE START VOREL 2LT PINHO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>149.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>102036</v>
+        <v>119826</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VINHO GALIOTTO 1LT TINTO SUAVE</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>25.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>137381</v>
+        <v>111567</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>129.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 17/05/2025</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>248750</v>
+        <v>110352</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>55.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>100038</v>
+        <v>110353</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>28.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SABADO - PREÇO BALA 17/05/25</t>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>100031</v>
+        <v>252617</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>27.99</v>
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>106663</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>113911</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>112163</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>113914</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>102282</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ENERG RED BULL 250ML TRAD</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>100780</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>EXT TOMATE OLE 190GR CP</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>134629</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>167687</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>FEIJAO CARIOCA JOAOZINHO PREMIUM 1KG</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>111571</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>100120</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>100789</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400GR PICANTE</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>100785</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>220451</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>174382</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>170363</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>156422</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>100642</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>274807</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>MACARRAO RICOSA ESPAGUETE 400GR COMUM</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>101726</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>234316</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>MILHO VERDE SOFRUTA  LATA 170G</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>101130</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MIST BOLO DONA BENTA 450GR CASEICHOCOLAT</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>287073</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>MOLHO DE TOMATE SABORELLE 300GR TRADICIO</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>167128</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>128920</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>122984</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>REFRI SPRITE PET 2L</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>257710</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>261980</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>228234</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>100706</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>221089</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>SARDINHA COQUEIRO OLEO 125G</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>106831</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>TEMP COMPLETO SABORELLE 930GR</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 19/05/25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>137423</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>VINAGRE SABORELLE COMPOSTO BRANCO 750ML</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>105470</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BOVINO - ACEM KG</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>152232</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BOVINO - BUCHO/HUMEM KG</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>105468</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>105458</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>BOVINO - CHAMBARI KG</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>105449</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO DURO KG</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>105435</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO MOLE KG</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>106053</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>18.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="97">
   <si>
     <t>Promoção</t>
   </si>
@@ -28,163 +28,283 @@
     <t>Preço Promoção</t>
   </si>
   <si>
-    <t>SABADO - FRUTOS DO MAR 17/05/25</t>
-  </si>
-  <si>
-    <t>SABADO - AÇOUGUE 17/05/25</t>
-  </si>
-  <si>
-    <t>SABADO - BIRITAO 17/05/2025</t>
-  </si>
-  <si>
-    <t>SABADO - PREÇO BALA 17/05/25</t>
-  </si>
-  <si>
-    <t>BOLINHO DE TILAPIA 270GR CONG</t>
-  </si>
-  <si>
-    <t>CAMARAO CINZA COSTAMAR 1KG DESC 36/40</t>
-  </si>
-  <si>
-    <t>CAMARAO COSTA SUL 300GR 45/80 COZIDO DES</t>
-  </si>
-  <si>
-    <t>COSTELA DE TILAPIA KG</t>
-  </si>
-  <si>
-    <t>FILE DE MERLUZA CONG COSTA SUL 500G</t>
-  </si>
-  <si>
-    <t>FILE DE PEIXE PANGA KG</t>
-  </si>
-  <si>
-    <t>FILE DE TILAPIA KG</t>
-  </si>
-  <si>
-    <t>HAMBURGUER COSTA SUL 90GR  DE SALMAO</t>
-  </si>
-  <si>
-    <t>MEXILHAO COSTA SUL 300GR MARISCO DESCONC</t>
-  </si>
-  <si>
-    <t>PESCADO PEIXITOS COSTA SUL 300GR</t>
-  </si>
-  <si>
-    <t>STEAK EMPANADO COSTA SUL 100GR DE PEIXE</t>
-  </si>
-  <si>
-    <t>TIRINHAS DE TILAP?A COSTA SUL 300GR EMPA</t>
-  </si>
-  <si>
-    <t>BOVINO - ALCATRA KG</t>
-  </si>
-  <si>
-    <t>BOVINO - BISTECA CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>BOVINO - CONTRA FILE KG</t>
-  </si>
-  <si>
-    <t>BOVINO - COSTELA KG</t>
+    <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+  </si>
+  <si>
+    <t>SEGUNDA - COROCOCO 19/05/25</t>
+  </si>
+  <si>
+    <t>SEGUNDA - OFERTAS 19/05/25</t>
+  </si>
+  <si>
+    <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+  </si>
+  <si>
+    <t>ASA FRANGO KG</t>
+  </si>
+  <si>
+    <t>COXA/SOBRECOXA FRANGO KG</t>
+  </si>
+  <si>
+    <t>COXINHA DA ASA FRANGO KG</t>
+  </si>
+  <si>
+    <t>FILE PEITO FRANGO KG</t>
+  </si>
+  <si>
+    <t>FRANGO CONG MARINGA KG</t>
+  </si>
+  <si>
+    <t>GALINHA LEVE NOROESTE CONG KG</t>
+  </si>
+  <si>
+    <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+  </si>
+  <si>
+    <t>BATATAS PRE-FRITAS CONG BOUA  400GR</t>
+  </si>
+  <si>
+    <t>BATATAS PRE-FRITAS CONG BOUA 2KG</t>
+  </si>
+  <si>
+    <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
+  </si>
+  <si>
+    <t>COXA SADIA FRANGO PACOTE 1KG</t>
+  </si>
+  <si>
+    <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+  </si>
+  <si>
+    <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+  </si>
+  <si>
+    <t>MASSA PASTEL JK 1KG</t>
+  </si>
+  <si>
+    <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+  </si>
+  <si>
+    <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
+  </si>
+  <si>
+    <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
+  </si>
+  <si>
+    <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
+  </si>
+  <si>
+    <t>TEKITOS SEARA FRANGO 300G</t>
+  </si>
+  <si>
+    <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
+  </si>
+  <si>
+    <t>AGUA SANIT QBOA 2L MULTI USO</t>
+  </si>
+  <si>
+    <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+  </si>
+  <si>
+    <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+  </si>
+  <si>
+    <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+  </si>
+  <si>
+    <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
+  </si>
+  <si>
+    <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
+  </si>
+  <si>
+    <t>ARROZ DELLARROZ BRANCO 5KG POLIDO</t>
+  </si>
+  <si>
+    <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+  </si>
+  <si>
+    <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+  </si>
+  <si>
+    <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+  </si>
+  <si>
+    <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+  </si>
+  <si>
+    <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+  </si>
+  <si>
+    <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+  </si>
+  <si>
+    <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 330ML UND</t>
+  </si>
+  <si>
+    <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+  </si>
+  <si>
+    <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+  </si>
+  <si>
+    <t>DESINFETANTE START VOREL 2LT PINHO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+  </si>
+  <si>
+    <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+  </si>
+  <si>
+    <t>ENERG RED BULL 250ML TRAD</t>
+  </si>
+  <si>
+    <t>EXT TOMATE OLE 190GR CP</t>
+  </si>
+  <si>
+    <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
+  </si>
+  <si>
+    <t>FEIJAO CARIOCA JOAOZINHO PREMIUM 1KG</t>
+  </si>
+  <si>
+    <t>FLOCAO ARROZ BONOARROZ 500GR</t>
+  </si>
+  <si>
+    <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+  </si>
+  <si>
+    <t>KETCHUP QUERO 400GR PICANTE</t>
+  </si>
+  <si>
+    <t>KETCHUP QUERO 400GR TRADICIONAL</t>
+  </si>
+  <si>
+    <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
+  </si>
+  <si>
+    <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+  </si>
+  <si>
+    <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+  </si>
+  <si>
+    <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+  </si>
+  <si>
+    <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
+  </si>
+  <si>
+    <t>MACARRAO RICOSA ESPAGUETE 400GR COMUM</t>
+  </si>
+  <si>
+    <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+  </si>
+  <si>
+    <t>MILHO VERDE SOFRUTA  LATA 170G</t>
+  </si>
+  <si>
+    <t>MIST BOLO DONA BENTA 450GR CASEICHOCOLAT</t>
+  </si>
+  <si>
+    <t>MOLHO DE TOMATE SABORELLE 300GR TRADICIO</t>
+  </si>
+  <si>
+    <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+  </si>
+  <si>
+    <t>POLVILHO MATUTO 1KG DOCE</t>
+  </si>
+  <si>
+    <t>REFRI SPRITE PET 2L</t>
+  </si>
+  <si>
+    <t>REFRIGERANTE COCA COLA 2L</t>
+  </si>
+  <si>
+    <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
+  </si>
+  <si>
+    <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+  </si>
+  <si>
+    <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+  </si>
+  <si>
+    <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+  </si>
+  <si>
+    <t>SARDINHA COQUEIRO OLEO 125G</t>
+  </si>
+  <si>
+    <t>TEMP COMPLETO SABORELLE 930GR</t>
+  </si>
+  <si>
+    <t>VINAGRE SABORELLE COMPOSTO BRANCO 750ML</t>
+  </si>
+  <si>
+    <t>BOVINO - ACEM KG</t>
+  </si>
+  <si>
+    <t>BOVINO - BUCHO/HUMEM KG</t>
+  </si>
+  <si>
+    <t>BOVINO - CARNE MOIDA KG</t>
+  </si>
+  <si>
+    <t>BOVINO - CHAMBARI KG</t>
+  </si>
+  <si>
+    <t>BOVINO - COXAO DURO KG</t>
   </si>
   <si>
     <t>BOVINO - COXAO MOLE KG</t>
   </si>
   <si>
-    <t>BOVINO - FRALDINHA KG</t>
-  </si>
-  <si>
-    <t>BOVINO - MACA DO PEITO KG</t>
-  </si>
-  <si>
-    <t>LING PERDIGAO CARNE SUINA KG</t>
-  </si>
-  <si>
-    <t>LINGUICA BOVINA KG CASEIRA</t>
-  </si>
-  <si>
-    <t>LINGUICA MISTA FRICO KG</t>
-  </si>
-  <si>
-    <t>LINGUICA SUINA FRICO FINA APIMENTADA KG</t>
-  </si>
-  <si>
-    <t>SUINO - SUAN FRESCA KG</t>
-  </si>
-  <si>
-    <t>AGUARD VELHO BARREIRO 910ML</t>
-  </si>
-  <si>
-    <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
-  </si>
-  <si>
-    <t>BEB FIU FIU ABORIGENE 750ML</t>
-  </si>
-  <si>
-    <t>BEB FIU FIU CAJAZINHA 750ML</t>
-  </si>
-  <si>
-    <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
-  </si>
-  <si>
-    <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
-  </si>
-  <si>
-    <t>CACHACA BANANAZINHA 900ML</t>
-  </si>
-  <si>
-    <t>CACHACA SELETA 600ML</t>
-  </si>
-  <si>
-    <t>CERV ANTARTICA ORIGINAL 300ML</t>
-  </si>
-  <si>
-    <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
-  </si>
-  <si>
-    <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
-  </si>
-  <si>
-    <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
-  </si>
-  <si>
-    <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
-  </si>
-  <si>
-    <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
-  </si>
-  <si>
-    <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
-  </si>
-  <si>
-    <t>GIN TANQUERAY LONDON 750ML</t>
-  </si>
-  <si>
-    <t>VINHO GALIOTTO 1LT TINTO SUAVE</t>
-  </si>
-  <si>
-    <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
-  </si>
-  <si>
-    <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
-  </si>
-  <si>
-    <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
-  </si>
-  <si>
-    <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
+    <t>SUINO - BISTECA CARRE FRESCA KG</t>
+  </si>
+  <si>
+    <t>SUINO - BISTECA PERNIL FRESCA KG</t>
   </si>
 </sst>
 </file>
@@ -542,7 +662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
@@ -564,13 +684,13 @@
         <v>4</v>
       </c>
       <c r="B2">
-        <v>311307</v>
+        <v>105842</v>
       </c>
       <c r="C2" t="s">
         <v>8</v>
       </c>
       <c r="D2">
-        <v>15.99</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -578,13 +698,13 @@
         <v>4</v>
       </c>
       <c r="B3">
-        <v>303488</v>
+        <v>105838</v>
       </c>
       <c r="C3" t="s">
         <v>9</v>
       </c>
       <c r="D3">
-        <v>118.99</v>
+        <v>11.89</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -592,13 +712,13 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>323495</v>
+        <v>105840</v>
       </c>
       <c r="C4" t="s">
         <v>10</v>
       </c>
       <c r="D4">
-        <v>36.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -606,13 +726,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>262170</v>
+        <v>109597</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
       </c>
       <c r="D5">
-        <v>30.99</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -620,13 +740,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>164651</v>
+        <v>105853</v>
       </c>
       <c r="C6" t="s">
         <v>12</v>
       </c>
       <c r="D6">
-        <v>27.99</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -634,13 +754,13 @@
         <v>4</v>
       </c>
       <c r="B7">
-        <v>141831</v>
+        <v>185934</v>
       </c>
       <c r="C7" t="s">
         <v>13</v>
       </c>
       <c r="D7">
-        <v>39.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -648,83 +768,83 @@
         <v>4</v>
       </c>
       <c r="B8">
-        <v>203263</v>
+        <v>228422</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8">
-        <v>49.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B9">
-        <v>320788</v>
+        <v>193650</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9">
-        <v>7.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10">
-        <v>323489</v>
+        <v>194792</v>
       </c>
       <c r="C10" t="s">
         <v>16</v>
       </c>
       <c r="D10">
-        <v>25.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B11">
-        <v>284245</v>
+        <v>119923</v>
       </c>
       <c r="C11" t="s">
         <v>17</v>
       </c>
       <c r="D11">
-        <v>10.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B12">
-        <v>260606</v>
+        <v>104602</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12">
-        <v>4.39</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B13">
-        <v>284246</v>
+        <v>306504</v>
       </c>
       <c r="C13" t="s">
         <v>19</v>
       </c>
       <c r="D13">
-        <v>10.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -732,13 +852,13 @@
         <v>5</v>
       </c>
       <c r="B14">
-        <v>105450</v>
+        <v>108788</v>
       </c>
       <c r="C14" t="s">
         <v>20</v>
       </c>
       <c r="D14">
-        <v>36.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -746,13 +866,13 @@
         <v>5</v>
       </c>
       <c r="B15">
-        <v>105461</v>
+        <v>309350</v>
       </c>
       <c r="C15" t="s">
         <v>21</v>
       </c>
       <c r="D15">
-        <v>31.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -760,13 +880,13 @@
         <v>5</v>
       </c>
       <c r="B16">
-        <v>105451</v>
+        <v>108773</v>
       </c>
       <c r="C16" t="s">
         <v>22</v>
       </c>
       <c r="D16">
-        <v>36.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -774,13 +894,13 @@
         <v>5</v>
       </c>
       <c r="B17">
-        <v>105471</v>
+        <v>261357</v>
       </c>
       <c r="C17" t="s">
         <v>23</v>
       </c>
       <c r="D17">
-        <v>18.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -788,13 +908,13 @@
         <v>5</v>
       </c>
       <c r="B18">
-        <v>105435</v>
+        <v>108771</v>
       </c>
       <c r="C18" t="s">
         <v>24</v>
       </c>
       <c r="D18">
-        <v>36.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -802,13 +922,13 @@
         <v>5</v>
       </c>
       <c r="B19">
-        <v>105474</v>
+        <v>170464</v>
       </c>
       <c r="C19" t="s">
         <v>25</v>
       </c>
       <c r="D19">
-        <v>30.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -816,13 +936,13 @@
         <v>5</v>
       </c>
       <c r="B20">
-        <v>107260</v>
+        <v>138538</v>
       </c>
       <c r="C20" t="s">
         <v>26</v>
       </c>
       <c r="D20">
-        <v>29.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -830,69 +950,69 @@
         <v>5</v>
       </c>
       <c r="B21">
-        <v>146785</v>
+        <v>127328</v>
       </c>
       <c r="C21" t="s">
         <v>27</v>
       </c>
       <c r="D21">
-        <v>28.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="22" spans="1:4">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B22">
-        <v>305039</v>
+        <v>100431</v>
       </c>
       <c r="C22" t="s">
         <v>28</v>
       </c>
       <c r="D22">
-        <v>15.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="23" spans="1:4">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B23">
-        <v>189031</v>
+        <v>116139</v>
       </c>
       <c r="C23" t="s">
         <v>29</v>
       </c>
       <c r="D23">
-        <v>18.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>167154</v>
+        <v>107395</v>
       </c>
       <c r="C24" t="s">
         <v>30</v>
       </c>
       <c r="D24">
-        <v>26.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B25">
-        <v>106034</v>
+        <v>100038</v>
       </c>
       <c r="C25" t="s">
         <v>31</v>
       </c>
       <c r="D25">
-        <v>13.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -900,13 +1020,13 @@
         <v>6</v>
       </c>
       <c r="B26">
-        <v>102242</v>
+        <v>325990</v>
       </c>
       <c r="C26" t="s">
         <v>32</v>
       </c>
       <c r="D26">
-        <v>16.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -914,13 +1034,13 @@
         <v>6</v>
       </c>
       <c r="B27">
-        <v>236674</v>
+        <v>100020</v>
       </c>
       <c r="C27" t="s">
         <v>33</v>
       </c>
       <c r="D27">
-        <v>44.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -928,13 +1048,13 @@
         <v>6</v>
       </c>
       <c r="B28">
-        <v>236672</v>
+        <v>273799</v>
       </c>
       <c r="C28" t="s">
         <v>34</v>
       </c>
       <c r="D28">
-        <v>44.99</v>
+        <v>22.99</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -942,13 +1062,13 @@
         <v>6</v>
       </c>
       <c r="B29">
-        <v>236671</v>
+        <v>111378</v>
       </c>
       <c r="C29" t="s">
         <v>35</v>
       </c>
       <c r="D29">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -956,13 +1076,13 @@
         <v>6</v>
       </c>
       <c r="B30">
-        <v>236673</v>
+        <v>261728</v>
       </c>
       <c r="C30" t="s">
         <v>36</v>
       </c>
       <c r="D30">
-        <v>44.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -970,13 +1090,13 @@
         <v>6</v>
       </c>
       <c r="B31">
-        <v>286589</v>
+        <v>286197</v>
       </c>
       <c r="C31" t="s">
         <v>37</v>
       </c>
       <c r="D31">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -984,13 +1104,13 @@
         <v>6</v>
       </c>
       <c r="B32">
-        <v>287184</v>
+        <v>102085</v>
       </c>
       <c r="C32" t="s">
         <v>38</v>
       </c>
       <c r="D32">
-        <v>9.99</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -998,13 +1118,13 @@
         <v>6</v>
       </c>
       <c r="B33">
-        <v>286326</v>
+        <v>101137</v>
       </c>
       <c r="C33" t="s">
         <v>39</v>
       </c>
       <c r="D33">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -1012,13 +1132,13 @@
         <v>6</v>
       </c>
       <c r="B34">
-        <v>287177</v>
+        <v>287369</v>
       </c>
       <c r="C34" t="s">
         <v>40</v>
       </c>
       <c r="D34">
-        <v>9.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -1026,13 +1146,13 @@
         <v>6</v>
       </c>
       <c r="B35">
-        <v>215568</v>
+        <v>170451</v>
       </c>
       <c r="C35" t="s">
         <v>41</v>
       </c>
       <c r="D35">
-        <v>39.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -1040,13 +1160,13 @@
         <v>6</v>
       </c>
       <c r="B36">
-        <v>174010</v>
+        <v>242930</v>
       </c>
       <c r="C36" t="s">
         <v>42</v>
       </c>
       <c r="D36">
-        <v>45.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -1054,13 +1174,13 @@
         <v>6</v>
       </c>
       <c r="B37">
-        <v>171895</v>
+        <v>303283</v>
       </c>
       <c r="C37" t="s">
         <v>43</v>
       </c>
       <c r="D37">
-        <v>4.59</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -1068,13 +1188,13 @@
         <v>6</v>
       </c>
       <c r="B38">
-        <v>170451</v>
+        <v>101063</v>
       </c>
       <c r="C38" t="s">
         <v>44</v>
       </c>
       <c r="D38">
-        <v>2.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -1082,13 +1202,13 @@
         <v>6</v>
       </c>
       <c r="B39">
-        <v>313599</v>
+        <v>123791</v>
       </c>
       <c r="C39" t="s">
         <v>45</v>
       </c>
       <c r="D39">
-        <v>3.69</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -1096,13 +1216,13 @@
         <v>6</v>
       </c>
       <c r="B40">
-        <v>267604</v>
+        <v>123792</v>
       </c>
       <c r="C40" t="s">
         <v>46</v>
       </c>
       <c r="D40">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -1110,13 +1230,13 @@
         <v>6</v>
       </c>
       <c r="B41">
-        <v>303283</v>
+        <v>123793</v>
       </c>
       <c r="C41" t="s">
         <v>47</v>
       </c>
       <c r="D41">
-        <v>5.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -1124,13 +1244,13 @@
         <v>6</v>
       </c>
       <c r="B42">
-        <v>273004</v>
+        <v>123795</v>
       </c>
       <c r="C42" t="s">
         <v>48</v>
       </c>
       <c r="D42">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -1138,13 +1258,13 @@
         <v>6</v>
       </c>
       <c r="B43">
-        <v>273000</v>
+        <v>123796</v>
       </c>
       <c r="C43" t="s">
         <v>49</v>
       </c>
       <c r="D43">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -1152,13 +1272,13 @@
         <v>6</v>
       </c>
       <c r="B44">
-        <v>273005</v>
+        <v>123797</v>
       </c>
       <c r="C44" t="s">
         <v>50</v>
       </c>
       <c r="D44">
-        <v>8.49</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -1166,13 +1286,13 @@
         <v>6</v>
       </c>
       <c r="B45">
-        <v>206930</v>
+        <v>119826</v>
       </c>
       <c r="C45" t="s">
         <v>51</v>
       </c>
       <c r="D45">
-        <v>149.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -1180,13 +1300,13 @@
         <v>6</v>
       </c>
       <c r="B46">
-        <v>102036</v>
+        <v>111567</v>
       </c>
       <c r="C46" t="s">
         <v>52</v>
       </c>
       <c r="D46">
-        <v>25.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -1194,13 +1314,13 @@
         <v>6</v>
       </c>
       <c r="B47">
-        <v>137381</v>
+        <v>110352</v>
       </c>
       <c r="C47" t="s">
         <v>53</v>
       </c>
       <c r="D47">
-        <v>129.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1208,41 +1328,601 @@
         <v>6</v>
       </c>
       <c r="B48">
-        <v>248750</v>
+        <v>110353</v>
       </c>
       <c r="C48" t="s">
         <v>54</v>
       </c>
       <c r="D48">
-        <v>55.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="49" spans="1:4">
       <c r="A49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B49">
-        <v>100038</v>
+        <v>252617</v>
       </c>
       <c r="C49" t="s">
         <v>55</v>
       </c>
       <c r="D49">
-        <v>28.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="50" spans="1:4">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B50">
-        <v>100031</v>
+        <v>106663</v>
       </c>
       <c r="C50" t="s">
         <v>56</v>
       </c>
       <c r="D50">
-        <v>27.99</v>
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4">
+      <c r="A51" t="s">
+        <v>6</v>
+      </c>
+      <c r="B51">
+        <v>113911</v>
+      </c>
+      <c r="C51" t="s">
+        <v>57</v>
+      </c>
+      <c r="D51">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4">
+      <c r="A52" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52">
+        <v>112163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>58</v>
+      </c>
+      <c r="D52">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4">
+      <c r="A53" t="s">
+        <v>6</v>
+      </c>
+      <c r="B53">
+        <v>113914</v>
+      </c>
+      <c r="C53" t="s">
+        <v>59</v>
+      </c>
+      <c r="D53">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4">
+      <c r="A54" t="s">
+        <v>6</v>
+      </c>
+      <c r="B54">
+        <v>102282</v>
+      </c>
+      <c r="C54" t="s">
+        <v>60</v>
+      </c>
+      <c r="D54">
+        <v>8.69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4">
+      <c r="A55" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55">
+        <v>100780</v>
+      </c>
+      <c r="C55" t="s">
+        <v>61</v>
+      </c>
+      <c r="D55">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4">
+      <c r="A56" t="s">
+        <v>6</v>
+      </c>
+      <c r="B56">
+        <v>134629</v>
+      </c>
+      <c r="C56" t="s">
+        <v>62</v>
+      </c>
+      <c r="D56">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4">
+      <c r="A57" t="s">
+        <v>6</v>
+      </c>
+      <c r="B57">
+        <v>167687</v>
+      </c>
+      <c r="C57" t="s">
+        <v>63</v>
+      </c>
+      <c r="D57">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4">
+      <c r="A58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58">
+        <v>111571</v>
+      </c>
+      <c r="C58" t="s">
+        <v>64</v>
+      </c>
+      <c r="D58">
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4">
+      <c r="A59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59">
+        <v>100120</v>
+      </c>
+      <c r="C59" t="s">
+        <v>65</v>
+      </c>
+      <c r="D59">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4">
+      <c r="A60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60">
+        <v>100789</v>
+      </c>
+      <c r="C60" t="s">
+        <v>66</v>
+      </c>
+      <c r="D60">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4">
+      <c r="A61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61">
+        <v>100785</v>
+      </c>
+      <c r="C61" t="s">
+        <v>67</v>
+      </c>
+      <c r="D61">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4">
+      <c r="A62" t="s">
+        <v>6</v>
+      </c>
+      <c r="B62">
+        <v>220451</v>
+      </c>
+      <c r="C62" t="s">
+        <v>68</v>
+      </c>
+      <c r="D62">
+        <v>6.59</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4">
+      <c r="A63" t="s">
+        <v>6</v>
+      </c>
+      <c r="B63">
+        <v>174382</v>
+      </c>
+      <c r="C63" t="s">
+        <v>69</v>
+      </c>
+      <c r="D63">
+        <v>37.99</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4">
+      <c r="A64" t="s">
+        <v>6</v>
+      </c>
+      <c r="B64">
+        <v>170363</v>
+      </c>
+      <c r="C64" t="s">
+        <v>70</v>
+      </c>
+      <c r="D64">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4">
+      <c r="A65" t="s">
+        <v>6</v>
+      </c>
+      <c r="B65">
+        <v>156422</v>
+      </c>
+      <c r="C65" t="s">
+        <v>71</v>
+      </c>
+      <c r="D65">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4">
+      <c r="A66" t="s">
+        <v>6</v>
+      </c>
+      <c r="B66">
+        <v>100642</v>
+      </c>
+      <c r="C66" t="s">
+        <v>72</v>
+      </c>
+      <c r="D66">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4">
+      <c r="A67" t="s">
+        <v>6</v>
+      </c>
+      <c r="B67">
+        <v>274807</v>
+      </c>
+      <c r="C67" t="s">
+        <v>73</v>
+      </c>
+      <c r="D67">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4">
+      <c r="A68" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68">
+        <v>101726</v>
+      </c>
+      <c r="C68" t="s">
+        <v>74</v>
+      </c>
+      <c r="D68">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4">
+      <c r="A69" t="s">
+        <v>6</v>
+      </c>
+      <c r="B69">
+        <v>234316</v>
+      </c>
+      <c r="C69" t="s">
+        <v>75</v>
+      </c>
+      <c r="D69">
+        <v>3.79</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4">
+      <c r="A70" t="s">
+        <v>6</v>
+      </c>
+      <c r="B70">
+        <v>101130</v>
+      </c>
+      <c r="C70" t="s">
+        <v>76</v>
+      </c>
+      <c r="D70">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4">
+      <c r="A71" t="s">
+        <v>6</v>
+      </c>
+      <c r="B71">
+        <v>287073</v>
+      </c>
+      <c r="C71" t="s">
+        <v>77</v>
+      </c>
+      <c r="D71">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4">
+      <c r="A72" t="s">
+        <v>6</v>
+      </c>
+      <c r="B72">
+        <v>167128</v>
+      </c>
+      <c r="C72" t="s">
+        <v>78</v>
+      </c>
+      <c r="D72">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4">
+      <c r="A73" t="s">
+        <v>6</v>
+      </c>
+      <c r="B73">
+        <v>128920</v>
+      </c>
+      <c r="C73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D73">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4">
+      <c r="A74" t="s">
+        <v>6</v>
+      </c>
+      <c r="B74">
+        <v>122984</v>
+      </c>
+      <c r="C74" t="s">
+        <v>80</v>
+      </c>
+      <c r="D74">
+        <v>9.59</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4">
+      <c r="A75" t="s">
+        <v>6</v>
+      </c>
+      <c r="B75">
+        <v>104406</v>
+      </c>
+      <c r="C75" t="s">
+        <v>81</v>
+      </c>
+      <c r="D75">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4">
+      <c r="A76" t="s">
+        <v>6</v>
+      </c>
+      <c r="B76">
+        <v>257710</v>
+      </c>
+      <c r="C76" t="s">
+        <v>82</v>
+      </c>
+      <c r="D76">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4">
+      <c r="A77" t="s">
+        <v>6</v>
+      </c>
+      <c r="B77">
+        <v>261980</v>
+      </c>
+      <c r="C77" t="s">
+        <v>83</v>
+      </c>
+      <c r="D77">
+        <v>20.99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4">
+      <c r="A78" t="s">
+        <v>6</v>
+      </c>
+      <c r="B78">
+        <v>228234</v>
+      </c>
+      <c r="C78" t="s">
+        <v>84</v>
+      </c>
+      <c r="D78">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4">
+      <c r="A79" t="s">
+        <v>6</v>
+      </c>
+      <c r="B79">
+        <v>100706</v>
+      </c>
+      <c r="C79" t="s">
+        <v>85</v>
+      </c>
+      <c r="D79">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4">
+      <c r="A80" t="s">
+        <v>6</v>
+      </c>
+      <c r="B80">
+        <v>221089</v>
+      </c>
+      <c r="C80" t="s">
+        <v>86</v>
+      </c>
+      <c r="D80">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4">
+      <c r="A81" t="s">
+        <v>6</v>
+      </c>
+      <c r="B81">
+        <v>106831</v>
+      </c>
+      <c r="C81" t="s">
+        <v>87</v>
+      </c>
+      <c r="D81">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4">
+      <c r="A82" t="s">
+        <v>6</v>
+      </c>
+      <c r="B82">
+        <v>137423</v>
+      </c>
+      <c r="C82" t="s">
+        <v>88</v>
+      </c>
+      <c r="D82">
+        <v>4.39</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4">
+      <c r="A83" t="s">
+        <v>7</v>
+      </c>
+      <c r="B83">
+        <v>105470</v>
+      </c>
+      <c r="C83" t="s">
+        <v>89</v>
+      </c>
+      <c r="D83">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4">
+      <c r="A84" t="s">
+        <v>7</v>
+      </c>
+      <c r="B84">
+        <v>152232</v>
+      </c>
+      <c r="C84" t="s">
+        <v>90</v>
+      </c>
+      <c r="D84">
+        <v>14.99</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4">
+      <c r="A85" t="s">
+        <v>7</v>
+      </c>
+      <c r="B85">
+        <v>105468</v>
+      </c>
+      <c r="C85" t="s">
+        <v>91</v>
+      </c>
+      <c r="D85">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4">
+      <c r="A86" t="s">
+        <v>7</v>
+      </c>
+      <c r="B86">
+        <v>105458</v>
+      </c>
+      <c r="C86" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4">
+      <c r="A87" t="s">
+        <v>7</v>
+      </c>
+      <c r="B87">
+        <v>105449</v>
+      </c>
+      <c r="C87" t="s">
+        <v>93</v>
+      </c>
+      <c r="D87">
+        <v>32.99</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4">
+      <c r="A88" t="s">
+        <v>7</v>
+      </c>
+      <c r="B88">
+        <v>105435</v>
+      </c>
+      <c r="C88" t="s">
+        <v>94</v>
+      </c>
+      <c r="D88">
+        <v>36.99</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4">
+      <c r="A89" t="s">
+        <v>7</v>
+      </c>
+      <c r="B89">
+        <v>106053</v>
+      </c>
+      <c r="C89" t="s">
+        <v>95</v>
+      </c>
+      <c r="D89">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4">
+      <c r="A90" t="s">
+        <v>7</v>
+      </c>
+      <c r="B90">
+        <v>105062</v>
+      </c>
+      <c r="C90" t="s">
+        <v>96</v>
+      </c>
+      <c r="D90">
+        <v>18.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D89"/>
+  <dimension ref="A1:D88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,1023 +453,1023 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105842</v>
+        <v>157014</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ASA FRANGO KG</t>
+          <t>BOVINO - ACEM C/ OSSO KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.69</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105838</v>
+        <v>105461</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>COXA/SOBRECOXA FRANGO KG</t>
+          <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>11.69</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105840</v>
+        <v>105468</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA FRANGO KG</t>
+          <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.39</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>109597</v>
+        <v>105451</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FILE PEITO FRANGO KG</t>
+          <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>19.89</v>
+        <v>36.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105853</v>
+        <v>105449</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FRANGO CONG MARINGA KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.89</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25 PESAVEIS</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>228422</v>
+        <v>173342</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
+          <t>BOVINO - MOCOTO KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>193650</v>
+        <v>105452</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BATATAS PRE-FRITAS CONG BOUA  400GR</t>
+          <t>BOVINO - PATINHO KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>8.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>194792</v>
+        <v>105853</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BATATAS PRE-FRITAS CONG BOUA 2KG</t>
+          <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>40.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>119923</v>
+        <v>305039</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>32.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104602</v>
+        <v>105765</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>COXA SADIA FRANGO PACOTE 1KG</t>
+          <t>MORTADELA MISTA PERDIGAO KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>306504</v>
+        <v>239921</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
+          <t>OVOS BRANCOS CARTELA 30 UNID</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.49</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>108788</v>
+        <v>106054</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - AÇOUGUE 20/05/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>309350</v>
+        <v>106034</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MASSA PASTEL JK 1KG</t>
+          <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>20.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>108773</v>
+        <v>255232</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
+          <t>ACHOC PO TODDY 750G</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>17.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>261357</v>
+        <v>100426</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
+          <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>108771</v>
+        <v>181416</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
+          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>170464</v>
+        <v>136523</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
+          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.19</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>138538</v>
+        <v>225003</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TEKITOS SEARA FRANGO 300G</t>
+          <t>ARROZ RAMPINELLI 5KG TIPO1</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>8.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEGUNDA - COROCOCO 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>127328</v>
+        <v>100031</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
+          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8.49</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>100431</v>
+        <v>326645</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7.19</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>116139</v>
+        <v>250013</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7.49</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>107395</v>
+        <v>286746</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>BISCOITO ROSQUINHA 600GR SULLPER  COCO</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7.49</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>100038</v>
+        <v>239682</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>BOMBOM GAROTO SORTIDO 250G</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>325990</v>
+        <v>102085</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.99</v>
+        <v>12.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100020</v>
+        <v>101137</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>25.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>273799</v>
+        <v>287369</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ARROZ DELLARROZ BRANCO 5KG POLIDO</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>22.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>111378</v>
+        <v>170451</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>261728</v>
+        <v>247800</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.19</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>286197</v>
+        <v>267604</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102085</v>
+        <v>303282</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT UNID</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.39</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>101137</v>
+        <v>220499</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>CORONA EXTRA N LONG NECK 330ML</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>287369</v>
+        <v>106866</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>CREME DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>170451</v>
+        <v>101066</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CREME LEITE ITALAC 200GR TP</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.79</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>242930</v>
+        <v>112978</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>303283</v>
+        <v>208281</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+          <t>DES AERO MOOD MEN 150ML</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>101063</v>
+        <v>208304</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>123791</v>
+        <v>208280</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+          <t>DES AERO MOOD WOMEN 150ML</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>123792</v>
+        <v>142863</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+          <t>DESINFETANTE BAK YPE 2L LAVANDA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>123793</v>
+        <v>134193</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+          <t>DESINFETANTE BAK YPE FLORAL 2LTS</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>123795</v>
+        <v>254080</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+          <t>DESINFETANTE BAK YPE LAVANDA L2LP1,8L</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>123796</v>
+        <v>312369</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>123797</v>
+        <v>312371</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT PINHO</t>
+          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>119826</v>
+        <v>312370</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>111567</v>
+        <v>312366</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>110352</v>
+        <v>312367</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>110353</v>
+        <v>312368</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>252617</v>
+        <v>298933</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>106663</v>
+        <v>298932</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>113911</v>
+        <v>298931</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>112163</v>
+        <v>298930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>113914</v>
+        <v>298929</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>2.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>102282</v>
+        <v>298928</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.69</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>100780</v>
+        <v>298927</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>3.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>134629</v>
+        <v>311881</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FAR TRIGO MIRELLA 1KG S/FERMENTO PAPEL</t>
+          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>5.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>167687</v>
+        <v>100391</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA JOAOZINHO PREMIUM 1KG</t>
+          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>6.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>111571</v>
+        <v>100394</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.09</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>100120</v>
+        <v>100392</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO BONOMILHO 500G</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1479,559 +1479,541 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>100789</v>
+        <v>100402</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>KETCHUP QUERO 400GR PICANTE</t>
+          <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>100785</v>
+        <v>100403</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>KETCHUP QUERO 400GR TRADICIONAL</t>
+          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>220451</v>
+        <v>100393</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>LEITE COND. TRIANGULO 395G TP SEMI</t>
+          <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>6.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>174382</v>
+        <v>100390</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>37.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>170363</v>
+        <v>312365</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>7.29</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>156422</v>
+        <v>312364</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>100642</v>
+        <v>102287</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MAC PAULISTA ESPAGUETE 500GR SEMOLA</t>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.79</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>274807</v>
+        <v>273714</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MACARRAO RICOSA ESPAGUETE 400GR COMUM</t>
+          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>3.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>101726</v>
+        <v>100110</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>234316</v>
+        <v>100027</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MILHO VERDE SOFRUTA  LATA 170G</t>
+          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>3.79</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>101130</v>
+        <v>100014</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MIST BOLO DONA BENTA 450GR CASEICHOCOLAT</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>7.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>287073</v>
+        <v>163918</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MOLHO DE TOMATE SABORELLE 300GR TRADICIO</t>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>167128</v>
+        <v>140665</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+          <t>FEIJAO PRETO KICALDO TP1 1KG</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8.59</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>128920</v>
+        <v>111571</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8.99</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>122984</v>
+        <v>100119</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>REFRI SPRITE PET 2L</t>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>9.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>104406</v>
+        <v>139059</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>LAVA LOUCAS LIQ YPE LIMAO FRASCO 500ML</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.49</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>257710</v>
+        <v>108434</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
+          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>261980</v>
+        <v>174382</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>20.99</v>
+        <v>37.99</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>228234</v>
+        <v>307145</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.99</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>100706</v>
+        <v>251877</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO 125GR MOLHO DE TOMATE</t>
+          <t>LEITE PO NINHO INTEGRAL LT 380G</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>5.69</v>
+        <v>20.99</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>221089</v>
+        <v>303196</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SARDINHA COQUEIRO OLEO 125G</t>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>5.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>106831</v>
+        <v>149122</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR</t>
+          <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.99</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>137423</v>
+        <v>234626</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>VINAGRE SABORELLE COMPOSTO BRANCO 750ML</t>
+          <t>MILHO VERDE BONARE LATA 170G</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>4.39</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>105470</v>
+        <v>106680</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM KG</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>23.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>152232</v>
+        <v>104403</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>REFRIG FANTA UVA 2L</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>14.99</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>105468</v>
+        <v>104410</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>17.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>105458</v>
+        <v>104406</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>18.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>105449</v>
+        <v>257710</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>32.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>105435</v>
+        <v>248450</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>36.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
+          <t>TERÇA - OFERTAS 20/05/25</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>106053</v>
+        <v>100373</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>18.99</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>SEGUNDA - AÇOUGUE 19/05/25</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>105062</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>18.99</v>
+        <v>24.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,789 +453,789 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>157014</v>
+        <v>105007</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINO - ACEM C/ OSSO KG</t>
+          <t>ABOBORA CABOTIA KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105461</v>
+        <v>104937</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+          <t>ALHO A GRANEL KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105468</v>
+        <v>105023</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>BANANA PRATA KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105451</v>
+        <v>104998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>BANANA TERRA KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105449</v>
+        <v>104903</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>BATATA DOCE ROSA KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>33.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>173342</v>
+        <v>105010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - MOCOTO KG</t>
+          <t>BATATA MONALISA KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>8.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105452</v>
+        <v>105001</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - PATINHO KG</t>
+          <t>BETERRABA KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>33.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105853</v>
+        <v>104919</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FRANGO CONG MARINGA KG</t>
+          <t>CEBOLA NACIONAL KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>305039</v>
+        <v>104862</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>CENOURA KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105765</v>
+        <v>104931</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MORTADELA MISTA PERDIGAO KG</t>
+          <t>LARANJA KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>239921</v>
+        <v>104944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>OVOS BRANCOS CARTELA 30 UNID</t>
+          <t>MACA NACIONAL KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.7</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>106054</v>
+        <v>104928</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUINO - LOMBO FRESCO KG</t>
+          <t>MANGA PALMER KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>18.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TERÇA - AÇOUGUE 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>106034</v>
+        <v>104883</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>MANGA TOMY KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>255232</v>
+        <v>104947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>ACHOC PO TODDY 750G</t>
+          <t>MELANCIA INTEIRA KG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.99</v>
+        <v>2.79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>100426</v>
+        <v>104996</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 1L MULTIPLO USO</t>
+          <t>MELAO AMARELO KG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>181416</v>
+        <v>113290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
+          <t>MELAO AMARELO REI / REDINHA KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>136523</v>
+        <v>104992</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARROZ KOBLENZ TP1 BRANCO 5KG</t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>27.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>225003</v>
+        <v>104961</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ARROZ RAMPINELLI 5KG TIPO1</t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>23.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>100031</v>
+        <v>104890</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
+          <t>UVA RED GLOBE NACIONAL KG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>326645</v>
+        <v>105460</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
+          <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>250013</v>
+        <v>105450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>BOVINO - ALCATRA KG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>286746</v>
+        <v>105459</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BISCOITO ROSQUINHA 600GR SULLPER  COCO</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>7.19</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>239682</v>
+        <v>239334</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOMBOM GAROTO SORTIDO 250G</t>
+          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>102085</v>
+        <v>105468</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.49</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>101137</v>
+        <v>105435</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>287369</v>
+        <v>107260</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>3.49</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>170451</v>
+        <v>305039</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2.89</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>247800</v>
+        <v>105062</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CERV BUDWEISER 330ML LAGER LN UNID</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>5.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>267604</v>
+        <v>106032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+          <t>SUINO - TOUCINHO FRESCO KG</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>303282</v>
+        <v>318330</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT UNID</t>
+          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>5.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>220499</v>
+        <v>100431</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CORONA EXTRA N LONG NECK 330ML</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>106866</v>
+        <v>102242</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CREME DE MILHO SINHA 500GR</t>
+          <t>AGUARD VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2.49</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>101066</v>
+        <v>116139</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CREME LEITE ITALAC 200GR TP</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>112978</v>
+        <v>107395</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500GR</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2.69</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>208281</v>
+        <v>100038</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DES AERO MOOD MEN 150ML</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>208304</v>
+        <v>148775</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
+          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>208280</v>
+        <v>199440</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DES AERO MOOD WOMEN 150ML</t>
+          <t>ARROZ SANTA FE 5 KG TP1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>142863</v>
+        <v>100040</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DESINFETANTE BAK YPE 2L LAVANDA</t>
+          <t>ARROZ TIO JORGE 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>10.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>134193</v>
+        <v>250013</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DESINFETANTE BAK YPE FLORAL 2LTS</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>10.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>254080</v>
+        <v>286197</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DESINFETANTE BAK YPE LAVANDA L2LP1,8L</t>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>10.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>312369</v>
+        <v>114037</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
+          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>6.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>312371</v>
+        <v>252992</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
+          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>312370</v>
+        <v>298701</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.99</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>312366</v>
+        <v>242930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1245,775 +1245,487 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>312367</v>
+        <v>110330</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>312368</v>
+        <v>123791</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
+          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>298933</v>
+        <v>123792</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>298932</v>
+        <v>123793</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>298931</v>
+        <v>123795</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>298930</v>
+        <v>123796</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>298929</v>
+        <v>123797</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESINFETANTE START VOREL 2LT PINHO</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>6.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>298928</v>
+        <v>100423</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DETERG LIQ LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>298927</v>
+        <v>100419</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>311881</v>
+        <v>220037</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
+          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6.99</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>100391</v>
+        <v>204461</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
+          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>100394</v>
+        <v>100420</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
+          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>100392</v>
+        <v>100417</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
+          <t>DETERG LIQ LIMPOL 500ML MACA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>100402</v>
+        <v>106661</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML COCO</t>
+          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>100403</v>
+        <v>167686</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
+          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.69</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>100393</v>
+        <v>100014</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML MACA</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>100390</v>
+        <v>106922</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2.69</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>312365</v>
+        <v>131884</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>6.99</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>312364</v>
+        <v>130920</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6.99</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>102287</v>
+        <v>167128</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>4.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>273714</v>
+        <v>316048</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>EXTRATO TOMATE ELEFANTE 300G POTE</t>
+          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>7.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>100110</v>
+        <v>326954</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>FARINHA MILHO SINHA 500G BIJU</t>
+          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>3.19</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>100027</v>
+        <v>289451</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
+          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>7.69</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>100014</v>
+        <v>228234</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>4.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>163918</v>
+        <v>106831</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FEIJAO KICALDO 1KG CARIOCA</t>
+          <t>TEMP COMPLETO SABORELLE 930GR</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>6.99</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>140665</v>
+        <v>111010</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FEIJAO PRETO KICALDO TP1 1KG</t>
+          <t>TEMP COMPLETO SABORELLE 930GR S/PIMENTA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>8.390000000000001</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
+          <t>QUARTA - OFERTAS 21/05/25</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>111571</v>
+        <v>100884</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
+          <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>100119</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>139059</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>LAVA LOUCAS LIQ YPE LIMAO FRASCO 500ML</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>108434</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>LEITE CONDENSADO ITALAC 395GR SEMIDESNAT</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>5.99</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>174382</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>37.99</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>307145</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>LEITE PO NINHO 380GR INTEGRAL INSTANTANE</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>251877</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>LEITE PO NINHO INTEGRAL LT 380G</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>20.99</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>303196</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>2.39</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>149122</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>7.69</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>234626</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>MILHO VERDE BONARE LATA 170G</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>3.19</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>106680</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>OLEO SOJA SOYA  900ML</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>8.49</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>104403</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>REFRIG FANTA UVA 2L</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>9.390000000000001</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>104410</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>8.99</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>104406</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.99</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>257710</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>11.99</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>248450</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>SABAO EM PO OMO 1,6KG LAVAGEM PERFEITA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>21.99</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>TERÇA - OFERTAS 20/05/25</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>100373</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>24.99</v>
+        <v>5.49</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.49</v>
+        <v>5.59</v>
       </c>
     </row>
     <row r="5">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>4.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="8">
@@ -609,7 +609,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>4.99</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="11">
@@ -627,7 +627,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>7.99</v>
+        <v>8.390000000000001</v>
       </c>
     </row>
     <row r="12">
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.99</v>
+        <v>12.39</v>
       </c>
     </row>
     <row r="13">
@@ -745,15 +745,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>104992</v>
+        <v>239921</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>OVOS BRANCOS CARTELA 30 UNID</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.99</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="19">
@@ -763,15 +763,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>104961</v>
+        <v>104992</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>REPOLHO VERDE KG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>6.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="20">
@@ -781,33 +781,33 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>104890</v>
+        <v>104961</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>UVA RED GLOBE NACIONAL KG</t>
+          <t>TOMATE CARMEM KG</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>21.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>QUARTA - VERDURA 21/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>105460</v>
+        <v>104890</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>UVA RED GLOBE NACIONAL KG</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>19.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="22">
@@ -817,15 +817,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>105450</v>
+        <v>105460</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOVINO - ALCATRA KG</t>
+          <t>BOVINA - BISTECA PALETA KG</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>34.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="23">
@@ -835,15 +835,15 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105459</v>
+        <v>105450</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA MACA PEITO KG</t>
+          <t>BOVINO - ALCATRA KG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="24">
@@ -853,15 +853,15 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>239334</v>
+        <v>105459</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>26.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="25">
@@ -871,15 +871,15 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>105468</v>
+        <v>239334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>17.99</v>
+        <v>26.99</v>
       </c>
     </row>
     <row r="26">
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>105435</v>
+        <v>105468</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="27">
@@ -907,15 +907,15 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>107260</v>
+        <v>105435</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>BOVINO - COXAO MOLE KG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29.99</v>
+        <v>34.99</v>
       </c>
     </row>
     <row r="28">
@@ -925,15 +925,15 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>305039</v>
+        <v>107260</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>BOVINO - MACA DO PEITO KG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>17.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="29">
@@ -943,15 +943,15 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>105062</v>
+        <v>305039</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="30">
@@ -961,11 +961,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>106032</v>
+        <v>105062</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -975,19 +975,19 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>QUARTA - AÇOUGUE 21/05/25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>318330</v>
+        <v>106032</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
+          <t>SUINO - TOUCINHO FRESCO KG</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="32">
@@ -997,15 +997,15 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100431</v>
+        <v>318330</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>7.19</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="33">
@@ -1015,15 +1015,15 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>102242</v>
+        <v>100431</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AGUARD VELHO BARREIRO 910ML</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="34">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>116139</v>
+        <v>102242</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>AGUARD VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>7.39</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="35">
@@ -1051,11 +1051,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>107395</v>
+        <v>116139</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1069,15 +1069,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>100038</v>
+        <v>107395</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>27.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="37">
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>148775</v>
+        <v>100038</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>18.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="38">
@@ -1105,15 +1105,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>199440</v>
+        <v>148775</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>19.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="39">
@@ -1123,15 +1123,15 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>100040</v>
+        <v>199440</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARROZ TIO JORGE 5 KG BRANCO TIPO 1</t>
+          <t>ARROZ SANTA FE 5 KG TP1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>24.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="40">
@@ -1141,15 +1141,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>250013</v>
+        <v>100040</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>ARROZ TIO JORGE 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6.59</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="41">
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>286197</v>
+        <v>250013</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>7.99</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="42">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>114037</v>
+        <v>286197</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>15.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="43">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>252992</v>
+        <v>114037</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
+          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="44">
@@ -1213,15 +1213,15 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>298701</v>
+        <v>252992</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>4.19</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="45">
@@ -1231,15 +1231,15 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>242930</v>
+        <v>298701</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>6.99</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="46">
@@ -1249,15 +1249,15 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>110330</v>
+        <v>242930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="47">
@@ -1267,15 +1267,15 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>123791</v>
+        <v>110330</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="48">
@@ -1285,11 +1285,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>123792</v>
+        <v>123791</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>123793</v>
+        <v>123792</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1321,11 +1321,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>123795</v>
+        <v>123793</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -1339,11 +1339,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>123796</v>
+        <v>123795</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -1357,11 +1357,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>123797</v>
+        <v>123796</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT PINHO</t>
+          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -1375,15 +1375,15 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>100423</v>
+        <v>123797</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML COCO</t>
+          <t>DESINFETANTE START VOREL 2LT PINHO</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>2.59</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="54">
@@ -1393,11 +1393,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>100419</v>
+        <v>100423</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
+          <t>DETERG LIQ LIMPOL 500ML COCO</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -1411,11 +1411,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>220037</v>
+        <v>100419</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
+          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -1429,11 +1429,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>204461</v>
+        <v>220037</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
+          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>100420</v>
+        <v>204461</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
+          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>100417</v>
+        <v>100420</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML MACA</t>
+          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1483,11 +1483,11 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>106661</v>
+        <v>100417</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
+          <t>DETERG LIQ LIMPOL 500ML MACA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -1501,15 +1501,15 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>167686</v>
+        <v>106661</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
+          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>5.89</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="61">
@@ -1519,15 +1519,15 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>100014</v>
+        <v>167686</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="62">
@@ -1537,15 +1537,15 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>106922</v>
+        <v>100014</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>42.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="63">
@@ -1555,15 +1555,15 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>131884</v>
+        <v>106922</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>3.39</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="64">
@@ -1573,15 +1573,15 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>130920</v>
+        <v>131884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.89</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="65">
@@ -1591,15 +1591,15 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>167128</v>
+        <v>130920</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>8.789999999999999</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="66">
@@ -1609,15 +1609,15 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>316048</v>
+        <v>167128</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
+          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>17.99</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -1627,15 +1627,15 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>326954</v>
+        <v>316048</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>8.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="68">
@@ -1645,15 +1645,15 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>289451</v>
+        <v>326954</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
+          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>29.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="69">
@@ -1663,15 +1663,15 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>228234</v>
+        <v>289451</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="70">
@@ -1681,15 +1681,15 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>106831</v>
+        <v>228234</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR</t>
+          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.49</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="71">
@@ -1699,11 +1699,11 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>111010</v>
+        <v>106831</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR S/PIMENTA</t>
+          <t>TEMP COMPLETO SABORELLE 930GR</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -1717,14 +1717,32 @@
         </is>
       </c>
       <c r="B72" t="n">
+        <v>111010</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>TEMP COMPLETO SABORELLE 930GR S/PIMENTA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>11.49</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>QUARTA - OFERTAS 21/05/25</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
         <v>100884</v>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C73" t="inlineStr">
         <is>
           <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="D72" t="n">
+      <c r="D73" t="n">
         <v>5.49</v>
       </c>
     </row>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,33 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105007</v>
+        <v>105458</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ABOBORA CABOTIA KG</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4.49</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>104937</v>
+        <v>105449</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALHO A GRANEL KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -489,1261 +489,2107 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105023</v>
+        <v>115278</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BANANA PRATA KG</t>
+          <t>BOVINO - MIOLO DA PALETA KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>5.59</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>104998</v>
+        <v>231292</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BANANA TERRA KG</t>
+          <t>BOVINO - MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>7.99</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>104903</v>
+        <v>305039</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BATATA DOCE ROSA KG</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105010</v>
+        <v>106053</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BATATA MONALISA KG</t>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.89</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105001</v>
+        <v>105062</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>104919</v>
+        <v>105433</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEBOLA NACIONAL KG</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>104862</v>
+        <v>106054</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>5.49</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>104931</v>
+        <v>258810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>SUINO - PANCETA KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.390000000000001</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>104944</v>
+        <v>106050</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MACA NACIONAL KG</t>
+          <t>SUINO - PE SUINO FRESCO KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.39</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>104928</v>
+        <v>106052</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>104883</v>
+        <v>298239</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>MANGA TOMY KG</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>6.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104947</v>
+        <v>100431</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MELANCIA INTEIRA KG</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>2.79</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>104996</v>
+        <v>100020</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>MELAO AMARELO KG</t>
+          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>5.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>113290</v>
+        <v>258938</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MELAO AMARELO REI / REDINHA KG</t>
+          <t>ARROZ BRILHANTE TIPO1 BRANCO 5KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>239921</v>
+        <v>269680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>OVOS BRANCOS CARTELA 30 UNID</t>
+          <t>ARROZ DONA VAVA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>0.65</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>104992</v>
+        <v>326645</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>104961</v>
+        <v>130107</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>TOMATE CARMEM KG</t>
+          <t>AZEITE COCINERO EXTRA VIRGEM 500ML</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>6.49</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>QUARTA - VERDURA 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>104890</v>
+        <v>250013</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>UVA RED GLOBE NACIONAL KG</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>21.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>105460</v>
+        <v>215568</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>BOVINA - BISTECA PALETA KG</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>19.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105450</v>
+        <v>293188</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>BOVINO - ALCATRA KG</t>
+          <t>CACHACA PIRASSUNUNGA 51 RAIZ 600ML</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>34.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105459</v>
+        <v>305475</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA MACA PEITO KG</t>
+          <t>CAFE UNIAO 250GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>21.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>239334</v>
+        <v>265727</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BOVINO - CAPA DO CONTRA FILE KG</t>
+          <t>CERVEJA HEINEKEN 269ML LATA C/ 8UNID</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>105468</v>
+        <v>303283</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>17.99</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>105435</v>
+        <v>235809</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO MOLE KG</t>
+          <t>CR D SORRISO TR LIMP COMP PCO ESP 120G</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>34.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>107260</v>
+        <v>101063</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>29.99</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>305039</v>
+        <v>112978</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>17.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>105062</v>
+        <v>248717</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>DESINFETANTE POLITRIZ 1,75 LT LIMAO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>QUARTA - AÇOUGUE 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>106032</v>
+        <v>110507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>SUINO - TOUCINHO FRESCO KG</t>
+          <t>DESINFETANTE POLITRIZ 1,75L EUCALIPTO</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>318330</v>
+        <v>100275</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ACHOCOLATADO NESCAU 350GR EM PO</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT ALFAZEMA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>100431</v>
+        <v>248716</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT FLORAL</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>7.19</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>102242</v>
+        <v>100277</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AGUARD VELHO BARREIRO 910ML</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT GARDENIA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>116139</v>
+        <v>100274</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L FLORISTA</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT LAVANDA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>7.39</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>107395</v>
+        <v>110571</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AMACIANTE +FAMILIA 2L ROSAS</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT MARINE</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>7.39</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>100038</v>
+        <v>106624</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT ORQUIDEA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>27.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>148775</v>
+        <v>100281</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT PINHO</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>199440</v>
+        <v>100391</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARROZ SANTA FE 5 KG TP1</t>
+          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>19.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>100040</v>
+        <v>100394</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARROZ TIO JORGE 5 KG BRANCO TIPO 1</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>24.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>250013</v>
+        <v>100392</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>6.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>286197</v>
+        <v>100402</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+          <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>114037</v>
+        <v>100403</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CAFE SANTA CLARA 250GR CLASSICO</t>
+          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>15.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>252992</v>
+        <v>100393</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CEREAL SUCRILHOS KELLOGS 240G ORIGINAL</t>
+          <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>298701</v>
+        <v>100390</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CERVEJA AMSTEL 350ML LAGER SLEEK C/12 UN</t>
+          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>4.19</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>242930</v>
+        <v>253879</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>ENERG BALY MACA VERDE LATA 250ML</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>110330</v>
+        <v>102282</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO BONOMILHO 500GR CUSCUZ</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.19</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>123791</v>
+        <v>244425</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT CITRUS</t>
+          <t>ENERG.BALY FRUTAS TROPICAIS LATA 250ML</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>123792</v>
+        <v>244427</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT EUCALIPTO</t>
+          <t>ENERG.BALY MELANCIA LATA 250ML</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>123793</v>
+        <v>318892</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT FLORAL</t>
+          <t>ENERGETICO BALY 250ML ABACAXI  C/ HORTEL</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>123795</v>
+        <v>315650</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT JASMIM</t>
+          <t>ENERGETICO BALY 250ML CITRUS</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>123796</v>
+        <v>244422</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT LAVANDA</t>
+          <t>ENERGETICO BALY 250ML COCO E ACAI</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>123797</v>
+        <v>312640</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DESINFETANTE START VOREL 2LT PINHO</t>
+          <t>ENERGETICO BALY 250ML COLA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>100423</v>
+        <v>244423</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML COCO</t>
+          <t>ENERGETICO BALY 250ML ENERGY DRINK LT</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>100419</v>
+        <v>303516</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML CRISTAL</t>
+          <t>ENERGETICO BALY 250ML FLYNOW S/ACUCAR</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>220037</v>
+        <v>312067</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML JABOTICABA</t>
+          <t>ENERGETICO BALY 250ML FRUTAS VERMELHAS</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>204461</v>
+        <v>302658</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LAVANDA</t>
+          <t>ENERGETICO BALY 250ML MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>100420</v>
+        <v>305260</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML LIMAO</t>
+          <t>ENERGETICO BALY 250ML PITAYA DRAGON</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>100417</v>
+        <v>302659</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML MACA</t>
+          <t>ENERGETICO BALY 250ML TANGERINA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>106661</v>
+        <v>312639</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DETERG LIQ LIMPOL 500ML NEUTRO</t>
+          <t>ENERGETICO BALY 250ML TROPICAL ZERO ACUC</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2.59</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>167686</v>
+        <v>303517</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>FEIJAO CARIOCA KI SABOR 1KG</t>
+          <t>ENERGETICO BALY 250ML ZERO ACUCAR</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>5.89</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>100014</v>
+        <v>273004</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>106922</v>
+        <v>273000</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>42.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>131884</v>
+        <v>273005</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>3.39</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>130920</v>
+        <v>304353</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MILHO VERDE FUGINI VAPOR LT 200GR</t>
+          <t>ENX BUCAL CEPACOL 500ML MENTA FUSION</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>3.89</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>167128</v>
+        <v>313958</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OLEO SOJA REFINADO CONCORDIA 900ML</t>
+          <t>ENX BUCAL CEPACOL 500ML MENTA ICE S/ALCO</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>8.789999999999999</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>316048</v>
+        <v>276631</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO LEBLON 30M L12P11 SOFT B</t>
+          <t>ENX BUCAL CEPACOL 500ML MENTA PROTECT+FL</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>326954</v>
+        <v>313959</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+          <t>ENXAG BUCAL CEPACOL 500ML CITRUS FUSION</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>8.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>289451</v>
+        <v>276630</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SABAO EM PO +CASA 5KG MULTIACAO SACHE</t>
+          <t>ENXAGUANTE BUCAL CEPACOL 500ML MENTA INT</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>29.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>228234</v>
+        <v>315319</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SABAO OMO PO LAVAG PERFEIT 800G CAIXA</t>
+          <t>ENXAGUE BUCAL CEPACOL LEV 500ML PAG 350M</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>106831</v>
+        <v>100780</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.49</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>111010</v>
+        <v>324143</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TEMP COMPLETO SABORELLE 930GR S/PIMENTA</t>
+          <t>FARINHA DE MANDIOCA OVINHA DONA DE 1 KG</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.49</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>QUARTA - OFERTAS 21/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B73" t="n">
+        <v>100110</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>100027</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>8.19</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>100014</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>FEIJAO GOL CORES 1KG</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>100013</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>FEIJAO TIO JORGE 1 KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>111571</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>255841</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO AMAFIL 500G</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>113183</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>LEITE COND MARAJOARA 395GR SEMIDESNATADO</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>106922</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>219003</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>LEITE UHT INTEGRAL ZERO LACTOSE C/TAMPA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>6.49</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>260659</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>LIMPADOR QBOA 500ML LIMPEZA PESADA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>303196</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>101726</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>149121</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MASSA P/ TAPIOCA AMAFIL 500G</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>4.49</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>107640</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>MILHO VERDE QUERO 170GR LATA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3.59</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>321107</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>106680</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>OLEO SOJA SOYA  900ML</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>322795</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>PAPEL HIGIENICO ONDUNORTE ROSE NT 6X12 (</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>320166</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>PAPEL TOALHA  ABSOLUTO 240FLHAS C/2 ROLO</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>128920</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>104403</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>REFRIG FANTA UVA 2L</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>9.49</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>104414</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>REFRIG SUKITA 2L UVA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>257157</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>ROSCA MICOS DE COCO 600G</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>263553</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>ROSQUINHA LEITE MICOS 600G</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>144261</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>SAB PALM NATURALS T.SEGREDO SEDUTOR 150G</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>107698</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR ALOE E OLIVA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>107699</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR COCO E ALGODAO</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>157417</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR GELEIA REAL E PROT</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>108866</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR LEITE E PETALAS ROSA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>108867</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR MANT CACAU E KARITE</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>167507</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR OL.NUTRI</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>108873</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR OLE AMEN E LANOLINA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>121641</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>SAB PALMOLIVE 150GR OLE ARGAN E OL COMPL</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>292093</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>SABAO BARRA ESTRELA 900GR NEUTRO</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>326954</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>296910</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SABAO EM PO ASSIM 800GR TRIPLACAO FLORAL</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>286199</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>261083</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>190286</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SABONETE NATURALS JASMIM 150G</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>324239</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SABONETE PALMOLIVE 150GR ARGILA PRETA E</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>301365</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SABONETE PALMOLIVE 150GR MELANCIA E LICH</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>228933</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SABONETE PALMOLIVE 150GR SENSACAO PURIFI</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>306134</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SABONETE PALMOLIVE 150GR TANGERINA E ALE</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>100373</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>SODA CAUSTICA SOL 1KG</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>25.99</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>259589</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>STELLA ARTOIS ONE WAY 600ML</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>286325</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>114072</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>TALCO DESOD TABU PERFUMADO 100GR</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
         <v>100884</v>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
-      <c r="D73" t="n">
-        <v>5.49</v>
+      <c r="D120" t="n">
+        <v>5.39</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D120"/>
+  <dimension ref="A1:D121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,217 +453,217 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105458</v>
+        <v>298239</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105449</v>
+        <v>100431</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - COXAO DURO KG</t>
+          <t>AGUA SANIT QBOA 2L MULTI USO</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.99</v>
+        <v>7.39</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>115278</v>
+        <v>100020</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DA PALETA KG</t>
+          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>231292</v>
+        <v>258938</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - MIOLO DO ACEM KG</t>
+          <t>ARROZ BRILHANTE TIPO1 BRANCO 5KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>305039</v>
+        <v>269680</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>ARROZ DONA VAVA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>106053</v>
+        <v>326645</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105062</v>
+        <v>130107</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>AZEITE COCINERO EXTRA VIRGEM 500ML</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.99</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105433</v>
+        <v>250013</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SUINO - COSTELA SUINA KG</t>
+          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>23.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106054</v>
+        <v>215568</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUINO - LOMBO FRESCO KG</t>
+          <t>CACHACA BANANAZINHA 900ML</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>19.99</v>
+        <v>39.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>258810</v>
+        <v>293188</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUINO - PANCETA KG</t>
+          <t>CACHACA PIRASSUNUNGA 51 RAIZ 600ML</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106050</v>
+        <v>305475</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUINO - PE SUINO FRESCO KG</t>
+          <t>CAFE UNIAO 250GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>QUINTA - AÇOUGUE 22/05/25</t>
+          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>106052</v>
+        <v>265727</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>SUINO - PELE SUINA FRESCA KG</t>
+          <t>CERVEJA HEINEKEN 269ML LATA C/ 8UNID</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.99</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="14">
@@ -673,15 +673,15 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>298239</v>
+        <v>303283</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>8.59</v>
+        <v>5.89</v>
       </c>
     </row>
     <row r="15">
@@ -691,15 +691,15 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100431</v>
+        <v>235809</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AGUA SANIT QBOA 2L MULTI USO</t>
+          <t>CR D SORRISO TR LIMP COMP PCO ESP 120G</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>7.39</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="16">
@@ -709,15 +709,15 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>100020</v>
+        <v>101063</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
+          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>25.99</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="17">
@@ -727,15 +727,15 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>258938</v>
+        <v>112978</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ARROZ BRILHANTE TIPO1 BRANCO 5KG</t>
+          <t>CUSCUZ DE MILHO SINHA 500GR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>23.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="18">
@@ -745,15 +745,15 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>269680</v>
+        <v>248717</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ARROZ DONA VAVA 5KG TIPO 1</t>
+          <t>DESINFETANTE POLITRIZ 1,75 LT LIMAO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>23.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="19">
@@ -763,15 +763,15 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>326645</v>
+        <v>110507</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
+          <t>DESINFETANTE POLITRIZ 1,75L EUCALIPTO</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>19.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="20">
@@ -781,15 +781,15 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>130107</v>
+        <v>100275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AZEITE COCINERO EXTRA VIRGEM 500ML</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT ALFAZEMA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>52.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="21">
@@ -799,15 +799,15 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>250013</v>
+        <v>248716</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BISC MARILAN CRACKER ESPECIAL 350GR</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT FLORAL</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>6.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="22">
@@ -817,15 +817,15 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>215568</v>
+        <v>100277</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CACHACA BANANAZINHA 900ML</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT GARDENIA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>39.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="23">
@@ -835,11 +835,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>293188</v>
+        <v>100274</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CACHACA PIRASSUNUNGA 51 RAIZ 600ML</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT LAVANDA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -853,15 +853,15 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>305475</v>
+        <v>110571</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CAFE UNIAO 250GR TRADICIONAL</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT MARINE</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="25">
@@ -871,15 +871,15 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>265727</v>
+        <v>106624</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 269ML LATA C/ 8UNID</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT ORQUIDEA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>4.49</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="26">
@@ -889,15 +889,15 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>303283</v>
+        <v>100281</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 350ML SLEEK LT C/12 UNI</t>
+          <t>DESINFETANTE POLITRIZ 1,75LT PINHO</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>5.89</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="27">
@@ -907,15 +907,15 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>235809</v>
+        <v>100391</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CR D SORRISO TR LIMP COMP PCO ESP 120G</t>
+          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>4.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="28">
@@ -925,15 +925,15 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>101063</v>
+        <v>100394</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CREME LEITE PIRACANJUBA 200GR UHT</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>4.69</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="29">
@@ -943,11 +943,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>112978</v>
+        <v>100392</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CUSCUZ DE MILHO SINHA 500GR</t>
+          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -961,15 +961,15 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>248717</v>
+        <v>100402</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75 LT LIMAO</t>
+          <t>DETERGENTE LIQ YPE 500ML COCO</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="31">
@@ -979,15 +979,15 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>110507</v>
+        <v>100403</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75L EUCALIPTO</t>
+          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>6.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="32">
@@ -997,15 +997,15 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100275</v>
+        <v>100393</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT ALFAZEMA</t>
+          <t>DETERGENTE LIQ YPE 500ML MACA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>6.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="33">
@@ -1015,15 +1015,15 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>248716</v>
+        <v>100390</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT FLORAL</t>
+          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>6.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="34">
@@ -1033,15 +1033,15 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>100277</v>
+        <v>253879</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT GARDENIA</t>
+          <t>ENERG BALY MACA VERDE LATA 250ML</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="35">
@@ -1051,15 +1051,15 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>100274</v>
+        <v>102282</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT LAVANDA</t>
+          <t>ENERG RED BULL 250ML TRAD</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>6.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="36">
@@ -1069,15 +1069,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>110571</v>
+        <v>244425</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT MARINE</t>
+          <t>ENERG.BALY FRUTAS TROPICAIS LATA 250ML</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="37">
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>106624</v>
+        <v>244427</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT ORQUIDEA</t>
+          <t>ENERG.BALY MELANCIA LATA 250ML</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="38">
@@ -1105,15 +1105,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>100281</v>
+        <v>318892</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>DESINFETANTE POLITRIZ 1,75LT PINHO</t>
+          <t>ENERGETICO BALY 250ML ABACAXI  C/ HORTEL</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="39">
@@ -1123,15 +1123,15 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>100391</v>
+        <v>315650</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CAPIM LIMAO</t>
+          <t>ENERGETICO BALY 250ML CITRUS</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="40">
@@ -1141,15 +1141,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>100394</v>
+        <v>244422</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR</t>
+          <t>ENERGETICO BALY 250ML COCO E ACAI</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="41">
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>100392</v>
+        <v>312640</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML CLEAR CARE</t>
+          <t>ENERGETICO BALY 250ML COLA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="42">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>100402</v>
+        <v>244423</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML COCO</t>
+          <t>ENERGETICO BALY 250ML ENERGY DRINK LT</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="43">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>100403</v>
+        <v>303516</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML LIMAO</t>
+          <t>ENERGETICO BALY 250ML FLYNOW S/ACUCAR</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="44">
@@ -1213,15 +1213,15 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>100393</v>
+        <v>312067</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML MACA</t>
+          <t>ENERGETICO BALY 250ML FRUTAS VERMELHAS</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="45">
@@ -1231,15 +1231,15 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>100390</v>
+        <v>302658</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQ YPE 500ML NEUTRO</t>
+          <t>ENERGETICO BALY 250ML MORANGO E PESSEGO</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="46">
@@ -1249,11 +1249,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>253879</v>
+        <v>305260</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ENERG BALY MACA VERDE LATA 250ML</t>
+          <t>ENERGETICO BALY 250ML PITAYA DRAGON</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -1267,15 +1267,15 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>102282</v>
+        <v>302659</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ENERG RED BULL 250ML TRAD</t>
+          <t>ENERGETICO BALY 250ML TANGERINA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>8.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="48">
@@ -1285,11 +1285,11 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>244425</v>
+        <v>312639</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ENERG.BALY FRUTAS TROPICAIS LATA 250ML</t>
+          <t>ENERGETICO BALY 250ML TROPICAL ZERO ACUC</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>244427</v>
+        <v>303517</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ENERG.BALY MELANCIA LATA 250ML</t>
+          <t>ENERGETICO BALY 250ML ZERO ACUCAR</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -1321,15 +1321,15 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>318892</v>
+        <v>273004</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML ABACAXI  C/ HORTEL</t>
+          <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="51">
@@ -1339,15 +1339,15 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>315650</v>
+        <v>273000</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML CITRUS</t>
+          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="52">
@@ -1357,15 +1357,15 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>244422</v>
+        <v>273005</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML COCO E ACAI</t>
+          <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>4.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="53">
@@ -1375,15 +1375,15 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>312640</v>
+        <v>304353</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML COLA</t>
+          <t>ENX BUCAL CEPACOL 500ML MENTA FUSION</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="54">
@@ -1393,15 +1393,15 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>244423</v>
+        <v>313958</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML ENERGY DRINK LT</t>
+          <t>ENX BUCAL CEPACOL 500ML MENTA ICE S/ALCO</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="55">
@@ -1411,15 +1411,15 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>303516</v>
+        <v>276631</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML FLYNOW S/ACUCAR</t>
+          <t>ENX BUCAL CEPACOL 500ML MENTA PROTECT+FL</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="56">
@@ -1429,15 +1429,15 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>312067</v>
+        <v>313959</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML FRUTAS VERMELHAS</t>
+          <t>ENXAG BUCAL CEPACOL 500ML CITRUS FUSION</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="57">
@@ -1447,15 +1447,15 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>302658</v>
+        <v>276630</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML MORANGO E PESSEGO</t>
+          <t>ENXAGUANTE BUCAL CEPACOL 500ML MENTA INT</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="58">
@@ -1465,15 +1465,15 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>305260</v>
+        <v>315319</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML PITAYA DRAGON</t>
+          <t>ENXAGUE BUCAL CEPACOL LEV 500ML PAG 350M</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>4.99</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="59">
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>302659</v>
+        <v>100780</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML TANGERINA</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>4.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="60">
@@ -1501,15 +1501,15 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>312639</v>
+        <v>324143</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML TROPICAL ZERO ACUC</t>
+          <t>FARINHA DE MANDIOCA OVINHA DONA DE 1 KG</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>4.99</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="61">
@@ -1519,15 +1519,15 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>303517</v>
+        <v>100110</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ENERGETICO BALY 250ML ZERO ACUCAR</t>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>4.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="62">
@@ -1537,15 +1537,15 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>273004</v>
+        <v>100027</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML MELANCIA LATA</t>
+          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>8.99</v>
+        <v>8.19</v>
       </c>
     </row>
     <row r="63">
@@ -1555,15 +1555,15 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>273000</v>
+        <v>100014</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML MORANGO E KIWI</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>8.99</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="64">
@@ -1573,15 +1573,15 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>273005</v>
+        <v>100013</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ENERGETICO ENGOV UP 269ML ORIGINAL LATA</t>
+          <t>FEIJAO TIO JORGE 1 KG CARIOCA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>8.99</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="65">
@@ -1591,15 +1591,15 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>304353</v>
+        <v>111571</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ENX BUCAL CEPACOL 500ML MENTA FUSION</t>
+          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>15.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="66">
@@ -1609,15 +1609,15 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>313958</v>
+        <v>255841</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ENX BUCAL CEPACOL 500ML MENTA ICE S/ALCO</t>
+          <t>FLOCAO DE MILHO AMAFIL 500G</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>15.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="67">
@@ -1627,15 +1627,15 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>276631</v>
+        <v>113183</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>ENX BUCAL CEPACOL 500ML MENTA PROTECT+FL</t>
+          <t>LEITE COND MARAJOARA 395GR SEMIDESNATADO</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>15.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="68">
@@ -1645,15 +1645,15 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>313959</v>
+        <v>170363</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>ENXAG BUCAL CEPACOL 500ML CITRUS FUSION</t>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>15.99</v>
+        <v>7.19</v>
       </c>
     </row>
     <row r="69">
@@ -1663,15 +1663,15 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>276630</v>
+        <v>106922</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ENXAGUANTE BUCAL CEPACOL 500ML MENTA INT</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>15.99</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="70">
@@ -1681,15 +1681,15 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>315319</v>
+        <v>219003</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ENXAGUE BUCAL CEPACOL LEV 500ML PAG 350M</t>
+          <t>LEITE UHT INTEGRAL ZERO LACTOSE C/TAMPA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>15.99</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="71">
@@ -1699,15 +1699,15 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>100780</v>
+        <v>260659</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>LIMPADOR QBOA 500ML LIMPEZA PESADA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>3.19</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="72">
@@ -1717,15 +1717,15 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>324143</v>
+        <v>303196</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FARINHA DE MANDIOCA OVINHA DONA DE 1 KG</t>
+          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>8.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="73">
@@ -1735,15 +1735,15 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>100110</v>
+        <v>101726</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FARINHA MILHO SINHA 500G BIJU</t>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>3.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="74">
@@ -1753,15 +1753,15 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>100027</v>
+        <v>149121</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO ORQUIDEA 1KG SEM FERMENTO</t>
+          <t>MASSA P/ TAPIOCA AMAFIL 500G</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>8.19</v>
+        <v>4.49</v>
       </c>
     </row>
     <row r="75">
@@ -1771,15 +1771,15 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>100014</v>
+        <v>107640</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>MILHO VERDE QUERO 170GR LATA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>4.99</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="76">
@@ -1789,15 +1789,15 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>100013</v>
+        <v>321107</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>FEIJAO TIO JORGE 1 KG CARIOCA</t>
+          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>6.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="77">
@@ -1807,15 +1807,15 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>111571</v>
+        <v>106680</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FLOCAO ARROZ BONOARROZ 500GR</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>3.19</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="78">
@@ -1825,15 +1825,15 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>255841</v>
+        <v>322795</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO AMAFIL 500G</t>
+          <t>PAPEL HIGIENICO ONDUNORTE ROSE NT 6X12 (</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>2.99</v>
+        <v>12.99</v>
       </c>
     </row>
     <row r="79">
@@ -1843,15 +1843,15 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>113183</v>
+        <v>320166</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>LEITE COND MARAJOARA 395GR SEMIDESNATADO</t>
+          <t>PAPEL TOALHA  ABSOLUTO 240FLHAS C/2 ROLO</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>6.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="80">
@@ -1861,15 +1861,15 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>106922</v>
+        <v>128920</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>42.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="81">
@@ -1879,15 +1879,15 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>219003</v>
+        <v>104403</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LEITE UHT INTEGRAL ZERO LACTOSE C/TAMPA</t>
+          <t>REFRIG FANTA UVA 2L</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>6.49</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="82">
@@ -1897,15 +1897,15 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>260659</v>
+        <v>104414</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>LIMPADOR QBOA 500ML LIMPEZA PESADA</t>
+          <t>REFRIG SUKITA 2L UVA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>5.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="83">
@@ -1915,15 +1915,15 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>303196</v>
+        <v>104406</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MACARRAO ESPAGUETE GALO 400GR AMARELO</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>2.39</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="84">
@@ -1933,15 +1933,15 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>101726</v>
+        <v>257157</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+          <t>ROSCA MICOS DE COCO 600G</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>8.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="85">
@@ -1951,15 +1951,15 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>149121</v>
+        <v>263553</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MASSA P/ TAPIOCA AMAFIL 500G</t>
+          <t>ROSQUINHA LEITE MICOS 600G</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>4.49</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="86">
@@ -1969,15 +1969,15 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>107640</v>
+        <v>144261</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MILHO VERDE QUERO 170GR LATA</t>
+          <t>SAB PALM NATURALS T.SEGREDO SEDUTOR 150G</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.59</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="87">
@@ -1987,15 +1987,15 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>321107</v>
+        <v>107698</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MOLHO PRONTO QUERO 240GR TRADICIONAL SCH</t>
+          <t>SAB PALMOLIVE 150GR ALOE E OLIVA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>2.39</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="88">
@@ -2005,15 +2005,15 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>106680</v>
+        <v>107699</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>SAB PALMOLIVE 150GR COCO E ALGODAO</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>8.59</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="89">
@@ -2023,15 +2023,15 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>322795</v>
+        <v>157417</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>PAPEL HIGIENICO ONDUNORTE ROSE NT 6X12 (</t>
+          <t>SAB PALMOLIVE 150GR GELEIA REAL E PROT</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="90">
@@ -2041,15 +2041,15 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>320166</v>
+        <v>108866</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>PAPEL TOALHA  ABSOLUTO 240FLHAS C/2 ROLO</t>
+          <t>SAB PALMOLIVE 150GR LEITE E PETALAS ROSA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>9.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="91">
@@ -2059,15 +2059,15 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>128920</v>
+        <v>108867</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>SAB PALMOLIVE 150GR MANT CACAU E KARITE</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>7.99</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="92">
@@ -2077,15 +2077,15 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>104403</v>
+        <v>167507</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>REFRIG FANTA UVA 2L</t>
+          <t>SAB PALMOLIVE 150GR OL.NUTRI</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>9.49</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="93">
@@ -2095,15 +2095,15 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>104414</v>
+        <v>108873</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>REFRIG SUKITA 2L UVA</t>
+          <t>SAB PALMOLIVE 150GR OLE AMEN E LANOLINA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7.49</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="94">
@@ -2113,15 +2113,15 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>104406</v>
+        <v>121641</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>SAB PALMOLIVE 150GR OLE ARGAN E OL COMPL</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.49</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="95">
@@ -2131,15 +2131,15 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>257157</v>
+        <v>292093</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ROSCA MICOS DE COCO 600G</t>
+          <t>SABAO BARRA ESTRELA 900GR NEUTRO</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>7.49</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="96">
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>263553</v>
+        <v>326954</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ROSQUINHA LEITE MICOS 600G</t>
+          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7.49</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="97">
@@ -2167,15 +2167,15 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>144261</v>
+        <v>296910</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>SAB PALM NATURALS T.SEGREDO SEDUTOR 150G</t>
+          <t>SABAO EM PO ASSIM 800GR TRIPLACAO FLORAL</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>3.69</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="98">
@@ -2185,15 +2185,15 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>107698</v>
+        <v>286199</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR ALOE E OLIVA</t>
+          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>3.69</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="99">
@@ -2203,15 +2203,15 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>107699</v>
+        <v>261083</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR COCO E ALGODAO</t>
+          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.69</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="100">
@@ -2221,11 +2221,11 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>157417</v>
+        <v>190286</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR GELEIA REAL E PROT</t>
+          <t>SABONETE NATURALS JASMIM 150G</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>108866</v>
+        <v>324239</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR LEITE E PETALAS ROSA</t>
+          <t>SABONETE PALMOLIVE 150GR ARGILA PRETA E</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -2257,11 +2257,11 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>108867</v>
+        <v>301365</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR MANT CACAU E KARITE</t>
+          <t>SABONETE PALMOLIVE 150GR MELANCIA E LICH</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -2275,11 +2275,11 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>167507</v>
+        <v>228933</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR OL.NUTRI</t>
+          <t>SABONETE PALMOLIVE 150GR SENSACAO PURIFI</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -2293,11 +2293,11 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>108873</v>
+        <v>306134</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR OLE AMEN E LANOLINA</t>
+          <t>SABONETE PALMOLIVE 150GR TANGERINA E ALE</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -2311,15 +2311,15 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>121641</v>
+        <v>100373</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SAB PALMOLIVE 150GR OLE ARGAN E OL COMPL</t>
+          <t>SODA CAUSTICA SOL 1KG</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>3.69</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="106">
@@ -2329,15 +2329,15 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>292093</v>
+        <v>259589</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SABAO BARRA ESTRELA 900GR NEUTRO</t>
+          <t>STELLA ARTOIS ONE WAY 600ML</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.99</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="107">
@@ -2347,15 +2347,15 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>326954</v>
+        <v>286325</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SABAO BARRA REGENTE 5X200GR NEUTRO</t>
+          <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>8.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="108">
@@ -2365,15 +2365,15 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>296910</v>
+        <v>114072</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SABAO EM PO ASSIM 800GR TRIPLACAO FLORAL</t>
+          <t>TALCO DESOD TABU PERFUMADO 100GR</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>8.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="109">
@@ -2383,213 +2383,231 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>286199</v>
+        <v>100884</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SABAO PO TIXAN YPE 800GR MACIEZ CAIXA</t>
+          <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>9.99</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>261083</v>
+        <v>105458</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SABAO PO TIXAN YPE 800GR PRIMAVERA CAIXA</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>9.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>190286</v>
+        <v>105449</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>SABONETE NATURALS JASMIM 150G</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>3.69</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>324239</v>
+        <v>115278</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SABONETE PALMOLIVE 150GR ARGILA PRETA E</t>
+          <t>BOVINO - MIOLO DA PALETA KG</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>3.69</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>301365</v>
+        <v>231292</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SABONETE PALMOLIVE 150GR MELANCIA E LICH</t>
+          <t>BOVINO - MIOLO DO ACEM KG</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>3.69</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>228933</v>
+        <v>305039</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SABONETE PALMOLIVE 150GR SENSACAO PURIFI</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>3.69</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>306134</v>
+        <v>106053</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SABONETE PALMOLIVE 150GR TANGERINA E ALE</t>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>3.69</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>100373</v>
+        <v>105062</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>SODA CAUSTICA SOL 1KG</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>25.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>259589</v>
+        <v>105433</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>STELLA ARTOIS ONE WAY 600ML</t>
+          <t>SUINO - COSTELA SUINA KG</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.49</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>286325</v>
+        <v>106054</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SUCO DE UVA AURORA 1,5LT TINTO TP</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>23.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>114072</v>
+        <v>258810</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>TALCO DESOD TABU PERFUMADO 100GR</t>
+          <t>SUINO - PANCETA KG</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>SEMANAL - ARRASADORAS 22 A 25/05/26</t>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>100884</v>
+        <v>106050</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>TEMPERO SAZON 60GR SCH CARNES/VERMELHO</t>
+          <t>SUINO - PE SUINO FRESCO KG</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>5.39</v>
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>QUINTA - AÇOUGUE 22/05/25</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>106052</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SUINO - PELE SUINA FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,33 +453,33 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105467</v>
+        <v>100038</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINA - LINGUA KG</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.99</v>
+        <v>27.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>152232</v>
+        <v>101137</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -489,19 +489,19 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105458</v>
+        <v>107376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="5">
@@ -511,15 +511,15 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105471</v>
+        <v>105467</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>BOVINA - LINGUA KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="6">
@@ -529,15 +529,15 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>105474</v>
+        <v>152232</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>BOVINO - BUCHO/HUMEM KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
@@ -547,15 +547,15 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>107260</v>
+        <v>105458</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="8">
@@ -565,15 +565,15 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>173342</v>
+        <v>105471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - MOCOTO KG</t>
+          <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="9">
@@ -583,15 +583,15 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>106008</v>
+        <v>105474</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>INGREDIENTES P/ FEIJOADA KG</t>
+          <t>BOVINO - FRALDINHA KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="10">
@@ -601,14 +601,68 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>107260</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>BOVINO - MACA DO PEITO KG</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>173342</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>BOVINO - MOCOTO KG</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>106008</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INGREDIENTES P/ FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SEXTA - AÇOUGUE 23/05/25</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>305039</v>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D13" t="n">
         <v>16.99</v>
       </c>
     </row>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,217 +453,487 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100038</v>
+        <v>102242</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>AGUARD VELHO BARREIRO 910ML</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>101137</v>
+        <v>236674</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107376</v>
+        <v>236672</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
+          <t>BEB FIU FIU ABORIGENE 750ML</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105467</v>
+        <v>236671</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINA - LINGUA KG</t>
+          <t>BEB FIU FIU CAJAZINHA 750ML</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152232</v>
+        <v>236673</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105458</v>
+        <v>286589</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>287184</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105474</v>
+        <v>286326</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107260</v>
+        <v>287177</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>173342</v>
+        <v>174010</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOVINO - MOCOTO KG</t>
+          <t>CACHACA SELETA 600ML</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.99</v>
+        <v>45.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106008</v>
+        <v>171895</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INGREDIENTES P/ FEIJOADA KG</t>
+          <t>CERV ANTARTICA ORIGINAL 300ML</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.99</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - BIRITAO 24/05/2025</t>
         </is>
       </c>
       <c r="B13" t="n">
+        <v>313599</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>267604</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>206930</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>GIN TANQUERAY LONDON 750ML</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>137381</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>248750</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>55.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>105461</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>105468</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>BOVINO - CARNE MOIDA KG</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>105451</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>BOVINO - CONTRA FILE KG</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>33.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>105471</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>BOVINO - COSTELA KG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>105449</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>BOVINO - COXAO DURO KG</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>30.99</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>105474</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>BOVINO - FRALDINHA KG</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>29.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>106008</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>INGREDIENTES P/ FEIJOADA KG</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
         <v>305039</v>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
-      <c r="D13" t="n">
-        <v>16.99</v>
+      <c r="D25" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>106053</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>105062</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>17.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>106034</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SUINO - SUAN FRESCA KG</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>13.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,123 +453,123 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100038</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>BOVINO - BISTECA CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>101137</v>
+        <v>105468</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>BOVINO - CARNE MOIDA KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEXTA -OFERTA ESPECIAL 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>107376</v>
+        <v>105451</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CERVEJA SKOL 269ML PILSEN LT C/15 UNID</t>
+          <t>BOVINO - CONTRA FILE KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>2.99</v>
+        <v>33.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>105467</v>
+        <v>105471</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BOVINA - LINGUA KG</t>
+          <t>BOVINO - COSTELA KG</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>152232</v>
+        <v>105449</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BOVINO - BUCHO/HUMEM KG</t>
+          <t>BOVINO - COXAO DURO KG</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.99</v>
+        <v>30.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105458</v>
+        <v>105474</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - CHAMBARI KG</t>
+          <t>BOVINO - FRALDINHA KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.99</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>106008</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>BOVINO - COSTELA KG</t>
+          <t>INGREDIENTES P/ FEIJOADA KG</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -579,91 +579,577 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>105474</v>
+        <v>305039</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>LINGUICA BOVINA KG CASEIRA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>30.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107260</v>
+        <v>106053</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BOVINO - MACA DO PEITO KG</t>
+          <t>SUINO - BISTECA CARRE FRESCA KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>29.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>173342</v>
+        <v>105062</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>BOVINO - MOCOTO KG</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - AÇOUGUE 24/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106008</v>
+        <v>106034</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>INGREDIENTES P/ FEIJOADA KG</t>
+          <t>SUINO - SUAN FRESCA KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>18.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEXTA - AÇOUGUE 23/05/25</t>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>305039</v>
+        <v>100031</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>27.99</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>105001</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>BETERRABA KG</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>5.39</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>104862</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CENOURA KG</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6.19</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>111131</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHUCHU VERDE KG</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>289785</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>COXA SEARA 1KG PACOTE</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>289786</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>COXINHA DA ASA SEARA 1KG PACOTE</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>104931</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LARANJA KG</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>146785</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LING PERDIGAO CARNE SUINA KG</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>28.99</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>104928</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MANGA PALMER KG</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>104883</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>MANGA TOMY KG</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>7.69</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>113290</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>MELAO AMARELO REI / REDINHA KG</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>15.99</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>104992</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>REPOLHO VERDE KG</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>102242</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AGUARD VELHO BARREIRO 910ML</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
         <v>16.99</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>236674</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>236672</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU ABORIGENE 750ML</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>236671</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU CAJAZINHA 750ML</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>236673</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>44.99</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>286589</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>287184</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>286326</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>287177</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>174010</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CACHACA SELETA 600ML</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>45.99</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>171895</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CERV ANTARTICA ORIGINAL 300ML</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>313599</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>267604</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>206930</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>GIN TANQUERAY LONDON 750ML</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>149.99</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>137381</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>129.99</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>SABADO - BIRITAO 24/05/2025</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>248750</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>55.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,61 +453,61 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>105461</v>
+        <v>105470</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>BOVINO - BISTECA CONTRA FILE KG</t>
+          <t>BOVINO - ACEM KG</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>105468</v>
+        <v>105459</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>BOVINO - CARNE MOIDA KG</t>
+          <t>BOVINO - BISTECA MACA PEITO KG</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.99</v>
+        <v>21.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>105451</v>
+        <v>105458</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>BOVINO - CONTRA FILE KG</t>
+          <t>BOVINO - CHAMBARI KG</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B5" t="n">
@@ -519,13 +519,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -537,619 +537,1897 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>105474</v>
+        <v>105475</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>BOVINO - FRALDINHA KG</t>
+          <t>BOVINO - MUSCULO KG</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>29.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>106008</v>
+        <v>105453</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>INGREDIENTES P/ FEIJOADA KG</t>
+          <t>FILE MIGNON KG</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.99</v>
+        <v>44.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>305039</v>
+        <v>105062</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>LINGUICA BOVINA KG CASEIRA</t>
+          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - AÇOUGUE 26/05/25</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>106053</v>
+        <v>106054</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA CARRE FRESCA KG</t>
+          <t>SUINO - LOMBO FRESCO KG</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>105062</v>
+        <v>193650</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SUINO - BISTECA PERNIL FRESCA KG</t>
+          <t>BATATAS PRE-FRITAS CONG BOUA  400GR</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SABADO - AÇOUGUE 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>106034</v>
+        <v>194792</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SUINO - SUAN FRESCA KG</t>
+          <t>BATATAS PRE-FRITAS CONG BOUA 2KG</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.99</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>100031</v>
+        <v>119923</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ARROZ REI  ARTHUR 5 KG BRANCO TIPO 1</t>
+          <t>CORACAO FRANGO AMERICANO CONG 1KG</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>27.99</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>105001</v>
+        <v>104602</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BETERRABA KG</t>
+          <t>COXA SADIA FRANGO PACOTE 1KG</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>5.39</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>104862</v>
+        <v>306504</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CENOURA KG</t>
+          <t>FIGADO FRANGO CONGELADO PERDIGAO 1KG</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>6.19</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>111131</v>
+        <v>108788</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CHUCHU VERDE KG</t>
+          <t>FRANGO A PASSARINHO SADIA TEMPE PC 1KG</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>289785</v>
+        <v>108773</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>COXA SEARA 1KG PACOTE</t>
+          <t>MOELA FRANGO SADIA CONG BDJ 1KG</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>289786</v>
+        <v>261357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>COXINHA DA ASA SEARA 1KG PACOTE</t>
+          <t>PEITO DE FRANGO SADIA 400GR DESFIADO</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>19.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>104931</v>
+        <v>108771</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>LARANJA KG</t>
+          <t>SOBRECOXA FGO CONG BDJ SADIA 1KG</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>9.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>146785</v>
+        <v>170464</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>LING PERDIGAO CARNE SUINA KG</t>
+          <t>STEAK FRANGO EMPANADO SADIA 100G STCE</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.99</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>104928</v>
+        <v>138538</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MANGA PALMER KG</t>
+          <t>TEKITOS SEARA FRANGO 300G</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>7.69</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>104883</v>
+        <v>127328</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>MANGA TOMY KG</t>
+          <t>TEKITOS SEARA QUEIJO OREGANO 300GR</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>7.69</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>113290</v>
+        <v>105842</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>MELAO AMARELO REI / REDINHA KG</t>
+          <t>ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SABADO - OFERTA ESPECIAL 24/05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>104992</v>
+        <v>107259</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>REPOLHO VERDE KG</t>
+          <t>CORACAO FRANGO KG</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>4.99</v>
+        <v>25.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>102242</v>
+        <v>105838</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AGUARD VELHO BARREIRO 910ML</t>
+          <t>COXA/SOBRECOXA FRANGO KG</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.99</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>236674</v>
+        <v>105840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BEB FIU FIU ABACAXI CORTELA 750ML</t>
+          <t>COXINHA DA ASA FRANGO KG</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>44.99</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>236672</v>
+        <v>109597</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BEB FIU FIU ABORIGENE 750ML</t>
+          <t>FILE PEITO FRANGO KG</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>44.99</v>
+        <v>19.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>236671</v>
+        <v>132881</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>BEB FIU FIU CAJAZINHA 750ML</t>
+          <t>SALSICHA FRIATO KG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>44.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>236673</v>
+        <v>298239</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BEB FIU FIU TANGERINA ACEROLA 750ML</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>44.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>286589</v>
+        <v>181416</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML BERRY VIBES</t>
+          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>287184</v>
+        <v>107394</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML CITRUS</t>
+          <t>AMAC ROUPAS YPE 2L CARINHO</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>286326</v>
+        <v>106712</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML RED HITS</t>
+          <t>AMAC ROUPAS YPE 2LT TERNURA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>287177</v>
+        <v>107413</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>BEBIDA ENGOV AFTER 250ML TANGERINA</t>
+          <t>AMACIANTE YPE 2L DELICADO BRANCO</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>9.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>174010</v>
+        <v>179914</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CACHACA SELETA 600ML</t>
+          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>45.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>171895</v>
+        <v>100038</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CERV ANTARTICA ORIGINAL 300ML</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.59</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>313599</v>
+        <v>325990</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 269ML C/ 15UN</t>
+          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3.69</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>267604</v>
+        <v>148775</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CERVEJA BUDWEISER 330ML ZERO ALCOOL LN U</t>
+          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>5.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>206930</v>
+        <v>100020</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>GIN TANQUERAY LONDON 750ML</t>
+          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>149.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>137381</v>
+        <v>325991</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>WHISKY JOHNNIE WALKER RED LABEL. 1LT</t>
+          <t>ARROZ PARBOLIZADO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>129.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SABADO - BIRITAO 24/05/2025</t>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>248750</v>
+        <v>326645</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WHISKY NATU NOBILIS  APERITIVO 1L</t>
+          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>55.99</v>
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>111378</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13.99</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>261728</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>286197</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>102085</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>101137</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>287369</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>170451</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2.89</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>242930</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>317589</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CREME DE LEITE UHT ITALAC 200GR 10% DE G</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2.99</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>208281</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>DES AERO MOOD MEN 150ML</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>208304</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>208280</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>DES AERO MOOD WOMEN 150ML</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>214812</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 2L CITRONELA</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>214065</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 2L FLORAL</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>107851</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 2L HERBAL</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>109602</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 2L LAVANDA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>100316</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 2LT EUCALIPTO</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>100315</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>DESINFETANTE +FAMILIA 2LT PINHO</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>312369</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>312371</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>312370</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>312366</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>312367</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>312368</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>298932</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>298931</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>298930</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>298929</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>298928</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>298933</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>298927</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>311881</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>119826</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>111567</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>110352</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>110353</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>252617</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>106663</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>113911</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>112163</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>113914</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>2.69</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>312365</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>312364</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>102287</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>100780</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>EXT TOMATE OLE 190GR CP</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>3.19</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>100110</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>100024</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>5.69</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>100014</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>FEIJAO GOL CORES 1KG</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>4.99</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>163918</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>6.69</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>284913</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>FLOCAO DE MILHO BONOFLOKOS 400GR</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>100119</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2.49</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>100789</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400GR PICANTE</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>100785</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>KETCHUP QUERO 400GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>155080</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>7.49</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>174382</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>38.99</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>170363</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>106922</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>42.99</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>156422</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>5.99</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>131884</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>101726</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>149122</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>7.99</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>221945</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>MILHO VERDE LATA 170G PREDILECTA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>3.99</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>106680</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>OLEO SOJA SOYA  900ML</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>128920</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>8.49</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>104410</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>8.99</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>104406</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>REFRIGERANTE COCA COLA 2L</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>257710</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.99</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>261980</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>100705</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>100693</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>100876</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>14.99</v>
       </c>
     </row>
   </sheetData>

--- a/ofertas_consolidadas.xlsx
+++ b/ofertas_consolidadas.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -843,7 +843,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.99</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="24">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.99</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="26">
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="27">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>19.99</v>
+        <v>19.89</v>
       </c>
     </row>
     <row r="28">
@@ -925,69 +925,69 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>132881</v>
+        <v>105853</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SALSICHA FRIATO KG</t>
+          <t>FRANGO CONG MARINGA KG</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>8.99</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 26//05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>298239</v>
+        <v>152244</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
+          <t>GALINHA PESADA NOROESTE CONG KG</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>8.59</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 26//05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>181416</v>
+        <v>228422</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
+          <t>LINGUICA SUPER FRANGO KG FRANGO GROSSA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEGUNDA - OFERTAS 26//05/25</t>
+          <t>SEGUNDA - COROCOCO 26/05/25 PESÁVEIS</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>107394</v>
+        <v>132881</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AMAC ROUPAS YPE 2L CARINHO</t>
+          <t>SALSICHA FRIATO KG</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.99</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="32">
@@ -997,15 +997,15 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>106712</v>
+        <v>298239</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AMAC ROUPAS YPE 2LT TERNURA</t>
+          <t>ACUCAR CRISTAL ECOCUCAR 2KG</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>10.99</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="33">
@@ -1015,11 +1015,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>107413</v>
+        <v>181416</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AMACIANTE YPE 2L DELICADO BRANCO</t>
+          <t>AMAC ROUPAS YPE 2L ACONCHEGO L2L PG1,8L</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1033,11 +1033,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>179914</v>
+        <v>107394</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
+          <t>AMAC ROUPAS YPE 2L CARINHO</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1051,15 +1051,15 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>100038</v>
+        <v>106712</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
+          <t>AMAC ROUPAS YPE 2LT TERNURA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>28.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="36">
@@ -1069,15 +1069,15 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>325990</v>
+        <v>107413</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
+          <t>AMACIANTE YPE 2L DELICADO BRANCO</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>23.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="37">
@@ -1087,15 +1087,15 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>148775</v>
+        <v>179914</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
+          <t>AMACIANTE YPE 2L INTENSO L2L P1,8L</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>17.99</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="38">
@@ -1105,15 +1105,15 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>100020</v>
+        <v>100038</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
+          <t>ARROZ BRANCO BREJEIRO 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>24.99</v>
+        <v>28.99</v>
       </c>
     </row>
     <row r="39">
@@ -1123,11 +1123,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>325991</v>
+        <v>325990</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ARROZ PARBOLIZADO FLORA 5KG TIPO 1</t>
+          <t>ARROZ BRANCO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1141,15 +1141,15 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>326645</v>
+        <v>148775</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
+          <t>ARROZ BRANCO PIANTA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>18.99</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="41">
@@ -1159,15 +1159,15 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>111378</v>
+        <v>100020</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
+          <t>ARROZ BRANCO REALENGO 5KG BRANCO TIPO 1</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.99</v>
+        <v>24.99</v>
       </c>
     </row>
     <row r="42">
@@ -1177,15 +1177,15 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>261728</v>
+        <v>325991</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
+          <t>ARROZ PARBOLIZADO FLORA 5KG TIPO 1</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>7.99</v>
+        <v>23.99</v>
       </c>
     </row>
     <row r="43">
@@ -1195,15 +1195,15 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>286197</v>
+        <v>326645</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
+          <t>ARROZ SEU ARROZ 5KG TP1 BRANCO</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>7.99</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="44">
@@ -1213,15 +1213,15 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>102085</v>
+        <v>111378</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
+          <t>AZEITONA VERDE LA VIOLETERA 160GR FATIAD</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.99</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="45">
@@ -1231,15 +1231,15 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>101137</v>
+        <v>261728</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
+          <t>BISCOITO FORTALEZA 350GR CREAM CRACKER</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>16.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="46">
@@ -1249,15 +1249,15 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>287369</v>
+        <v>286197</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
+          <t>BISCOITO MABEL 600GR ROSCA COCO</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="47">
@@ -1267,15 +1267,15 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>170451</v>
+        <v>102085</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
+          <t>CACHACA 51 PIRASSUNUNGA 965ML TRAD</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2.89</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="48">
@@ -1285,15 +1285,15 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>242930</v>
+        <v>101137</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CERVEJA HEINEKEN 330ML UND</t>
+          <t>CAFE MARATA 250GR A VACUO TRADIC</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>6.99</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="49">
@@ -1303,15 +1303,15 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>317589</v>
+        <v>287369</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CREME DE LEITE UHT ITALAC 200GR 10% DE G</t>
+          <t>CERV ANTARCTICA ORIGINAL 269ML LT C/15UN</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="50">
@@ -1321,15 +1321,15 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>208281</v>
+        <v>170451</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DES AERO MOOD MEN 150ML</t>
+          <t>CERV BRAHMA CHOPP LATA 269ML C/ 15 UNID</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>7.99</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="51">
@@ -1339,15 +1339,15 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>208304</v>
+        <v>242930</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
+          <t>CERVEJA HEINEKEN 330ML UND</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="52">
@@ -1357,15 +1357,15 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>208280</v>
+        <v>317589</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DES AERO MOOD WOMEN 150ML</t>
+          <t>CREME DE LEITE UHT ITALAC 200GR 10% DE G</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>7.99</v>
+        <v>2.99</v>
       </c>
     </row>
     <row r="53">
@@ -1375,15 +1375,15 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>214812</v>
+        <v>208281</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 2L CITRONELA</t>
+          <t>DES AERO MOOD MEN 150ML</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="54">
@@ -1393,15 +1393,15 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>214065</v>
+        <v>208304</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 2L FLORAL</t>
+          <t>DES AERO MOOD PROTECT UNISSEX 150ML</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="55">
@@ -1411,15 +1411,15 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>107851</v>
+        <v>208280</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 2L HERBAL</t>
+          <t>DES AERO MOOD WOMEN 150ML</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>6.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="56">
@@ -1429,11 +1429,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>109602</v>
+        <v>214812</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 2L LAVANDA</t>
+          <t>DESINFETANTE +FAMILIA 2L CITRONELA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>100316</v>
+        <v>214065</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 2LT EUCALIPTO</t>
+          <t>DESINFETANTE +FAMILIA 2L FLORAL</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -1465,11 +1465,11 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>100315</v>
+        <v>107851</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>DESINFETANTE +FAMILIA 2LT PINHO</t>
+          <t>DESINFETANTE +FAMILIA 2L HERBAL</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -1483,15 +1483,15 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>312369</v>
+        <v>109602</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
+          <t>DESINFETANTE +FAMILIA 2L LAVANDA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="60">
@@ -1501,15 +1501,15 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>312371</v>
+        <v>100316</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
+          <t>DESINFETANTE +FAMILIA 2LT EUCALIPTO</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="61">
@@ -1519,15 +1519,15 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>312370</v>
+        <v>100315</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
+          <t>DESINFETANTE +FAMILIA 2LT PINHO</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>7.99</v>
+        <v>6.99</v>
       </c>
     </row>
     <row r="62">
@@ -1537,11 +1537,11 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>312366</v>
+        <v>312369</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
+          <t>DESOD AERO MOOD 150ML ENERGY MEN</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -1555,11 +1555,11 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>312367</v>
+        <v>312371</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
+          <t>DESOD AERO MOOD 150ML FLOR LAVANDA FEM</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -1573,11 +1573,11 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>312368</v>
+        <v>312370</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT CARE FEM</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -1591,11 +1591,11 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>298932</v>
+        <v>312366</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESOD AERO MOOD 150ML HIDRAT PROTECT FEM</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -1609,11 +1609,11 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>298931</v>
+        <v>312367</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESOD AEROSOL MOOD 150ML FRUTAS VERMELHA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -1627,11 +1627,11 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>298930</v>
+        <v>312368</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
+          <t>DESODORANTE AERO MOOD 150ML POWER MEN</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -1645,7 +1645,7 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>298929</v>
+        <v>298932</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -1663,7 +1663,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>298928</v>
+        <v>298931</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>298933</v>
+        <v>298930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>298927</v>
+        <v>298929</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -1717,11 +1717,11 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>311881</v>
+        <v>298928</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -1735,15 +1735,15 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>119826</v>
+        <v>298933</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>2.69</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="74">
@@ -1753,15 +1753,15 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>111567</v>
+        <v>298927</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
+          <t>DESODORANTE ANTITRANSPIRANTE MOOD 150ML</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>2.69</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="75">
@@ -1771,15 +1771,15 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>110352</v>
+        <v>311881</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
+          <t>DESODORANTE MOOD 150ML CARE FEM HIDRAT I</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>2.69</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="76">
@@ -1789,11 +1789,11 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>110353</v>
+        <v>119826</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML CLEAR</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -1807,11 +1807,11 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>252617</v>
+        <v>111567</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML COCO</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -1825,11 +1825,11 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>106663</v>
+        <v>110352</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML LIMAO</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -1843,11 +1843,11 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>113911</v>
+        <v>110353</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MACA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -1861,11 +1861,11 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>112163</v>
+        <v>252617</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML MICELAR</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -1879,11 +1879,11 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>113914</v>
+        <v>106663</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML NEUTRO</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -1897,15 +1897,15 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>312365</v>
+        <v>113911</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MACA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="83">
@@ -1915,15 +1915,15 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>312364</v>
+        <v>112163</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. MARINE</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>7.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="84">
@@ -1933,15 +1933,15 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>102287</v>
+        <v>113914</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
+          <t>DETERGENTE LIQUIDO MINUANO 500ML. NEUTRO</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>4.99</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="85">
@@ -1951,15 +1951,15 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>100780</v>
+        <v>312365</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>EXT TOMATE OLE 190GR CP</t>
+          <t>DSOD AERO MOOD 150ML FLOR ALGODAO WOMEN</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>3.19</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="86">
@@ -1969,15 +1969,15 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>100110</v>
+        <v>312364</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FARINHA MILHO SINHA 500G BIJU</t>
+          <t>DSODORANTE AERO MOOD 150ML IMPACT MEN</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>3.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="87">
@@ -1987,15 +1987,15 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>100024</v>
+        <v>102287</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
+          <t>ENERGETICO EXTRA POWER 270ML UNID</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>5.69</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="88">
@@ -2005,15 +2005,15 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>100014</v>
+        <v>100780</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FEIJAO GOL CORES 1KG</t>
+          <t>EXT TOMATE OLE 190GR CP</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4.99</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="89">
@@ -2023,15 +2023,15 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>163918</v>
+        <v>100110</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FEIJAO KICALDO 1KG CARIOCA</t>
+          <t>FARINHA MILHO SINHA 500G BIJU</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>6.69</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="90">
@@ -2041,15 +2041,15 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>284913</v>
+        <v>100024</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FLOCAO DE MILHO BONOFLOKOS 400GR</t>
+          <t>FARINHA TRIGO DONA BENTA 1KG SEM FERMENT</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1.99</v>
+        <v>5.69</v>
       </c>
     </row>
     <row r="91">
@@ -2059,15 +2059,15 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>100119</v>
+        <v>100014</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
+          <t>FEIJAO GOL CORES 1KG</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>2.49</v>
+        <v>4.99</v>
       </c>
     </row>
     <row r="92">
@@ -2077,15 +2077,15 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>100789</v>
+        <v>163918</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>KETCHUP QUERO 400GR PICANTE</t>
+          <t>FEIJAO KICALDO 1KG CARIOCA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>7.99</v>
+        <v>6.69</v>
       </c>
     </row>
     <row r="93">
@@ -2095,15 +2095,15 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>100785</v>
+        <v>284913</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>KETCHUP QUERO 400GR TRADICIONAL</t>
+          <t>FLOCAO DE MILHO BONOFLOKOS 400GR</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>7.99</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="94">
@@ -2113,15 +2113,15 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>155080</v>
+        <v>100119</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
+          <t>FLOCAO MILHO SINHA  500GR MILHO</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>7.49</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="95">
@@ -2131,15 +2131,15 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>174382</v>
+        <v>100789</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
+          <t>KETCHUP QUERO 400GR PICANTE</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>38.99</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="96">
@@ -2149,15 +2149,15 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>170363</v>
+        <v>100785</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
+          <t>KETCHUP QUERO 400GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>7.29</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="97">
@@ -2167,15 +2167,15 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>106922</v>
+        <v>155080</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>LEITE PO CCGL INTEGRAL 1KG</t>
+          <t>LEITE CONDENSADO LEITBOM TP 395G</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>42.99</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="98">
@@ -2185,15 +2185,15 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>156422</v>
+        <v>174382</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
+          <t>LEITE EM PO INTEGRAL 1 KG ITALAC</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>5.99</v>
+        <v>38.99</v>
       </c>
     </row>
     <row r="99">
@@ -2203,15 +2203,15 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>131884</v>
+        <v>170363</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
+          <t>LEITE L.VIDA LEITBOM INTEGRAL</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>3.49</v>
+        <v>7.29</v>
       </c>
     </row>
     <row r="100">
@@ -2221,15 +2221,15 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>101726</v>
+        <v>106922</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
+          <t>LEITE PO CCGL INTEGRAL 1KG</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>8.99</v>
+        <v>42.99</v>
       </c>
     </row>
     <row r="101">
@@ -2239,15 +2239,15 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>149122</v>
+        <v>156422</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
+          <t>LIMP.VEJA MULT USO LEV 500 P450ML</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>7.99</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="102">
@@ -2257,15 +2257,15 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>221945</v>
+        <v>131884</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MILHO VERDE LATA 170G PREDILECTA</t>
+          <t>MACARRAO SELMI GALO ESPAGUETE 8 500GR VE</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>3.99</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="103">
@@ -2275,15 +2275,15 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>106680</v>
+        <v>101726</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OLEO SOJA SOYA  900ML</t>
+          <t>MAIONESE ARISCO 500GR TRADICIONAL</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>8.59</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="104">
@@ -2293,15 +2293,15 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>128920</v>
+        <v>149122</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>POLVILHO MATUTO 1KG DOCE</t>
+          <t>MASSA P/ TAPIOCA AMAFIL 1KG</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>8.49</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="105">
@@ -2311,15 +2311,15 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>104410</v>
+        <v>221945</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
+          <t>MILHO VERDE LATA 170G PREDILECTA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>8.99</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="106">
@@ -2329,15 +2329,15 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>104406</v>
+        <v>106680</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>REFRIGERANTE COCA COLA 2L</t>
+          <t>OLEO SOJA SOYA  900ML</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.49</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="107">
@@ -2347,15 +2347,15 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>257710</v>
+        <v>128920</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
+          <t>POLVILHO MATUTO 1KG DOCE</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.99</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="108">
@@ -2365,15 +2365,15 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>261980</v>
+        <v>104410</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+          <t>REFRIG GUARANA ANTARCTICA 2L PET ORIG</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>19.99</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="109">
@@ -2383,15 +2383,15 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>100705</v>
+        <v>104406</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+          <t>REFRIGERANTE COCA COLA 2L</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>5.49</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="110">
@@ -2401,15 +2401,15 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>100693</v>
+        <v>257710</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+          <t>SABAO BARRA YPE 5X160GR NEUTRO GLICERINA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>5.49</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="111">
@@ -2419,14 +2419,68 @@
         </is>
       </c>
       <c r="B111" t="n">
+        <v>261980</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>SABAO EM PO BRILHANTE 1,6KG LIMPEZA TOTA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>19.99</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>100705</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA 125GR TOMATE</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>100693</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SARDINHA GOMES DA COSTA LT 125GR OLEO</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>5.49</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>SEGUNDA - OFERTAS 26//05/25</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
         <v>100876</v>
       </c>
-      <c r="C111" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>TEMPERO ARISCO 1KG COMPLETO C/ PIMENTA</t>
         </is>
       </c>
-      <c r="D111" t="n">
+      <c r="D114" t="n">
         <v>14.99</v>
       </c>
     </row>
